--- a/BASE DE DATOS.xlsx
+++ b/BASE DE DATOS.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="J:\LAUNCH MANAGEMENT\1 KI\4_NX5a\09_Information\10_FTQ\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\almag\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4F3D65CE-BC26-4F02-AD01-F34EF512E388}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DD3F099B-30DF-44E5-A21F-CEDA2F809401}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{439F1396-05A1-464E-A03B-8C77E5396FAA}"/>
   </bookViews>
@@ -21,7 +21,7 @@
     <externalReference r:id="rId4"/>
   </externalReferences>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'BASE DE DATOS RIVIAN'!$B$4:$J$13</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'BASE DE DATOS RIVIAN'!$B$4:$J$33</definedName>
     <definedName name="DATA_01">[1]Data_Lineal!$H$4:$Y$30</definedName>
     <definedName name="DB_01">#REF!</definedName>
     <definedName name="DB_CAP01">'[2]CAPACIDAD (1)'!$X$9:$AM$29</definedName>
@@ -64,7 +64,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="119" uniqueCount="39">
   <si>
     <t>*</t>
   </si>
@@ -111,40 +111,76 @@
     <t>PRODUCCIÓN</t>
   </si>
   <si>
-    <t>KIA</t>
-  </si>
-  <si>
     <t>1100A</t>
   </si>
   <si>
-    <t>No coloca puntos de grasa Op.100</t>
+    <t>Falso rechazo Op.1100A</t>
   </si>
   <si>
-    <t>Falla detección en cámara Op.200</t>
+    <t>1100B</t>
   </si>
   <si>
-    <t>Falla detección de palanca por cámara Op.300</t>
+    <t>Hyundai/KIA</t>
   </si>
   <si>
-    <t>Falla detección en cámara Op.600</t>
+    <t>Falta de puntos de grasa Op.100</t>
   </si>
   <si>
-    <t>Coloca corredera en posicion incorrecta Op.400</t>
+    <t>Corredera mal posicionada Op.400</t>
   </si>
   <si>
-    <t>Corto en soldadura Op.800</t>
+    <t>Corto de soldadura Op.800</t>
   </si>
   <si>
-    <t>Falta de soldeo Op.800</t>
+    <t>Falta de soldadura Op.800</t>
   </si>
   <si>
-    <t>Falta de soldeo Op.1100A</t>
+    <t>Falta de soldadura Op.1100A</t>
   </si>
   <si>
-    <t>Falla en detección de cable en spiral Op.1100A</t>
+    <t>Lever Barcode Scan Facture Op.300</t>
   </si>
   <si>
-    <t>Falso rechazo Op.1100A</t>
+    <t>Falla en lectura de Scanner Op.300</t>
+  </si>
+  <si>
+    <t>Falla de inspección visual Op.200</t>
+  </si>
+  <si>
+    <t>Falla de inspección visual Op.300</t>
+  </si>
+  <si>
+    <t>Falla de inspección visual Op.600</t>
+  </si>
+  <si>
+    <t>Falla de inspección visual Op.400</t>
+  </si>
+  <si>
+    <t>Falla de sensor Op.400</t>
+  </si>
+  <si>
+    <t>Falla en lectura de Scanner Op.400</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SFC 965827AGG00003 is not in queue at operation </t>
+  </si>
+  <si>
+    <t>Material Towerdid</t>
+  </si>
+  <si>
+    <t>Falla de isnpección visual en spiral Op.700</t>
+  </si>
+  <si>
+    <t>Falla en atornillado Op.700</t>
+  </si>
+  <si>
+    <t>Falla sin especificación Op.900</t>
+  </si>
+  <si>
+    <t>Mal embobinado en spiral Op.1100A</t>
+  </si>
+  <si>
+    <t>Falla sin especificación Op.1100A</t>
   </si>
 </sst>
 </file>
@@ -155,7 +191,7 @@
     <numFmt numFmtId="164" formatCode="0.0%"/>
     <numFmt numFmtId="165" formatCode="0.000"/>
   </numFmts>
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -190,6 +226,14 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -218,7 +262,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -244,22 +288,24 @@
     <xf numFmtId="14" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Percent" xfId="1" builtinId="5"/>
+    <cellStyle name="Porcentaje" xfId="1" builtinId="5"/>
   </cellStyles>
   <dxfs count="21">
-    <dxf>
-      <numFmt numFmtId="1" formatCode="0"/>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
     <dxf>
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
@@ -268,12 +314,6 @@
     </dxf>
     <dxf>
       <numFmt numFmtId="1" formatCode="0"/>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
@@ -305,6 +345,16 @@
     </dxf>
     <dxf>
       <numFmt numFmtId="165" formatCode="0.000"/>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="1" formatCode="0"/>
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
@@ -24235,24 +24285,24 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{421FD8D0-4DB9-4A88-8653-0AE7AE89107A}" name="Tabla158" displayName="Tabla158" ref="B4:K13" totalsRowShown="0" headerRowDxfId="20" dataDxfId="19">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{421FD8D0-4DB9-4A88-8653-0AE7AE89107A}" name="Tabla158" displayName="Tabla158" ref="B4:K33" totalsRowShown="0" headerRowDxfId="20" dataDxfId="19">
   <tableColumns count="10">
     <tableColumn id="1" xr3:uid="{CDAA4D20-2955-41E2-BD7E-9330E166FFF4}" name="Fecha" dataDxfId="18"/>
     <tableColumn id="9" xr3:uid="{F70BB124-92DE-4024-874C-EE3BA966CDE6}" name="Semana" dataDxfId="17">
       <calculatedColumnFormula>WEEKNUM(Tabla158[[#This Row],[Fecha]])</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="2" xr3:uid="{FA1D52AD-522F-4EBC-834E-34285D7CD057}" name="Línea" dataDxfId="16"/>
-    <tableColumn id="3" xr3:uid="{817EDB5C-DF57-41CB-B733-E61AAABF8CCA}" name="Maquina" dataDxfId="5"/>
-    <tableColumn id="4" xr3:uid="{5F1693BE-115D-44D5-AF56-1D264ADD732C}" name="Version" dataDxfId="3"/>
-    <tableColumn id="5" xr3:uid="{5338F4E1-D693-43F8-949D-571F0CE39E9A}" name="Piezas OK" dataDxfId="4"/>
-    <tableColumn id="6" xr3:uid="{3D66411F-A368-4E6A-B088-6142D3936EC3}" name="Piezas NOK" dataDxfId="15"/>
-    <tableColumn id="10" xr3:uid="{C4AB812D-0BAE-4D93-864F-897D5721DC95}" name="Division " dataDxfId="14">
+    <tableColumn id="3" xr3:uid="{817EDB5C-DF57-41CB-B733-E61AAABF8CCA}" name="Maquina" dataDxfId="15"/>
+    <tableColumn id="4" xr3:uid="{5F1693BE-115D-44D5-AF56-1D264ADD732C}" name="Version" dataDxfId="14"/>
+    <tableColumn id="5" xr3:uid="{5338F4E1-D693-43F8-949D-571F0CE39E9A}" name="Piezas OK" dataDxfId="13"/>
+    <tableColumn id="6" xr3:uid="{3D66411F-A368-4E6A-B088-6142D3936EC3}" name="Piezas NOK" dataDxfId="12"/>
+    <tableColumn id="10" xr3:uid="{C4AB812D-0BAE-4D93-864F-897D5721DC95}" name="Division " dataDxfId="11">
       <calculatedColumnFormula>Tabla158[[#This Row],[Piezas NOK]]/Tabla158[[#This Row],[Piezas OK]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="8" xr3:uid="{F39DB17C-B4B4-4352-B595-2330856B09A4}" name="FTQ" dataDxfId="13">
+    <tableColumn id="8" xr3:uid="{F39DB17C-B4B4-4352-B595-2330856B09A4}" name="FTQ" dataDxfId="10">
       <calculatedColumnFormula>ABS(G$3-I5)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="12" xr3:uid="{09CB875C-7FE1-4B1A-9517-6670DA724128}" name="%" dataDxfId="12">
+    <tableColumn id="12" xr3:uid="{09CB875C-7FE1-4B1A-9517-6670DA724128}" name="%" dataDxfId="9">
       <calculatedColumnFormula>Tabla158[[#This Row],[FTQ]]</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -24261,17 +24311,17 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{83880157-341F-4984-9DA8-9308A0C526D5}" name="Tabla2610" displayName="Tabla2610" ref="M4:S14" totalsRowShown="0" headerRowDxfId="11" dataDxfId="10">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{83880157-341F-4984-9DA8-9308A0C526D5}" name="Tabla2610" displayName="Tabla2610" ref="M4:S30" totalsRowShown="0" headerRowDxfId="8" dataDxfId="7">
   <tableColumns count="7">
-    <tableColumn id="1" xr3:uid="{D688BA2E-A64E-4433-85E0-7EDBF854AF60}" name="Fecha" dataDxfId="9"/>
-    <tableColumn id="7" xr3:uid="{D3EA5E8D-DD68-48AC-8DAC-4A4077839479}" name="Semana" dataDxfId="8">
+    <tableColumn id="1" xr3:uid="{D688BA2E-A64E-4433-85E0-7EDBF854AF60}" name="Fecha" dataDxfId="6"/>
+    <tableColumn id="7" xr3:uid="{D3EA5E8D-DD68-48AC-8DAC-4A4077839479}" name="Semana" dataDxfId="5">
       <calculatedColumnFormula>WEEKNUM(Tabla2610[[#This Row],[Fecha]])</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{2BBDA3EE-1089-4999-82D7-821DAA1CF033}" name="Línea" dataDxfId="7"/>
-    <tableColumn id="3" xr3:uid="{A327B0AF-C947-4083-8F0A-4A5908FD3558}" name="Maquina" dataDxfId="2"/>
-    <tableColumn id="4" xr3:uid="{58C9F38E-D89E-450A-9CAA-EFCECBECC74C}" name="Version" dataDxfId="0"/>
+    <tableColumn id="2" xr3:uid="{2BBDA3EE-1089-4999-82D7-821DAA1CF033}" name="Línea" dataDxfId="4"/>
+    <tableColumn id="3" xr3:uid="{A327B0AF-C947-4083-8F0A-4A5908FD3558}" name="Maquina" dataDxfId="3"/>
+    <tableColumn id="4" xr3:uid="{58C9F38E-D89E-450A-9CAA-EFCECBECC74C}" name="Version" dataDxfId="2"/>
     <tableColumn id="5" xr3:uid="{5C95C72F-200A-46B3-A6FC-20E7D88A7BCD}" name="Defecto" dataDxfId="1"/>
-    <tableColumn id="6" xr3:uid="{33109690-8A43-4F38-8F52-FD73CBA9F32F}" name="Cantidad" dataDxfId="6"/>
+    <tableColumn id="6" xr3:uid="{33109690-8A43-4F38-8F52-FD73CBA9F32F}" name="Cantidad" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -24541,7 +24591,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{05A1B645-8848-474A-88BA-FA9209B01B4F}">
   <dimension ref="A1:V831"/>
-  <sheetFormatPr defaultColWidth="11.5546875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.5546875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="3.77734375" customWidth="1"/>
     <col min="2" max="2" width="13.21875" style="1" customWidth="1"/>
@@ -24555,7 +24605,7 @@
     <col min="12" max="12" width="2.44140625" customWidth="1"/>
     <col min="13" max="13" width="13.88671875" style="1" customWidth="1"/>
     <col min="14" max="14" width="10.5546875" style="1" customWidth="1"/>
-    <col min="15" max="15" width="9.88671875" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="12.44140625" style="1" customWidth="1"/>
     <col min="16" max="16" width="13.21875" style="1" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="11.77734375" style="1" bestFit="1" customWidth="1"/>
     <col min="18" max="18" width="47.5546875" style="1" customWidth="1"/>
@@ -24563,46 +24613,46 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:19" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B1" s="9" t="s">
+      <c r="B1" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="C1" s="9"/>
-      <c r="D1" s="9"/>
-      <c r="E1" s="9"/>
-      <c r="F1" s="9"/>
-      <c r="G1" s="9"/>
-      <c r="H1" s="9"/>
-      <c r="I1" s="9"/>
-      <c r="J1" s="9"/>
+      <c r="C1" s="10"/>
+      <c r="D1" s="10"/>
+      <c r="E1" s="10"/>
+      <c r="F1" s="10"/>
+      <c r="G1" s="10"/>
+      <c r="H1" s="10"/>
+      <c r="I1" s="10"/>
+      <c r="J1" s="10"/>
       <c r="K1" s="6"/>
-      <c r="M1" s="9" t="s">
+      <c r="M1" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="N1" s="9"/>
-      <c r="O1" s="9"/>
-      <c r="P1" s="9"/>
-      <c r="Q1" s="9"/>
-      <c r="R1" s="9"/>
-      <c r="S1" s="9"/>
+      <c r="N1" s="10"/>
+      <c r="O1" s="10"/>
+      <c r="P1" s="10"/>
+      <c r="Q1" s="10"/>
+      <c r="R1" s="10"/>
+      <c r="S1" s="10"/>
     </row>
     <row r="2" spans="2:19" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="9"/>
-      <c r="C2" s="9"/>
-      <c r="D2" s="9"/>
-      <c r="E2" s="9"/>
-      <c r="F2" s="9"/>
-      <c r="G2" s="9"/>
-      <c r="H2" s="9"/>
-      <c r="I2" s="9"/>
-      <c r="J2" s="9"/>
+      <c r="B2" s="10"/>
+      <c r="C2" s="10"/>
+      <c r="D2" s="10"/>
+      <c r="E2" s="10"/>
+      <c r="F2" s="10"/>
+      <c r="G2" s="10"/>
+      <c r="H2" s="10"/>
+      <c r="I2" s="10"/>
+      <c r="J2" s="10"/>
       <c r="K2" s="6"/>
-      <c r="M2" s="9"/>
-      <c r="N2" s="9"/>
-      <c r="O2" s="9"/>
-      <c r="P2" s="9"/>
-      <c r="Q2" s="9"/>
-      <c r="R2" s="9"/>
-      <c r="S2" s="9"/>
+      <c r="M2" s="10"/>
+      <c r="N2" s="10"/>
+      <c r="O2" s="10"/>
+      <c r="P2" s="10"/>
+      <c r="Q2" s="10"/>
+      <c r="R2" s="10"/>
+      <c r="S2" s="10"/>
     </row>
     <row r="3" spans="2:19" x14ac:dyDescent="0.3">
       <c r="G3" s="1">
@@ -24674,12 +24724,12 @@
         <v>29</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="E5" s="1">
         <v>100</v>
       </c>
-      <c r="F5" s="10">
+      <c r="F5" s="9">
         <v>12264732</v>
       </c>
       <c r="G5" s="1">
@@ -24708,16 +24758,16 @@
         <v>29</v>
       </c>
       <c r="O5" s="1" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="P5" s="1">
         <v>100</v>
       </c>
-      <c r="Q5" s="10">
+      <c r="Q5" s="9">
         <v>12264732</v>
       </c>
       <c r="R5" s="1" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="S5" s="1">
         <v>1</v>
@@ -24732,12 +24782,12 @@
         <v>29</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="E6" s="1">
         <v>200</v>
       </c>
-      <c r="F6" s="10">
+      <c r="F6" s="9">
         <v>12264732</v>
       </c>
       <c r="G6" s="1">
@@ -24766,16 +24816,16 @@
         <v>29</v>
       </c>
       <c r="O6" s="1" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="P6" s="1">
         <v>200</v>
       </c>
-      <c r="Q6" s="10">
+      <c r="Q6" s="9">
         <v>12264732</v>
       </c>
       <c r="R6" s="1" t="s">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="S6" s="1">
         <v>1</v>
@@ -24790,12 +24840,12 @@
         <v>29</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="E7" s="1">
         <v>300</v>
       </c>
-      <c r="F7" s="10">
+      <c r="F7" s="9">
         <v>12264732</v>
       </c>
       <c r="G7" s="1">
@@ -24824,16 +24874,16 @@
         <v>29</v>
       </c>
       <c r="O7" s="1" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="P7" s="1">
         <v>300</v>
       </c>
-      <c r="Q7" s="10">
+      <c r="Q7" s="9">
         <v>12264732</v>
       </c>
       <c r="R7" s="1" t="s">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="S7" s="1">
         <v>3</v>
@@ -24848,12 +24898,12 @@
         <v>29</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="E8" s="1">
         <v>400</v>
       </c>
-      <c r="F8" s="10">
+      <c r="F8" s="9">
         <v>12264732</v>
       </c>
       <c r="G8" s="1">
@@ -24882,16 +24932,16 @@
         <v>29</v>
       </c>
       <c r="O8" s="1" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="P8" s="1">
         <v>400</v>
       </c>
-      <c r="Q8" s="10">
+      <c r="Q8" s="9">
         <v>12264732</v>
       </c>
       <c r="R8" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="S8" s="1">
         <v>79</v>
@@ -24906,12 +24956,12 @@
         <v>29</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="E9" s="1">
         <v>600</v>
       </c>
-      <c r="F9" s="10">
+      <c r="F9" s="9">
         <v>12264732</v>
       </c>
       <c r="G9" s="1">
@@ -24940,16 +24990,16 @@
         <v>29</v>
       </c>
       <c r="O9" s="1" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="P9" s="1">
         <v>600</v>
       </c>
-      <c r="Q9" s="10">
+      <c r="Q9" s="9">
         <v>12264732</v>
       </c>
       <c r="R9" s="1" t="s">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="S9" s="1">
         <v>1</v>
@@ -24964,12 +25014,12 @@
         <v>29</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="E10" s="1">
         <v>700</v>
       </c>
-      <c r="F10" s="10">
+      <c r="F10" s="9">
         <v>12264732</v>
       </c>
       <c r="G10" s="1">
@@ -24998,16 +25048,16 @@
         <v>29</v>
       </c>
       <c r="O10" s="1" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="P10" s="1">
         <v>800</v>
       </c>
-      <c r="Q10" s="10">
+      <c r="Q10" s="9">
         <v>12264732</v>
       </c>
       <c r="R10" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="S10" s="1">
         <v>3</v>
@@ -25022,12 +25072,12 @@
         <v>29</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="E11" s="1">
         <v>800</v>
       </c>
-      <c r="F11" s="10">
+      <c r="F11" s="9">
         <v>12264732</v>
       </c>
       <c r="G11" s="1">
@@ -25056,16 +25106,16 @@
         <v>29</v>
       </c>
       <c r="O11" s="1" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="P11" s="1">
         <v>800</v>
       </c>
-      <c r="Q11" s="10">
+      <c r="Q11" s="9">
         <v>12264732</v>
       </c>
       <c r="R11" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="S11" s="1">
         <v>9</v>
@@ -25080,12 +25130,12 @@
         <v>29</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="E12" s="1">
         <v>900</v>
       </c>
-      <c r="F12" s="10">
+      <c r="F12" s="9">
         <v>12264732</v>
       </c>
       <c r="G12" s="1">
@@ -25114,16 +25164,16 @@
         <v>29</v>
       </c>
       <c r="O12" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="P12" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="P12" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="Q12" s="10">
+      <c r="Q12" s="9">
         <v>12264732</v>
       </c>
       <c r="R12" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="S12" s="1">
         <v>1</v>
@@ -25138,12 +25188,12 @@
         <v>29</v>
       </c>
       <c r="D13" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="E13" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="E13" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="F13" s="10">
+      <c r="F13" s="9">
         <v>12264732</v>
       </c>
       <c r="G13" s="1">
@@ -25172,26 +25222,56 @@
         <v>29</v>
       </c>
       <c r="O13" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="P13" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="P13" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="Q13" s="10">
+      <c r="Q13" s="9">
         <v>12264732</v>
       </c>
       <c r="R13" s="1" t="s">
-        <v>25</v>
+        <v>37</v>
       </c>
       <c r="S13" s="1">
         <v>1</v>
       </c>
     </row>
     <row r="14" spans="2:19" x14ac:dyDescent="0.3">
-      <c r="B14" s="4"/>
-      <c r="I14" s="3"/>
-      <c r="J14" s="1"/>
-      <c r="K14" s="5"/>
+      <c r="B14" s="4">
+        <v>46220</v>
+      </c>
+      <c r="C14" s="11">
+        <f>WEEKNUM(Tabla158[[#This Row],[Fecha]])</f>
+        <v>29</v>
+      </c>
+      <c r="D14" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="E14" s="1">
+        <v>100</v>
+      </c>
+      <c r="F14" s="9">
+        <v>12264732</v>
+      </c>
+      <c r="G14" s="1">
+        <v>130</v>
+      </c>
+      <c r="H14" s="1">
+        <v>0</v>
+      </c>
+      <c r="I14" s="3">
+        <f>Tabla158[[#This Row],[Piezas NOK]]/Tabla158[[#This Row],[Piezas OK]]</f>
+        <v>0</v>
+      </c>
+      <c r="J14" s="11">
+        <f t="shared" ref="J14:J22" si="1">ABS(G$3-I14)</f>
+        <v>1</v>
+      </c>
+      <c r="K14" s="5">
+        <f>Tabla158[[#This Row],[FTQ]]</f>
+        <v>1</v>
+      </c>
       <c r="M14" s="4">
         <v>46217</v>
       </c>
@@ -25200,152 +25280,1060 @@
         <v>29</v>
       </c>
       <c r="O14" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="P14" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="P14" s="1" t="s">
+      <c r="Q14" s="9">
+        <v>12264732</v>
+      </c>
+      <c r="R14" s="1" t="s">
         <v>16</v>
-      </c>
-      <c r="Q14" s="10">
-        <v>12264732</v>
-      </c>
-      <c r="R14" s="1" t="s">
-        <v>26</v>
       </c>
       <c r="S14" s="1">
         <v>1</v>
       </c>
     </row>
     <row r="15" spans="2:19" x14ac:dyDescent="0.3">
-      <c r="B15" s="4"/>
-      <c r="I15" s="3"/>
-      <c r="J15" s="1"/>
-      <c r="K15" s="5"/>
-      <c r="M15" s="4"/>
+      <c r="B15" s="4">
+        <v>46220</v>
+      </c>
+      <c r="C15" s="11">
+        <f>WEEKNUM(Tabla158[[#This Row],[Fecha]])</f>
+        <v>29</v>
+      </c>
+      <c r="D15" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="E15" s="1">
+        <v>200</v>
+      </c>
+      <c r="F15" s="9">
+        <v>12264732</v>
+      </c>
+      <c r="G15" s="1">
+        <v>61</v>
+      </c>
+      <c r="H15" s="1">
+        <v>3</v>
+      </c>
+      <c r="I15" s="3">
+        <f>Tabla158[[#This Row],[Piezas NOK]]/Tabla158[[#This Row],[Piezas OK]]</f>
+        <v>4.9180327868852458E-2</v>
+      </c>
+      <c r="J15" s="11">
+        <f t="shared" si="1"/>
+        <v>0.95081967213114749</v>
+      </c>
+      <c r="K15" s="5">
+        <f>Tabla158[[#This Row],[FTQ]]</f>
+        <v>0.95081967213114749</v>
+      </c>
+      <c r="M15" s="4">
+        <v>46220</v>
+      </c>
+      <c r="N15" s="11">
+        <f>WEEKNUM(Tabla2610[[#This Row],[Fecha]])</f>
+        <v>29</v>
+      </c>
+      <c r="O15" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="P15" s="1">
+        <v>100</v>
+      </c>
+      <c r="Q15" s="9">
+        <v>12264732</v>
+      </c>
+      <c r="R15" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="S15" s="1">
+        <v>3</v>
+      </c>
     </row>
     <row r="16" spans="2:19" x14ac:dyDescent="0.3">
-      <c r="B16" s="4"/>
-      <c r="I16" s="3"/>
-      <c r="J16" s="1"/>
-      <c r="K16" s="5"/>
-      <c r="M16" s="4"/>
-    </row>
-    <row r="17" spans="2:13" x14ac:dyDescent="0.3">
-      <c r="B17" s="4"/>
-      <c r="I17" s="3"/>
-      <c r="J17" s="1"/>
-      <c r="K17" s="5"/>
-      <c r="M17" s="4"/>
-    </row>
-    <row r="18" spans="2:13" x14ac:dyDescent="0.3">
-      <c r="B18" s="4"/>
-      <c r="I18" s="3"/>
-      <c r="J18" s="1"/>
-      <c r="K18" s="5"/>
-      <c r="M18" s="4"/>
-    </row>
-    <row r="19" spans="2:13" x14ac:dyDescent="0.3">
-      <c r="B19" s="4"/>
-      <c r="I19" s="3"/>
-      <c r="J19" s="1"/>
-      <c r="K19" s="5"/>
-      <c r="M19" s="4"/>
-    </row>
-    <row r="20" spans="2:13" x14ac:dyDescent="0.3">
-      <c r="B20" s="4"/>
-      <c r="I20" s="3"/>
-      <c r="J20" s="1"/>
-      <c r="K20" s="5"/>
-      <c r="M20" s="4"/>
-    </row>
-    <row r="21" spans="2:13" x14ac:dyDescent="0.3">
-      <c r="B21" s="4"/>
-      <c r="I21" s="3"/>
-      <c r="J21" s="1"/>
-      <c r="K21" s="5"/>
-      <c r="M21" s="4"/>
-    </row>
-    <row r="22" spans="2:13" x14ac:dyDescent="0.3">
-      <c r="B22" s="4"/>
-      <c r="I22" s="3"/>
-      <c r="J22" s="1"/>
-      <c r="K22" s="5"/>
-      <c r="M22" s="4"/>
-    </row>
-    <row r="23" spans="2:13" x14ac:dyDescent="0.3">
-      <c r="B23" s="4"/>
-      <c r="I23" s="3"/>
-      <c r="J23" s="1"/>
-      <c r="K23" s="5"/>
-      <c r="M23" s="4"/>
-    </row>
-    <row r="24" spans="2:13" x14ac:dyDescent="0.3">
-      <c r="B24" s="4"/>
-      <c r="I24" s="3"/>
-      <c r="J24" s="1"/>
-      <c r="K24" s="5"/>
-      <c r="M24" s="4"/>
-    </row>
-    <row r="25" spans="2:13" x14ac:dyDescent="0.3">
-      <c r="B25" s="4"/>
-      <c r="I25" s="3"/>
-      <c r="J25" s="1"/>
-      <c r="K25" s="5"/>
-      <c r="M25" s="4"/>
-    </row>
-    <row r="26" spans="2:13" x14ac:dyDescent="0.3">
-      <c r="B26" s="4"/>
-      <c r="I26" s="3"/>
-      <c r="J26" s="1"/>
-      <c r="K26" s="5"/>
-      <c r="M26" s="4"/>
-    </row>
-    <row r="27" spans="2:13" x14ac:dyDescent="0.3">
-      <c r="B27" s="4"/>
-      <c r="I27" s="3"/>
-      <c r="J27" s="1"/>
-      <c r="K27" s="5"/>
-      <c r="M27" s="4"/>
-    </row>
-    <row r="28" spans="2:13" x14ac:dyDescent="0.3">
-      <c r="B28" s="4"/>
-      <c r="I28" s="3"/>
-      <c r="J28" s="1"/>
-      <c r="K28" s="5"/>
-      <c r="M28" s="4"/>
-    </row>
-    <row r="29" spans="2:13" x14ac:dyDescent="0.3">
-      <c r="B29" s="4"/>
-      <c r="I29" s="3"/>
-      <c r="J29" s="1"/>
-      <c r="K29" s="5"/>
-      <c r="M29" s="4"/>
-    </row>
-    <row r="30" spans="2:13" x14ac:dyDescent="0.3">
-      <c r="B30" s="4"/>
-      <c r="I30" s="3"/>
-      <c r="J30" s="1"/>
-      <c r="K30" s="5"/>
-      <c r="M30" s="4"/>
-    </row>
-    <row r="31" spans="2:13" x14ac:dyDescent="0.3">
-      <c r="B31" s="4"/>
-      <c r="I31" s="3"/>
-      <c r="J31" s="1"/>
-      <c r="K31" s="5"/>
+      <c r="B16" s="4">
+        <v>46220</v>
+      </c>
+      <c r="C16" s="11">
+        <f>WEEKNUM(Tabla158[[#This Row],[Fecha]])</f>
+        <v>29</v>
+      </c>
+      <c r="D16" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="E16" s="1">
+        <v>300</v>
+      </c>
+      <c r="F16" s="9">
+        <v>12264732</v>
+      </c>
+      <c r="G16" s="1">
+        <v>70</v>
+      </c>
+      <c r="H16" s="1">
+        <v>20</v>
+      </c>
+      <c r="I16" s="3">
+        <f>Tabla158[[#This Row],[Piezas NOK]]/Tabla158[[#This Row],[Piezas OK]]</f>
+        <v>0.2857142857142857</v>
+      </c>
+      <c r="J16" s="11">
+        <f t="shared" si="1"/>
+        <v>0.7142857142857143</v>
+      </c>
+      <c r="K16" s="5">
+        <f>Tabla158[[#This Row],[FTQ]]</f>
+        <v>0.7142857142857143</v>
+      </c>
+      <c r="M16" s="4">
+        <v>46220</v>
+      </c>
+      <c r="N16" s="11">
+        <f>WEEKNUM(Tabla2610[[#This Row],[Fecha]])</f>
+        <v>29</v>
+      </c>
+      <c r="O16" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="P16" s="1">
+        <v>300</v>
+      </c>
+      <c r="Q16" s="9">
+        <v>12264732</v>
+      </c>
+      <c r="R16" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="S16" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="17" spans="2:19" x14ac:dyDescent="0.3">
+      <c r="B17" s="4">
+        <v>46220</v>
+      </c>
+      <c r="C17" s="11">
+        <f>WEEKNUM(Tabla158[[#This Row],[Fecha]])</f>
+        <v>29</v>
+      </c>
+      <c r="D17" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="E17" s="1">
+        <v>400</v>
+      </c>
+      <c r="F17" s="9">
+        <v>12264732</v>
+      </c>
+      <c r="G17" s="1">
+        <v>77</v>
+      </c>
+      <c r="H17" s="1">
+        <v>35</v>
+      </c>
+      <c r="I17" s="3">
+        <f>Tabla158[[#This Row],[Piezas NOK]]/Tabla158[[#This Row],[Piezas OK]]</f>
+        <v>0.45454545454545453</v>
+      </c>
+      <c r="J17" s="11">
+        <f t="shared" si="1"/>
+        <v>0.54545454545454541</v>
+      </c>
+      <c r="K17" s="5">
+        <f>Tabla158[[#This Row],[FTQ]]</f>
+        <v>0.54545454545454541</v>
+      </c>
+      <c r="M17" s="4">
+        <v>46220</v>
+      </c>
+      <c r="N17" s="11">
+        <f>WEEKNUM(Tabla2610[[#This Row],[Fecha]])</f>
+        <v>29</v>
+      </c>
+      <c r="O17" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="P17" s="1">
+        <v>300</v>
+      </c>
+      <c r="Q17" s="9">
+        <v>12264732</v>
+      </c>
+      <c r="R17" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="S17" s="1">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="18" spans="2:19" x14ac:dyDescent="0.3">
+      <c r="B18" s="4">
+        <v>46220</v>
+      </c>
+      <c r="C18" s="11">
+        <f>WEEKNUM(Tabla158[[#This Row],[Fecha]])</f>
+        <v>29</v>
+      </c>
+      <c r="D18" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="E18" s="1">
+        <v>600</v>
+      </c>
+      <c r="F18" s="9">
+        <v>12264732</v>
+      </c>
+      <c r="G18" s="1">
+        <v>77</v>
+      </c>
+      <c r="H18" s="1">
+        <v>8</v>
+      </c>
+      <c r="I18" s="3">
+        <f>Tabla158[[#This Row],[Piezas NOK]]/Tabla158[[#This Row],[Piezas OK]]</f>
+        <v>0.1038961038961039</v>
+      </c>
+      <c r="J18" s="11">
+        <f t="shared" si="1"/>
+        <v>0.89610389610389607</v>
+      </c>
+      <c r="K18" s="5">
+        <f>Tabla158[[#This Row],[FTQ]]</f>
+        <v>0.89610389610389607</v>
+      </c>
+      <c r="M18" s="4">
+        <v>46220</v>
+      </c>
+      <c r="N18" s="11">
+        <f>WEEKNUM(Tabla2610[[#This Row],[Fecha]])</f>
+        <v>29</v>
+      </c>
+      <c r="O18" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="P18" s="1">
+        <v>300</v>
+      </c>
+      <c r="Q18" s="9">
+        <v>12264732</v>
+      </c>
+      <c r="R18" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="S18" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="19" spans="2:19" x14ac:dyDescent="0.3">
+      <c r="B19" s="4">
+        <v>46220</v>
+      </c>
+      <c r="C19" s="11">
+        <f>WEEKNUM(Tabla158[[#This Row],[Fecha]])</f>
+        <v>29</v>
+      </c>
+      <c r="D19" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="E19" s="1">
+        <v>700</v>
+      </c>
+      <c r="F19" s="9">
+        <v>12264732</v>
+      </c>
+      <c r="G19" s="1">
+        <v>61</v>
+      </c>
+      <c r="H19" s="1">
+        <v>5</v>
+      </c>
+      <c r="I19" s="3">
+        <f>Tabla158[[#This Row],[Piezas NOK]]/Tabla158[[#This Row],[Piezas OK]]</f>
+        <v>8.1967213114754092E-2</v>
+      </c>
+      <c r="J19" s="11">
+        <f t="shared" si="1"/>
+        <v>0.91803278688524592</v>
+      </c>
+      <c r="K19" s="5">
+        <f>Tabla158[[#This Row],[FTQ]]</f>
+        <v>0.91803278688524592</v>
+      </c>
+      <c r="M19" s="4">
+        <v>46220</v>
+      </c>
+      <c r="N19" s="11">
+        <f>WEEKNUM(Tabla2610[[#This Row],[Fecha]])</f>
+        <v>29</v>
+      </c>
+      <c r="O19" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="P19" s="1">
+        <v>400</v>
+      </c>
+      <c r="Q19" s="9">
+        <v>12264732</v>
+      </c>
+      <c r="R19" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="S19" s="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="20" spans="2:19" x14ac:dyDescent="0.3">
+      <c r="B20" s="4">
+        <v>46220</v>
+      </c>
+      <c r="C20" s="11">
+        <f>WEEKNUM(Tabla158[[#This Row],[Fecha]])</f>
+        <v>29</v>
+      </c>
+      <c r="D20" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="E20" s="1">
+        <v>800</v>
+      </c>
+      <c r="F20" s="9">
+        <v>12264732</v>
+      </c>
+      <c r="G20" s="1">
+        <v>55</v>
+      </c>
+      <c r="H20" s="1">
+        <v>3</v>
+      </c>
+      <c r="I20" s="3">
+        <f>Tabla158[[#This Row],[Piezas NOK]]/Tabla158[[#This Row],[Piezas OK]]</f>
+        <v>5.4545454545454543E-2</v>
+      </c>
+      <c r="J20" s="11">
+        <f t="shared" si="1"/>
+        <v>0.94545454545454544</v>
+      </c>
+      <c r="K20" s="5">
+        <f>Tabla158[[#This Row],[FTQ]]</f>
+        <v>0.94545454545454544</v>
+      </c>
+      <c r="M20" s="4">
+        <v>46220</v>
+      </c>
+      <c r="N20" s="11">
+        <f>WEEKNUM(Tabla2610[[#This Row],[Fecha]])</f>
+        <v>29</v>
+      </c>
+      <c r="O20" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="P20" s="1">
+        <v>400</v>
+      </c>
+      <c r="Q20" s="9">
+        <v>12264732</v>
+      </c>
+      <c r="R20" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="S20" s="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="2:19" x14ac:dyDescent="0.3">
+      <c r="B21" s="4">
+        <v>46220</v>
+      </c>
+      <c r="C21" s="11">
+        <f>WEEKNUM(Tabla158[[#This Row],[Fecha]])</f>
+        <v>29</v>
+      </c>
+      <c r="D21" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="E21" s="1">
+        <v>900</v>
+      </c>
+      <c r="F21" s="9">
+        <v>12264732</v>
+      </c>
+      <c r="G21" s="1">
+        <v>55</v>
+      </c>
+      <c r="H21" s="1">
+        <v>4</v>
+      </c>
+      <c r="I21" s="3">
+        <f>Tabla158[[#This Row],[Piezas NOK]]/Tabla158[[#This Row],[Piezas OK]]</f>
+        <v>7.2727272727272724E-2</v>
+      </c>
+      <c r="J21" s="11">
+        <f t="shared" si="1"/>
+        <v>0.92727272727272725</v>
+      </c>
+      <c r="K21" s="5">
+        <f>Tabla158[[#This Row],[FTQ]]</f>
+        <v>0.92727272727272725</v>
+      </c>
+      <c r="M21" s="4">
+        <v>46220</v>
+      </c>
+      <c r="N21" s="11">
+        <f>WEEKNUM(Tabla2610[[#This Row],[Fecha]])</f>
+        <v>29</v>
+      </c>
+      <c r="O21" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="P21" s="1">
+        <v>400</v>
+      </c>
+      <c r="Q21" s="9">
+        <v>12264732</v>
+      </c>
+      <c r="R21" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="S21" s="1">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="22" spans="2:19" x14ac:dyDescent="0.3">
+      <c r="B22" s="4">
+        <v>46220</v>
+      </c>
+      <c r="C22" s="11">
+        <f>WEEKNUM(Tabla158[[#This Row],[Fecha]])</f>
+        <v>29</v>
+      </c>
+      <c r="D22" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="E22" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="F22" s="9">
+        <v>12264732</v>
+      </c>
+      <c r="G22" s="1">
+        <v>36</v>
+      </c>
+      <c r="H22" s="1">
+        <v>1</v>
+      </c>
+      <c r="I22" s="3">
+        <f>Tabla158[[#This Row],[Piezas NOK]]/Tabla158[[#This Row],[Piezas OK]]</f>
+        <v>2.7777777777777776E-2</v>
+      </c>
+      <c r="J22" s="11">
+        <f t="shared" si="1"/>
+        <v>0.97222222222222221</v>
+      </c>
+      <c r="K22" s="5">
+        <f>Tabla158[[#This Row],[FTQ]]</f>
+        <v>0.97222222222222221</v>
+      </c>
+      <c r="M22" s="4">
+        <v>46220</v>
+      </c>
+      <c r="N22" s="11">
+        <f>WEEKNUM(Tabla2610[[#This Row],[Fecha]])</f>
+        <v>29</v>
+      </c>
+      <c r="O22" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="P22" s="1">
+        <v>400</v>
+      </c>
+      <c r="Q22" s="9">
+        <v>12264732</v>
+      </c>
+      <c r="R22" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="S22" s="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" spans="2:19" x14ac:dyDescent="0.3">
+      <c r="B23" s="4">
+        <v>46220</v>
+      </c>
+      <c r="C23" s="11">
+        <f>WEEKNUM(Tabla158[[#This Row],[Fecha]])</f>
+        <v>29</v>
+      </c>
+      <c r="D23" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="E23" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F23" s="9">
+        <v>12264732</v>
+      </c>
+      <c r="G23" s="1">
+        <v>20</v>
+      </c>
+      <c r="H23" s="1">
+        <v>0</v>
+      </c>
+      <c r="I23" s="3">
+        <f>Tabla158[[#This Row],[Piezas NOK]]/Tabla158[[#This Row],[Piezas OK]]</f>
+        <v>0</v>
+      </c>
+      <c r="J23" s="11">
+        <f>ABS(G$3-I23)</f>
+        <v>1</v>
+      </c>
+      <c r="K23" s="5">
+        <f>Tabla158[[#This Row],[FTQ]]</f>
+        <v>1</v>
+      </c>
+      <c r="M23" s="4">
+        <v>46220</v>
+      </c>
+      <c r="N23" s="11">
+        <f>WEEKNUM(Tabla2610[[#This Row],[Fecha]])</f>
+        <v>29</v>
+      </c>
+      <c r="O23" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="P23" s="1">
+        <v>400</v>
+      </c>
+      <c r="Q23" s="9">
+        <v>12264732</v>
+      </c>
+      <c r="R23" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="S23" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="24" spans="2:19" x14ac:dyDescent="0.3">
+      <c r="B24" s="4">
+        <v>46220</v>
+      </c>
+      <c r="C24" s="11">
+        <f>WEEKNUM(Tabla158[[#This Row],[Fecha]])</f>
+        <v>29</v>
+      </c>
+      <c r="D24" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="E24" s="1">
+        <v>100</v>
+      </c>
+      <c r="F24" s="9">
+        <v>12264714</v>
+      </c>
+      <c r="G24" s="1">
+        <v>24</v>
+      </c>
+      <c r="H24" s="1">
+        <v>0</v>
+      </c>
+      <c r="I24" s="3">
+        <f>Tabla158[[#This Row],[Piezas NOK]]/Tabla158[[#This Row],[Piezas OK]]</f>
+        <v>0</v>
+      </c>
+      <c r="J24" s="11">
+        <f t="shared" ref="J24:J32" si="2">ABS(G$3-I24)</f>
+        <v>1</v>
+      </c>
+      <c r="K24" s="5">
+        <f>Tabla158[[#This Row],[FTQ]]</f>
+        <v>1</v>
+      </c>
+      <c r="M24" s="4">
+        <v>46220</v>
+      </c>
+      <c r="N24" s="11">
+        <f>WEEKNUM(Tabla2610[[#This Row],[Fecha]])</f>
+        <v>29</v>
+      </c>
+      <c r="O24" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="P24" s="1">
+        <v>600</v>
+      </c>
+      <c r="Q24" s="9">
+        <v>12264732</v>
+      </c>
+      <c r="R24" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="S24" s="1">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="25" spans="2:19" x14ac:dyDescent="0.3">
+      <c r="B25" s="4">
+        <v>46220</v>
+      </c>
+      <c r="C25" s="11">
+        <f>WEEKNUM(Tabla158[[#This Row],[Fecha]])</f>
+        <v>29</v>
+      </c>
+      <c r="D25" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="E25" s="1">
+        <v>200</v>
+      </c>
+      <c r="F25" s="9">
+        <v>12264714</v>
+      </c>
+      <c r="G25" s="1">
+        <v>24</v>
+      </c>
+      <c r="H25" s="1">
+        <v>0</v>
+      </c>
+      <c r="I25" s="3">
+        <f>Tabla158[[#This Row],[Piezas NOK]]/Tabla158[[#This Row],[Piezas OK]]</f>
+        <v>0</v>
+      </c>
+      <c r="J25" s="11">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+      <c r="K25" s="5">
+        <f>Tabla158[[#This Row],[FTQ]]</f>
+        <v>1</v>
+      </c>
+      <c r="M25" s="4">
+        <v>46220</v>
+      </c>
+      <c r="N25" s="11">
+        <f>WEEKNUM(Tabla2610[[#This Row],[Fecha]])</f>
+        <v>29</v>
+      </c>
+      <c r="O25" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="P25" s="1">
+        <v>600</v>
+      </c>
+      <c r="Q25" s="9">
+        <v>12264714</v>
+      </c>
+      <c r="R25" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="S25" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26" spans="2:19" x14ac:dyDescent="0.3">
+      <c r="B26" s="4">
+        <v>46220</v>
+      </c>
+      <c r="C26" s="11">
+        <f>WEEKNUM(Tabla158[[#This Row],[Fecha]])</f>
+        <v>29</v>
+      </c>
+      <c r="D26" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="E26" s="1">
+        <v>300</v>
+      </c>
+      <c r="F26" s="9">
+        <v>12264714</v>
+      </c>
+      <c r="G26" s="1">
+        <v>13</v>
+      </c>
+      <c r="H26" s="1">
+        <v>0</v>
+      </c>
+      <c r="I26" s="3">
+        <f>Tabla158[[#This Row],[Piezas NOK]]/Tabla158[[#This Row],[Piezas OK]]</f>
+        <v>0</v>
+      </c>
+      <c r="J26" s="11">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+      <c r="K26" s="5">
+        <f>Tabla158[[#This Row],[FTQ]]</f>
+        <v>1</v>
+      </c>
+      <c r="M26" s="4">
+        <v>46220</v>
+      </c>
+      <c r="N26" s="11">
+        <f>WEEKNUM(Tabla2610[[#This Row],[Fecha]])</f>
+        <v>29</v>
+      </c>
+      <c r="O26" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="P26" s="1">
+        <v>700</v>
+      </c>
+      <c r="Q26" s="9">
+        <v>12264732</v>
+      </c>
+      <c r="R26" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="S26" s="1">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="27" spans="2:19" x14ac:dyDescent="0.3">
+      <c r="B27" s="4">
+        <v>46220</v>
+      </c>
+      <c r="C27" s="11">
+        <f>WEEKNUM(Tabla158[[#This Row],[Fecha]])</f>
+        <v>29</v>
+      </c>
+      <c r="D27" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="E27" s="1">
+        <v>400</v>
+      </c>
+      <c r="F27" s="9">
+        <v>12264714</v>
+      </c>
+      <c r="G27" s="1">
+        <v>13</v>
+      </c>
+      <c r="H27" s="1">
+        <v>0</v>
+      </c>
+      <c r="I27" s="3">
+        <f>Tabla158[[#This Row],[Piezas NOK]]/Tabla158[[#This Row],[Piezas OK]]</f>
+        <v>0</v>
+      </c>
+      <c r="J27" s="11">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+      <c r="K27" s="5">
+        <f>Tabla158[[#This Row],[FTQ]]</f>
+        <v>1</v>
+      </c>
+      <c r="M27" s="4">
+        <v>46220</v>
+      </c>
+      <c r="N27" s="11">
+        <f>WEEKNUM(Tabla2610[[#This Row],[Fecha]])</f>
+        <v>29</v>
+      </c>
+      <c r="O27" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="P27" s="1">
+        <v>700</v>
+      </c>
+      <c r="Q27" s="9">
+        <v>12264732</v>
+      </c>
+      <c r="R27" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="S27" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="28" spans="2:19" x14ac:dyDescent="0.3">
+      <c r="B28" s="4">
+        <v>46220</v>
+      </c>
+      <c r="C28" s="11">
+        <f>WEEKNUM(Tabla158[[#This Row],[Fecha]])</f>
+        <v>29</v>
+      </c>
+      <c r="D28" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="E28" s="1">
+        <v>600</v>
+      </c>
+      <c r="F28" s="9">
+        <v>12264714</v>
+      </c>
+      <c r="G28" s="1">
+        <v>15</v>
+      </c>
+      <c r="H28" s="1">
+        <v>1</v>
+      </c>
+      <c r="I28" s="3">
+        <f>Tabla158[[#This Row],[Piezas NOK]]/Tabla158[[#This Row],[Piezas OK]]</f>
+        <v>6.6666666666666666E-2</v>
+      </c>
+      <c r="J28" s="11">
+        <f t="shared" si="2"/>
+        <v>0.93333333333333335</v>
+      </c>
+      <c r="K28" s="5">
+        <f>Tabla158[[#This Row],[FTQ]]</f>
+        <v>0.93333333333333335</v>
+      </c>
+      <c r="M28" s="4">
+        <v>46220</v>
+      </c>
+      <c r="N28" s="11">
+        <f>WEEKNUM(Tabla2610[[#This Row],[Fecha]])</f>
+        <v>29</v>
+      </c>
+      <c r="O28" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="P28" s="1">
+        <v>800</v>
+      </c>
+      <c r="Q28" s="9">
+        <v>12264732</v>
+      </c>
+      <c r="R28" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="S28" s="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="29" spans="2:19" x14ac:dyDescent="0.3">
+      <c r="B29" s="4">
+        <v>46220</v>
+      </c>
+      <c r="C29" s="11">
+        <f>WEEKNUM(Tabla158[[#This Row],[Fecha]])</f>
+        <v>29</v>
+      </c>
+      <c r="D29" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="E29" s="1">
+        <v>700</v>
+      </c>
+      <c r="F29" s="9">
+        <v>12264714</v>
+      </c>
+      <c r="G29" s="1">
+        <v>15</v>
+      </c>
+      <c r="H29" s="1">
+        <v>0</v>
+      </c>
+      <c r="I29" s="3">
+        <f>Tabla158[[#This Row],[Piezas NOK]]/Tabla158[[#This Row],[Piezas OK]]</f>
+        <v>0</v>
+      </c>
+      <c r="J29" s="11">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+      <c r="K29" s="5">
+        <f>Tabla158[[#This Row],[FTQ]]</f>
+        <v>1</v>
+      </c>
+      <c r="M29" s="4">
+        <v>46220</v>
+      </c>
+      <c r="N29" s="11">
+        <f>WEEKNUM(Tabla2610[[#This Row],[Fecha]])</f>
+        <v>29</v>
+      </c>
+      <c r="O29" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="P29" s="1">
+        <v>900</v>
+      </c>
+      <c r="Q29" s="9">
+        <v>12264732</v>
+      </c>
+      <c r="R29" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="S29" s="1">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="30" spans="2:19" x14ac:dyDescent="0.3">
+      <c r="B30" s="4">
+        <v>46220</v>
+      </c>
+      <c r="C30" s="11">
+        <f>WEEKNUM(Tabla158[[#This Row],[Fecha]])</f>
+        <v>29</v>
+      </c>
+      <c r="D30" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="E30" s="1">
+        <v>800</v>
+      </c>
+      <c r="F30" s="9">
+        <v>12264714</v>
+      </c>
+      <c r="G30" s="1">
+        <v>13</v>
+      </c>
+      <c r="H30" s="1">
+        <v>0</v>
+      </c>
+      <c r="I30" s="3">
+        <f>Tabla158[[#This Row],[Piezas NOK]]/Tabla158[[#This Row],[Piezas OK]]</f>
+        <v>0</v>
+      </c>
+      <c r="J30" s="11">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+      <c r="K30" s="5">
+        <f>Tabla158[[#This Row],[FTQ]]</f>
+        <v>1</v>
+      </c>
+      <c r="M30" s="4">
+        <v>46220</v>
+      </c>
+      <c r="N30" s="11">
+        <f>WEEKNUM(Tabla2610[[#This Row],[Fecha]])</f>
+        <v>29</v>
+      </c>
+      <c r="O30" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="P30" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q30" s="9">
+        <v>12264732</v>
+      </c>
+      <c r="R30" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="S30" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="31" spans="2:19" x14ac:dyDescent="0.3">
+      <c r="B31" s="4">
+        <v>46220</v>
+      </c>
+      <c r="C31" s="11">
+        <f>WEEKNUM(Tabla158[[#This Row],[Fecha]])</f>
+        <v>29</v>
+      </c>
+      <c r="D31" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="E31" s="1">
+        <v>900</v>
+      </c>
+      <c r="F31" s="9">
+        <v>12264714</v>
+      </c>
+      <c r="G31" s="1">
+        <v>4</v>
+      </c>
+      <c r="H31" s="1">
+        <v>0</v>
+      </c>
+      <c r="I31" s="3">
+        <f>Tabla158[[#This Row],[Piezas NOK]]/Tabla158[[#This Row],[Piezas OK]]</f>
+        <v>0</v>
+      </c>
+      <c r="J31" s="11">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+      <c r="K31" s="5">
+        <f>Tabla158[[#This Row],[FTQ]]</f>
+        <v>1</v>
+      </c>
       <c r="M31" s="4"/>
-    </row>
-    <row r="32" spans="2:13" x14ac:dyDescent="0.3">
-      <c r="B32" s="4"/>
-      <c r="I32" s="3"/>
-      <c r="J32" s="1"/>
-      <c r="K32" s="5"/>
+      <c r="N31" s="11"/>
+      <c r="Q31" s="9"/>
+    </row>
+    <row r="32" spans="2:19" x14ac:dyDescent="0.3">
+      <c r="B32" s="4">
+        <v>46220</v>
+      </c>
+      <c r="C32" s="11">
+        <f>WEEKNUM(Tabla158[[#This Row],[Fecha]])</f>
+        <v>29</v>
+      </c>
+      <c r="D32" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="E32" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="F32" s="9">
+        <v>12264714</v>
+      </c>
+      <c r="G32" s="1">
+        <v>3</v>
+      </c>
+      <c r="H32" s="1">
+        <v>0</v>
+      </c>
+      <c r="I32" s="3">
+        <f>Tabla158[[#This Row],[Piezas NOK]]/Tabla158[[#This Row],[Piezas OK]]</f>
+        <v>0</v>
+      </c>
+      <c r="J32" s="11">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+      <c r="K32" s="5">
+        <f>Tabla158[[#This Row],[FTQ]]</f>
+        <v>1</v>
+      </c>
       <c r="M32" s="4"/>
     </row>
     <row r="33" spans="2:13" x14ac:dyDescent="0.3">
-      <c r="B33" s="4"/>
-      <c r="I33" s="3"/>
-      <c r="J33" s="1"/>
-      <c r="K33" s="5"/>
+      <c r="B33" s="4">
+        <v>46220</v>
+      </c>
+      <c r="C33" s="11">
+        <f>WEEKNUM(Tabla158[[#This Row],[Fecha]])</f>
+        <v>29</v>
+      </c>
+      <c r="D33" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="E33" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F33" s="9">
+        <v>12264714</v>
+      </c>
+      <c r="G33" s="1">
+        <v>1</v>
+      </c>
+      <c r="H33" s="1">
+        <v>0</v>
+      </c>
+      <c r="I33" s="3">
+        <f>Tabla158[[#This Row],[Piezas NOK]]/Tabla158[[#This Row],[Piezas OK]]</f>
+        <v>0</v>
+      </c>
+      <c r="J33" s="11">
+        <f>ABS(G$3-I33)</f>
+        <v>1</v>
+      </c>
+      <c r="K33" s="5">
+        <f>Tabla158[[#This Row],[FTQ]]</f>
+        <v>1</v>
+      </c>
       <c r="M33" s="4"/>
     </row>
     <row r="34" spans="2:13" x14ac:dyDescent="0.3">
@@ -25357,6 +26345,7 @@
     </row>
     <row r="35" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B35" s="4"/>
+      <c r="H35" s="12"/>
       <c r="I35" s="3"/>
       <c r="J35" s="1"/>
       <c r="K35" s="5"/>

--- a/BASE DE DATOS.xlsx
+++ b/BASE DE DATOS.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\almag\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="J:\LAUNCH MANAGEMENT\1 KI\4_NX5a\09_Information\10_FTQ\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DD3F099B-30DF-44E5-A21F-CEDA2F809401}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2FD7427D-EDC1-493C-A618-5883F40F748A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{439F1396-05A1-464E-A03B-8C77E5396FAA}"/>
   </bookViews>
@@ -180,7 +180,7 @@
     <t>Mal embobinado en spiral Op.1100A</t>
   </si>
   <si>
-    <t>Falla sin especificación Op.1100A</t>
+    <t>0090.040 Op.1100A</t>
   </si>
 </sst>
 </file>
@@ -262,7 +262,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -291,19 +291,16 @@
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Porcentaje" xfId="1" builtinId="5"/>
+    <cellStyle name="Percent" xfId="1" builtinId="5"/>
   </cellStyles>
   <dxfs count="21">
     <dxf>
@@ -24591,7 +24588,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{05A1B645-8848-474A-88BA-FA9209B01B4F}">
   <dimension ref="A1:V831"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.5546875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="11.5546875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="3.77734375" customWidth="1"/>
     <col min="2" max="2" width="13.21875" style="1" customWidth="1"/>
@@ -24613,46 +24610,46 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:19" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B1" s="10" t="s">
+      <c r="B1" s="11" t="s">
         <v>14</v>
       </c>
-      <c r="C1" s="10"/>
-      <c r="D1" s="10"/>
-      <c r="E1" s="10"/>
-      <c r="F1" s="10"/>
-      <c r="G1" s="10"/>
-      <c r="H1" s="10"/>
-      <c r="I1" s="10"/>
-      <c r="J1" s="10"/>
+      <c r="C1" s="11"/>
+      <c r="D1" s="11"/>
+      <c r="E1" s="11"/>
+      <c r="F1" s="11"/>
+      <c r="G1" s="11"/>
+      <c r="H1" s="11"/>
+      <c r="I1" s="11"/>
+      <c r="J1" s="11"/>
       <c r="K1" s="6"/>
-      <c r="M1" s="10" t="s">
+      <c r="M1" s="11" t="s">
         <v>13</v>
       </c>
-      <c r="N1" s="10"/>
-      <c r="O1" s="10"/>
-      <c r="P1" s="10"/>
-      <c r="Q1" s="10"/>
-      <c r="R1" s="10"/>
-      <c r="S1" s="10"/>
+      <c r="N1" s="11"/>
+      <c r="O1" s="11"/>
+      <c r="P1" s="11"/>
+      <c r="Q1" s="11"/>
+      <c r="R1" s="11"/>
+      <c r="S1" s="11"/>
     </row>
     <row r="2" spans="2:19" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="10"/>
-      <c r="C2" s="10"/>
-      <c r="D2" s="10"/>
-      <c r="E2" s="10"/>
-      <c r="F2" s="10"/>
-      <c r="G2" s="10"/>
-      <c r="H2" s="10"/>
-      <c r="I2" s="10"/>
-      <c r="J2" s="10"/>
+      <c r="B2" s="11"/>
+      <c r="C2" s="11"/>
+      <c r="D2" s="11"/>
+      <c r="E2" s="11"/>
+      <c r="F2" s="11"/>
+      <c r="G2" s="11"/>
+      <c r="H2" s="11"/>
+      <c r="I2" s="11"/>
+      <c r="J2" s="11"/>
       <c r="K2" s="6"/>
-      <c r="M2" s="10"/>
-      <c r="N2" s="10"/>
-      <c r="O2" s="10"/>
-      <c r="P2" s="10"/>
-      <c r="Q2" s="10"/>
-      <c r="R2" s="10"/>
-      <c r="S2" s="10"/>
+      <c r="M2" s="11"/>
+      <c r="N2" s="11"/>
+      <c r="O2" s="11"/>
+      <c r="P2" s="11"/>
+      <c r="Q2" s="11"/>
+      <c r="R2" s="11"/>
+      <c r="S2" s="11"/>
     </row>
     <row r="3" spans="2:19" x14ac:dyDescent="0.3">
       <c r="G3" s="1">
@@ -25241,7 +25238,7 @@
       <c r="B14" s="4">
         <v>46220</v>
       </c>
-      <c r="C14" s="11">
+      <c r="C14" s="1">
         <f>WEEKNUM(Tabla158[[#This Row],[Fecha]])</f>
         <v>29</v>
       </c>
@@ -25264,7 +25261,7 @@
         <f>Tabla158[[#This Row],[Piezas NOK]]/Tabla158[[#This Row],[Piezas OK]]</f>
         <v>0</v>
       </c>
-      <c r="J14" s="11">
+      <c r="J14" s="1">
         <f t="shared" ref="J14:J22" si="1">ABS(G$3-I14)</f>
         <v>1</v>
       </c>
@@ -25299,7 +25296,7 @@
       <c r="B15" s="4">
         <v>46220</v>
       </c>
-      <c r="C15" s="11">
+      <c r="C15" s="1">
         <f>WEEKNUM(Tabla158[[#This Row],[Fecha]])</f>
         <v>29</v>
       </c>
@@ -25322,7 +25319,7 @@
         <f>Tabla158[[#This Row],[Piezas NOK]]/Tabla158[[#This Row],[Piezas OK]]</f>
         <v>4.9180327868852458E-2</v>
       </c>
-      <c r="J15" s="11">
+      <c r="J15" s="1">
         <f t="shared" si="1"/>
         <v>0.95081967213114749</v>
       </c>
@@ -25333,7 +25330,7 @@
       <c r="M15" s="4">
         <v>46220</v>
       </c>
-      <c r="N15" s="11">
+      <c r="N15" s="1">
         <f>WEEKNUM(Tabla2610[[#This Row],[Fecha]])</f>
         <v>29</v>
       </c>
@@ -25357,7 +25354,7 @@
       <c r="B16" s="4">
         <v>46220</v>
       </c>
-      <c r="C16" s="11">
+      <c r="C16" s="1">
         <f>WEEKNUM(Tabla158[[#This Row],[Fecha]])</f>
         <v>29</v>
       </c>
@@ -25380,7 +25377,7 @@
         <f>Tabla158[[#This Row],[Piezas NOK]]/Tabla158[[#This Row],[Piezas OK]]</f>
         <v>0.2857142857142857</v>
       </c>
-      <c r="J16" s="11">
+      <c r="J16" s="1">
         <f t="shared" si="1"/>
         <v>0.7142857142857143</v>
       </c>
@@ -25391,7 +25388,7 @@
       <c r="M16" s="4">
         <v>46220</v>
       </c>
-      <c r="N16" s="11">
+      <c r="N16" s="1">
         <f>WEEKNUM(Tabla2610[[#This Row],[Fecha]])</f>
         <v>29</v>
       </c>
@@ -25415,7 +25412,7 @@
       <c r="B17" s="4">
         <v>46220</v>
       </c>
-      <c r="C17" s="11">
+      <c r="C17" s="1">
         <f>WEEKNUM(Tabla158[[#This Row],[Fecha]])</f>
         <v>29</v>
       </c>
@@ -25438,7 +25435,7 @@
         <f>Tabla158[[#This Row],[Piezas NOK]]/Tabla158[[#This Row],[Piezas OK]]</f>
         <v>0.45454545454545453</v>
       </c>
-      <c r="J17" s="11">
+      <c r="J17" s="1">
         <f t="shared" si="1"/>
         <v>0.54545454545454541</v>
       </c>
@@ -25449,7 +25446,7 @@
       <c r="M17" s="4">
         <v>46220</v>
       </c>
-      <c r="N17" s="11">
+      <c r="N17" s="1">
         <f>WEEKNUM(Tabla2610[[#This Row],[Fecha]])</f>
         <v>29</v>
       </c>
@@ -25473,7 +25470,7 @@
       <c r="B18" s="4">
         <v>46220</v>
       </c>
-      <c r="C18" s="11">
+      <c r="C18" s="1">
         <f>WEEKNUM(Tabla158[[#This Row],[Fecha]])</f>
         <v>29</v>
       </c>
@@ -25496,7 +25493,7 @@
         <f>Tabla158[[#This Row],[Piezas NOK]]/Tabla158[[#This Row],[Piezas OK]]</f>
         <v>0.1038961038961039</v>
       </c>
-      <c r="J18" s="11">
+      <c r="J18" s="1">
         <f t="shared" si="1"/>
         <v>0.89610389610389607</v>
       </c>
@@ -25507,7 +25504,7 @@
       <c r="M18" s="4">
         <v>46220</v>
       </c>
-      <c r="N18" s="11">
+      <c r="N18" s="1">
         <f>WEEKNUM(Tabla2610[[#This Row],[Fecha]])</f>
         <v>29</v>
       </c>
@@ -25531,7 +25528,7 @@
       <c r="B19" s="4">
         <v>46220</v>
       </c>
-      <c r="C19" s="11">
+      <c r="C19" s="1">
         <f>WEEKNUM(Tabla158[[#This Row],[Fecha]])</f>
         <v>29</v>
       </c>
@@ -25554,7 +25551,7 @@
         <f>Tabla158[[#This Row],[Piezas NOK]]/Tabla158[[#This Row],[Piezas OK]]</f>
         <v>8.1967213114754092E-2</v>
       </c>
-      <c r="J19" s="11">
+      <c r="J19" s="1">
         <f t="shared" si="1"/>
         <v>0.91803278688524592</v>
       </c>
@@ -25565,7 +25562,7 @@
       <c r="M19" s="4">
         <v>46220</v>
       </c>
-      <c r="N19" s="11">
+      <c r="N19" s="1">
         <f>WEEKNUM(Tabla2610[[#This Row],[Fecha]])</f>
         <v>29</v>
       </c>
@@ -25589,7 +25586,7 @@
       <c r="B20" s="4">
         <v>46220</v>
       </c>
-      <c r="C20" s="11">
+      <c r="C20" s="1">
         <f>WEEKNUM(Tabla158[[#This Row],[Fecha]])</f>
         <v>29</v>
       </c>
@@ -25612,7 +25609,7 @@
         <f>Tabla158[[#This Row],[Piezas NOK]]/Tabla158[[#This Row],[Piezas OK]]</f>
         <v>5.4545454545454543E-2</v>
       </c>
-      <c r="J20" s="11">
+      <c r="J20" s="1">
         <f t="shared" si="1"/>
         <v>0.94545454545454544</v>
       </c>
@@ -25623,7 +25620,7 @@
       <c r="M20" s="4">
         <v>46220</v>
       </c>
-      <c r="N20" s="11">
+      <c r="N20" s="1">
         <f>WEEKNUM(Tabla2610[[#This Row],[Fecha]])</f>
         <v>29</v>
       </c>
@@ -25647,7 +25644,7 @@
       <c r="B21" s="4">
         <v>46220</v>
       </c>
-      <c r="C21" s="11">
+      <c r="C21" s="1">
         <f>WEEKNUM(Tabla158[[#This Row],[Fecha]])</f>
         <v>29</v>
       </c>
@@ -25670,7 +25667,7 @@
         <f>Tabla158[[#This Row],[Piezas NOK]]/Tabla158[[#This Row],[Piezas OK]]</f>
         <v>7.2727272727272724E-2</v>
       </c>
-      <c r="J21" s="11">
+      <c r="J21" s="1">
         <f t="shared" si="1"/>
         <v>0.92727272727272725</v>
       </c>
@@ -25681,7 +25678,7 @@
       <c r="M21" s="4">
         <v>46220</v>
       </c>
-      <c r="N21" s="11">
+      <c r="N21" s="1">
         <f>WEEKNUM(Tabla2610[[#This Row],[Fecha]])</f>
         <v>29</v>
       </c>
@@ -25705,7 +25702,7 @@
       <c r="B22" s="4">
         <v>46220</v>
       </c>
-      <c r="C22" s="11">
+      <c r="C22" s="1">
         <f>WEEKNUM(Tabla158[[#This Row],[Fecha]])</f>
         <v>29</v>
       </c>
@@ -25728,7 +25725,7 @@
         <f>Tabla158[[#This Row],[Piezas NOK]]/Tabla158[[#This Row],[Piezas OK]]</f>
         <v>2.7777777777777776E-2</v>
       </c>
-      <c r="J22" s="11">
+      <c r="J22" s="1">
         <f t="shared" si="1"/>
         <v>0.97222222222222221</v>
       </c>
@@ -25739,7 +25736,7 @@
       <c r="M22" s="4">
         <v>46220</v>
       </c>
-      <c r="N22" s="11">
+      <c r="N22" s="1">
         <f>WEEKNUM(Tabla2610[[#This Row],[Fecha]])</f>
         <v>29</v>
       </c>
@@ -25763,7 +25760,7 @@
       <c r="B23" s="4">
         <v>46220</v>
       </c>
-      <c r="C23" s="11">
+      <c r="C23" s="1">
         <f>WEEKNUM(Tabla158[[#This Row],[Fecha]])</f>
         <v>29</v>
       </c>
@@ -25786,7 +25783,7 @@
         <f>Tabla158[[#This Row],[Piezas NOK]]/Tabla158[[#This Row],[Piezas OK]]</f>
         <v>0</v>
       </c>
-      <c r="J23" s="11">
+      <c r="J23" s="1">
         <f>ABS(G$3-I23)</f>
         <v>1</v>
       </c>
@@ -25797,7 +25794,7 @@
       <c r="M23" s="4">
         <v>46220</v>
       </c>
-      <c r="N23" s="11">
+      <c r="N23" s="1">
         <f>WEEKNUM(Tabla2610[[#This Row],[Fecha]])</f>
         <v>29</v>
       </c>
@@ -25821,7 +25818,7 @@
       <c r="B24" s="4">
         <v>46220</v>
       </c>
-      <c r="C24" s="11">
+      <c r="C24" s="1">
         <f>WEEKNUM(Tabla158[[#This Row],[Fecha]])</f>
         <v>29</v>
       </c>
@@ -25844,7 +25841,7 @@
         <f>Tabla158[[#This Row],[Piezas NOK]]/Tabla158[[#This Row],[Piezas OK]]</f>
         <v>0</v>
       </c>
-      <c r="J24" s="11">
+      <c r="J24" s="1">
         <f t="shared" ref="J24:J32" si="2">ABS(G$3-I24)</f>
         <v>1</v>
       </c>
@@ -25855,7 +25852,7 @@
       <c r="M24" s="4">
         <v>46220</v>
       </c>
-      <c r="N24" s="11">
+      <c r="N24" s="1">
         <f>WEEKNUM(Tabla2610[[#This Row],[Fecha]])</f>
         <v>29</v>
       </c>
@@ -25879,7 +25876,7 @@
       <c r="B25" s="4">
         <v>46220</v>
       </c>
-      <c r="C25" s="11">
+      <c r="C25" s="1">
         <f>WEEKNUM(Tabla158[[#This Row],[Fecha]])</f>
         <v>29</v>
       </c>
@@ -25902,7 +25899,7 @@
         <f>Tabla158[[#This Row],[Piezas NOK]]/Tabla158[[#This Row],[Piezas OK]]</f>
         <v>0</v>
       </c>
-      <c r="J25" s="11">
+      <c r="J25" s="1">
         <f t="shared" si="2"/>
         <v>1</v>
       </c>
@@ -25913,7 +25910,7 @@
       <c r="M25" s="4">
         <v>46220</v>
       </c>
-      <c r="N25" s="11">
+      <c r="N25" s="1">
         <f>WEEKNUM(Tabla2610[[#This Row],[Fecha]])</f>
         <v>29</v>
       </c>
@@ -25937,7 +25934,7 @@
       <c r="B26" s="4">
         <v>46220</v>
       </c>
-      <c r="C26" s="11">
+      <c r="C26" s="1">
         <f>WEEKNUM(Tabla158[[#This Row],[Fecha]])</f>
         <v>29</v>
       </c>
@@ -25960,7 +25957,7 @@
         <f>Tabla158[[#This Row],[Piezas NOK]]/Tabla158[[#This Row],[Piezas OK]]</f>
         <v>0</v>
       </c>
-      <c r="J26" s="11">
+      <c r="J26" s="1">
         <f t="shared" si="2"/>
         <v>1</v>
       </c>
@@ -25971,7 +25968,7 @@
       <c r="M26" s="4">
         <v>46220</v>
       </c>
-      <c r="N26" s="11">
+      <c r="N26" s="1">
         <f>WEEKNUM(Tabla2610[[#This Row],[Fecha]])</f>
         <v>29</v>
       </c>
@@ -25995,7 +25992,7 @@
       <c r="B27" s="4">
         <v>46220</v>
       </c>
-      <c r="C27" s="11">
+      <c r="C27" s="1">
         <f>WEEKNUM(Tabla158[[#This Row],[Fecha]])</f>
         <v>29</v>
       </c>
@@ -26018,7 +26015,7 @@
         <f>Tabla158[[#This Row],[Piezas NOK]]/Tabla158[[#This Row],[Piezas OK]]</f>
         <v>0</v>
       </c>
-      <c r="J27" s="11">
+      <c r="J27" s="1">
         <f t="shared" si="2"/>
         <v>1</v>
       </c>
@@ -26029,7 +26026,7 @@
       <c r="M27" s="4">
         <v>46220</v>
       </c>
-      <c r="N27" s="11">
+      <c r="N27" s="1">
         <f>WEEKNUM(Tabla2610[[#This Row],[Fecha]])</f>
         <v>29</v>
       </c>
@@ -26053,7 +26050,7 @@
       <c r="B28" s="4">
         <v>46220</v>
       </c>
-      <c r="C28" s="11">
+      <c r="C28" s="1">
         <f>WEEKNUM(Tabla158[[#This Row],[Fecha]])</f>
         <v>29</v>
       </c>
@@ -26076,7 +26073,7 @@
         <f>Tabla158[[#This Row],[Piezas NOK]]/Tabla158[[#This Row],[Piezas OK]]</f>
         <v>6.6666666666666666E-2</v>
       </c>
-      <c r="J28" s="11">
+      <c r="J28" s="1">
         <f t="shared" si="2"/>
         <v>0.93333333333333335</v>
       </c>
@@ -26087,7 +26084,7 @@
       <c r="M28" s="4">
         <v>46220</v>
       </c>
-      <c r="N28" s="11">
+      <c r="N28" s="1">
         <f>WEEKNUM(Tabla2610[[#This Row],[Fecha]])</f>
         <v>29</v>
       </c>
@@ -26111,7 +26108,7 @@
       <c r="B29" s="4">
         <v>46220</v>
       </c>
-      <c r="C29" s="11">
+      <c r="C29" s="1">
         <f>WEEKNUM(Tabla158[[#This Row],[Fecha]])</f>
         <v>29</v>
       </c>
@@ -26134,7 +26131,7 @@
         <f>Tabla158[[#This Row],[Piezas NOK]]/Tabla158[[#This Row],[Piezas OK]]</f>
         <v>0</v>
       </c>
-      <c r="J29" s="11">
+      <c r="J29" s="1">
         <f t="shared" si="2"/>
         <v>1</v>
       </c>
@@ -26145,7 +26142,7 @@
       <c r="M29" s="4">
         <v>46220</v>
       </c>
-      <c r="N29" s="11">
+      <c r="N29" s="1">
         <f>WEEKNUM(Tabla2610[[#This Row],[Fecha]])</f>
         <v>29</v>
       </c>
@@ -26169,7 +26166,7 @@
       <c r="B30" s="4">
         <v>46220</v>
       </c>
-      <c r="C30" s="11">
+      <c r="C30" s="1">
         <f>WEEKNUM(Tabla158[[#This Row],[Fecha]])</f>
         <v>29</v>
       </c>
@@ -26192,7 +26189,7 @@
         <f>Tabla158[[#This Row],[Piezas NOK]]/Tabla158[[#This Row],[Piezas OK]]</f>
         <v>0</v>
       </c>
-      <c r="J30" s="11">
+      <c r="J30" s="1">
         <f t="shared" si="2"/>
         <v>1</v>
       </c>
@@ -26203,7 +26200,7 @@
       <c r="M30" s="4">
         <v>46220</v>
       </c>
-      <c r="N30" s="11">
+      <c r="N30" s="1">
         <f>WEEKNUM(Tabla2610[[#This Row],[Fecha]])</f>
         <v>29</v>
       </c>
@@ -26227,7 +26224,7 @@
       <c r="B31" s="4">
         <v>46220</v>
       </c>
-      <c r="C31" s="11">
+      <c r="C31" s="1">
         <f>WEEKNUM(Tabla158[[#This Row],[Fecha]])</f>
         <v>29</v>
       </c>
@@ -26250,7 +26247,7 @@
         <f>Tabla158[[#This Row],[Piezas NOK]]/Tabla158[[#This Row],[Piezas OK]]</f>
         <v>0</v>
       </c>
-      <c r="J31" s="11">
+      <c r="J31" s="1">
         <f t="shared" si="2"/>
         <v>1</v>
       </c>
@@ -26259,14 +26256,13 @@
         <v>1</v>
       </c>
       <c r="M31" s="4"/>
-      <c r="N31" s="11"/>
       <c r="Q31" s="9"/>
     </row>
     <row r="32" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B32" s="4">
         <v>46220</v>
       </c>
-      <c r="C32" s="11">
+      <c r="C32" s="1">
         <f>WEEKNUM(Tabla158[[#This Row],[Fecha]])</f>
         <v>29</v>
       </c>
@@ -26289,7 +26285,7 @@
         <f>Tabla158[[#This Row],[Piezas NOK]]/Tabla158[[#This Row],[Piezas OK]]</f>
         <v>0</v>
       </c>
-      <c r="J32" s="11">
+      <c r="J32" s="1">
         <f t="shared" si="2"/>
         <v>1</v>
       </c>
@@ -26303,7 +26299,7 @@
       <c r="B33" s="4">
         <v>46220</v>
       </c>
-      <c r="C33" s="11">
+      <c r="C33" s="1">
         <f>WEEKNUM(Tabla158[[#This Row],[Fecha]])</f>
         <v>29</v>
       </c>
@@ -26326,7 +26322,7 @@
         <f>Tabla158[[#This Row],[Piezas NOK]]/Tabla158[[#This Row],[Piezas OK]]</f>
         <v>0</v>
       </c>
-      <c r="J33" s="11">
+      <c r="J33" s="1">
         <f>ABS(G$3-I33)</f>
         <v>1</v>
       </c>
@@ -26345,7 +26341,7 @@
     </row>
     <row r="35" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B35" s="4"/>
-      <c r="H35" s="12"/>
+      <c r="H35" s="10"/>
       <c r="I35" s="3"/>
       <c r="J35" s="1"/>
       <c r="K35" s="5"/>

--- a/BASE DE DATOS.xlsx
+++ b/BASE DE DATOS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="J:\LAUNCH MANAGEMENT\1 KI\4_NX5a\09_Information\10_FTQ\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2FD7427D-EDC1-493C-A618-5883F40F748A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B81C1498-AB3E-42BA-9099-F89FB4C26158}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{439F1396-05A1-464E-A03B-8C77E5396FAA}"/>
   </bookViews>
@@ -21,7 +21,7 @@
     <externalReference r:id="rId4"/>
   </externalReferences>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'BASE DE DATOS RIVIAN'!$B$4:$J$33</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'BASE DE DATOS RIVIAN'!$B$4:$J$62</definedName>
     <definedName name="DATA_01">[1]Data_Lineal!$H$4:$Y$30</definedName>
     <definedName name="DB_01">#REF!</definedName>
     <definedName name="DB_CAP01">'[2]CAPACIDAD (1)'!$X$9:$AM$29</definedName>
@@ -64,7 +64,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="119" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="220" uniqueCount="51">
   <si>
     <t>*</t>
   </si>
@@ -156,19 +156,7 @@
     <t>Falla de inspección visual Op.400</t>
   </si>
   <si>
-    <t>Falla de sensor Op.400</t>
-  </si>
-  <si>
     <t>Falla en lectura de Scanner Op.400</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SFC 965827AGG00003 is not in queue at operation </t>
-  </si>
-  <si>
-    <t>Material Towerdid</t>
-  </si>
-  <si>
-    <t>Falla de isnpección visual en spiral Op.700</t>
   </si>
   <si>
     <t>Falla en atornillado Op.700</t>
@@ -180,7 +168,55 @@
     <t>Mal embobinado en spiral Op.1100A</t>
   </si>
   <si>
-    <t>0090.040 Op.1100A</t>
+    <t>Falla de sensor de slai Op.400</t>
+  </si>
+  <si>
+    <t>Falla de sensor S$9 Op.400</t>
+  </si>
+  <si>
+    <t>Material Towerdid Op.400</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SFC 965827AGG00003 is not in queue at operation Op.400 </t>
+  </si>
+  <si>
+    <t>Sin especificar Op. 600</t>
+  </si>
+  <si>
+    <t>Sin especificar ok Op. 600</t>
+  </si>
+  <si>
+    <t>Falso Rechazo (version de SCR) Op.700</t>
+  </si>
+  <si>
+    <t>Falta de grasa en PCB Op.400</t>
+  </si>
+  <si>
+    <t>Detecta piezas de sobre-producción Op.400</t>
+  </si>
+  <si>
+    <t>Mezcla de material con index incorrecto Op.700</t>
+  </si>
+  <si>
+    <t>Falla 0090.040 Op.1100A</t>
+  </si>
+  <si>
+    <t>Falla  0040.074 Op.1100A</t>
+  </si>
+  <si>
+    <t>Falla 0400.020 Op.1100A</t>
+  </si>
+  <si>
+    <t>Falla 0400.030 Op.1100A</t>
+  </si>
+  <si>
+    <t>Falla 0060.005 Op.1100A</t>
+  </si>
+  <si>
+    <t>Falla 0090.004 Op.1100B</t>
+  </si>
+  <si>
+    <t>Detecta pieza sin pasar en operación anterior Op.700</t>
   </si>
 </sst>
 </file>
@@ -262,7 +298,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -296,6 +332,9 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -24282,7 +24321,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{421FD8D0-4DB9-4A88-8653-0AE7AE89107A}" name="Tabla158" displayName="Tabla158" ref="B4:K33" totalsRowShown="0" headerRowDxfId="20" dataDxfId="19">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{421FD8D0-4DB9-4A88-8653-0AE7AE89107A}" name="Tabla158" displayName="Tabla158" ref="B4:K62" totalsRowShown="0" headerRowDxfId="20" dataDxfId="19">
   <tableColumns count="10">
     <tableColumn id="1" xr3:uid="{CDAA4D20-2955-41E2-BD7E-9330E166FFF4}" name="Fecha" dataDxfId="18"/>
     <tableColumn id="9" xr3:uid="{F70BB124-92DE-4024-874C-EE3BA966CDE6}" name="Semana" dataDxfId="17">
@@ -24308,7 +24347,7 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{83880157-341F-4984-9DA8-9308A0C526D5}" name="Tabla2610" displayName="Tabla2610" ref="M4:S30" totalsRowShown="0" headerRowDxfId="8" dataDxfId="7">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{83880157-341F-4984-9DA8-9308A0C526D5}" name="Tabla2610" displayName="Tabla2610" ref="M4:S61" totalsRowShown="0" headerRowDxfId="8" dataDxfId="7">
   <tableColumns count="7">
     <tableColumn id="1" xr3:uid="{D688BA2E-A64E-4433-85E0-7EDBF854AF60}" name="Fecha" dataDxfId="6"/>
     <tableColumn id="7" xr3:uid="{D3EA5E8D-DD68-48AC-8DAC-4A4077839479}" name="Semana" dataDxfId="5">
@@ -24587,7 +24626,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{05A1B645-8848-474A-88BA-FA9209B01B4F}">
-  <dimension ref="A1:V831"/>
+  <dimension ref="A1:V830"/>
   <sheetFormatPr defaultColWidth="11.5546875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="3.77734375" customWidth="1"/>
@@ -24605,7 +24644,7 @@
     <col min="15" max="15" width="12.44140625" style="1" customWidth="1"/>
     <col min="16" max="16" width="13.21875" style="1" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="11.77734375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="47.5546875" style="1" customWidth="1"/>
+    <col min="18" max="18" width="50.44140625" style="1" customWidth="1"/>
     <col min="19" max="19" width="13" style="1" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -25228,7 +25267,7 @@
         <v>12264732</v>
       </c>
       <c r="R13" s="1" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="S13" s="1">
         <v>1</v>
@@ -25338,7 +25377,7 @@
         <v>18</v>
       </c>
       <c r="P15" s="1">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="Q15" s="9">
         <v>12264732</v>
@@ -25634,7 +25673,7 @@
         <v>12264732</v>
       </c>
       <c r="R20" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="S20" s="1">
         <v>3</v>
@@ -25692,7 +25731,7 @@
         <v>12264732</v>
       </c>
       <c r="R21" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="S21" s="1">
         <v>21</v>
@@ -25750,7 +25789,7 @@
         <v>12264732</v>
       </c>
       <c r="R22" s="1" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="S22" s="1">
         <v>3</v>
@@ -25808,7 +25847,7 @@
         <v>12264732</v>
       </c>
       <c r="R23" s="1" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="S23" s="1">
         <v>5</v>
@@ -25982,7 +26021,7 @@
         <v>12264732</v>
       </c>
       <c r="R26" s="1" t="s">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="S26" s="1">
         <v>4</v>
@@ -26040,7 +26079,7 @@
         <v>12264732</v>
       </c>
       <c r="R27" s="1" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="S27" s="1">
         <v>1</v>
@@ -26156,7 +26195,7 @@
         <v>12264732</v>
       </c>
       <c r="R29" s="1" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="S29" s="1">
         <v>4</v>
@@ -26214,7 +26253,7 @@
         <v>12264732</v>
       </c>
       <c r="R30" s="1" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="S30" s="1">
         <v>1</v>
@@ -26255,8 +26294,28 @@
         <f>Tabla158[[#This Row],[FTQ]]</f>
         <v>1</v>
       </c>
-      <c r="M31" s="4"/>
-      <c r="Q31" s="9"/>
+      <c r="M31" s="4">
+        <v>46223</v>
+      </c>
+      <c r="N31" s="12">
+        <f>WEEKNUM(Tabla2610[[#This Row],[Fecha]])</f>
+        <v>30</v>
+      </c>
+      <c r="O31" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="P31" s="1">
+        <v>200</v>
+      </c>
+      <c r="Q31" s="9">
+        <v>12264714</v>
+      </c>
+      <c r="R31" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="S31" s="1">
+        <v>1</v>
+      </c>
     </row>
     <row r="32" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B32" s="4">
@@ -26293,9 +26352,30 @@
         <f>Tabla158[[#This Row],[FTQ]]</f>
         <v>1</v>
       </c>
-      <c r="M32" s="4"/>
-    </row>
-    <row r="33" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="M32" s="4">
+        <v>46223</v>
+      </c>
+      <c r="N32" s="12">
+        <f>WEEKNUM(Tabla2610[[#This Row],[Fecha]])</f>
+        <v>30</v>
+      </c>
+      <c r="O32" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="P32" s="1">
+        <v>300</v>
+      </c>
+      <c r="Q32" s="9">
+        <v>12264714</v>
+      </c>
+      <c r="R32" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="S32" s="1">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="33" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B33" s="4">
         <v>46220</v>
       </c>
@@ -26330,220 +26410,1698 @@
         <f>Tabla158[[#This Row],[FTQ]]</f>
         <v>1</v>
       </c>
-      <c r="M33" s="4"/>
-    </row>
-    <row r="34" spans="2:13" x14ac:dyDescent="0.3">
-      <c r="B34" s="4"/>
-      <c r="I34" s="3"/>
-      <c r="J34" s="1"/>
-      <c r="K34" s="5"/>
-      <c r="M34" s="4"/>
-    </row>
-    <row r="35" spans="2:13" x14ac:dyDescent="0.3">
-      <c r="B35" s="4"/>
-      <c r="H35" s="10"/>
-      <c r="I35" s="3"/>
-      <c r="J35" s="1"/>
-      <c r="K35" s="5"/>
-      <c r="M35" s="4"/>
-    </row>
-    <row r="36" spans="2:13" x14ac:dyDescent="0.3">
-      <c r="B36" s="4"/>
-      <c r="I36" s="3"/>
-      <c r="J36" s="1"/>
-      <c r="K36" s="5"/>
-      <c r="M36" s="4"/>
-    </row>
-    <row r="37" spans="2:13" x14ac:dyDescent="0.3">
-      <c r="B37" s="4"/>
-      <c r="I37" s="3"/>
-      <c r="J37" s="1"/>
-      <c r="K37" s="5"/>
-      <c r="M37" s="4"/>
-    </row>
-    <row r="38" spans="2:13" x14ac:dyDescent="0.3">
-      <c r="B38" s="4"/>
-      <c r="I38" s="3"/>
-      <c r="J38" s="1"/>
-      <c r="K38" s="5"/>
-      <c r="M38" s="4"/>
-    </row>
-    <row r="39" spans="2:13" x14ac:dyDescent="0.3">
-      <c r="B39" s="4"/>
-      <c r="I39" s="3"/>
-      <c r="J39" s="1"/>
-      <c r="K39" s="5"/>
-      <c r="M39" s="4"/>
-    </row>
-    <row r="40" spans="2:13" x14ac:dyDescent="0.3">
-      <c r="B40" s="4"/>
-      <c r="I40" s="3"/>
-      <c r="J40" s="1"/>
-      <c r="K40" s="5"/>
-      <c r="M40" s="4"/>
-    </row>
-    <row r="41" spans="2:13" x14ac:dyDescent="0.3">
-      <c r="B41" s="4"/>
-      <c r="I41" s="3"/>
-      <c r="J41" s="1"/>
-      <c r="K41" s="5"/>
-      <c r="M41" s="4"/>
-    </row>
-    <row r="42" spans="2:13" x14ac:dyDescent="0.3">
-      <c r="B42" s="4"/>
-      <c r="I42" s="3"/>
-      <c r="J42" s="1"/>
-      <c r="K42" s="5"/>
-      <c r="M42" s="4"/>
-    </row>
-    <row r="43" spans="2:13" x14ac:dyDescent="0.3">
-      <c r="B43" s="4"/>
-      <c r="I43" s="3"/>
-      <c r="J43" s="1"/>
-      <c r="K43" s="5"/>
-      <c r="M43" s="4"/>
-    </row>
-    <row r="44" spans="2:13" x14ac:dyDescent="0.3">
-      <c r="B44" s="4"/>
-      <c r="I44" s="3"/>
-      <c r="J44" s="1"/>
-      <c r="K44" s="5"/>
-      <c r="M44" s="4"/>
-    </row>
-    <row r="45" spans="2:13" x14ac:dyDescent="0.3">
-      <c r="B45" s="4"/>
-      <c r="I45" s="3"/>
-      <c r="J45" s="1"/>
-      <c r="K45" s="5"/>
-      <c r="M45" s="4"/>
-    </row>
-    <row r="46" spans="2:13" x14ac:dyDescent="0.3">
-      <c r="B46" s="4"/>
-      <c r="I46" s="3"/>
-      <c r="J46" s="1"/>
-      <c r="K46" s="5"/>
-      <c r="M46" s="4"/>
-    </row>
-    <row r="47" spans="2:13" x14ac:dyDescent="0.3">
-      <c r="B47" s="4"/>
-      <c r="I47" s="3"/>
-      <c r="J47" s="1"/>
-      <c r="K47" s="5"/>
-      <c r="M47" s="4"/>
-    </row>
-    <row r="48" spans="2:13" x14ac:dyDescent="0.3">
-      <c r="B48" s="4"/>
-      <c r="I48" s="3"/>
-      <c r="J48" s="1"/>
-      <c r="K48" s="5"/>
-      <c r="M48" s="4"/>
-    </row>
-    <row r="49" spans="2:13" x14ac:dyDescent="0.3">
-      <c r="B49" s="4"/>
-      <c r="I49" s="3"/>
-      <c r="J49" s="1"/>
-      <c r="K49" s="5"/>
-      <c r="M49" s="4"/>
-    </row>
-    <row r="50" spans="2:13" x14ac:dyDescent="0.3">
-      <c r="B50" s="4"/>
-      <c r="I50" s="3"/>
-      <c r="J50" s="1"/>
-      <c r="K50" s="5"/>
-      <c r="M50" s="4"/>
-    </row>
-    <row r="51" spans="2:13" x14ac:dyDescent="0.3">
-      <c r="B51" s="4"/>
-      <c r="I51" s="3"/>
-      <c r="J51" s="1"/>
-      <c r="K51" s="5"/>
-      <c r="M51" s="4"/>
-    </row>
-    <row r="52" spans="2:13" x14ac:dyDescent="0.3">
-      <c r="B52" s="4"/>
-      <c r="I52" s="3"/>
-      <c r="J52" s="1"/>
-      <c r="K52" s="5"/>
-      <c r="M52" s="4"/>
-    </row>
-    <row r="53" spans="2:13" x14ac:dyDescent="0.3">
-      <c r="B53" s="4"/>
-      <c r="I53" s="3"/>
-      <c r="J53" s="1"/>
-      <c r="K53" s="5"/>
-      <c r="M53" s="4"/>
-    </row>
-    <row r="54" spans="2:13" x14ac:dyDescent="0.3">
-      <c r="B54" s="4"/>
-      <c r="I54" s="3"/>
-      <c r="J54" s="1"/>
-      <c r="K54" s="5"/>
-      <c r="M54" s="4"/>
-    </row>
-    <row r="55" spans="2:13" x14ac:dyDescent="0.3">
-      <c r="B55" s="4"/>
-      <c r="I55" s="3"/>
-      <c r="J55" s="1"/>
-      <c r="K55" s="5"/>
-      <c r="M55" s="4"/>
-    </row>
-    <row r="56" spans="2:13" x14ac:dyDescent="0.3">
-      <c r="B56" s="4"/>
-      <c r="I56" s="3"/>
-      <c r="J56" s="1"/>
-      <c r="K56" s="5"/>
-      <c r="M56" s="4"/>
-    </row>
-    <row r="57" spans="2:13" x14ac:dyDescent="0.3">
-      <c r="B57" s="4"/>
-      <c r="I57" s="3"/>
-      <c r="J57" s="1"/>
-      <c r="K57" s="5"/>
-      <c r="M57" s="4"/>
-    </row>
-    <row r="58" spans="2:13" x14ac:dyDescent="0.3">
-      <c r="B58" s="4"/>
-      <c r="I58" s="3"/>
-      <c r="J58" s="1"/>
-      <c r="K58" s="5"/>
-      <c r="M58" s="4"/>
-    </row>
-    <row r="59" spans="2:13" x14ac:dyDescent="0.3">
-      <c r="B59" s="4"/>
-      <c r="I59" s="3"/>
-      <c r="J59" s="1"/>
-      <c r="K59" s="5"/>
-      <c r="M59" s="4"/>
-    </row>
-    <row r="60" spans="2:13" x14ac:dyDescent="0.3">
-      <c r="B60" s="4"/>
-      <c r="I60" s="3"/>
-      <c r="J60" s="1"/>
-      <c r="K60" s="5"/>
-      <c r="M60" s="4"/>
-    </row>
-    <row r="61" spans="2:13" x14ac:dyDescent="0.3">
-      <c r="B61" s="4"/>
-      <c r="I61" s="3"/>
-      <c r="J61" s="1"/>
-      <c r="K61" s="5"/>
-      <c r="M61" s="4"/>
-    </row>
-    <row r="62" spans="2:13" x14ac:dyDescent="0.3">
-      <c r="B62" s="4"/>
-      <c r="I62" s="3"/>
-      <c r="J62" s="1"/>
-      <c r="K62" s="5"/>
+      <c r="M33" s="4">
+        <v>46223</v>
+      </c>
+      <c r="N33" s="12">
+        <f>WEEKNUM(Tabla2610[[#This Row],[Fecha]])</f>
+        <v>30</v>
+      </c>
+      <c r="O33" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="P33" s="1">
+        <v>400</v>
+      </c>
+      <c r="Q33" s="9">
+        <v>12264714</v>
+      </c>
+      <c r="R33" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="S33" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="34" spans="2:19" x14ac:dyDescent="0.3">
+      <c r="B34" s="4">
+        <v>46223</v>
+      </c>
+      <c r="C34" s="1">
+        <f>WEEKNUM(Tabla158[[#This Row],[Fecha]])</f>
+        <v>30</v>
+      </c>
+      <c r="D34" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="E34" s="1">
+        <v>100</v>
+      </c>
+      <c r="F34" s="9">
+        <v>12264714</v>
+      </c>
+      <c r="G34" s="1">
+        <v>78</v>
+      </c>
+      <c r="H34" s="1">
+        <v>0</v>
+      </c>
+      <c r="I34" s="3">
+        <f>Tabla158[[#This Row],[Piezas NOK]]/Tabla158[[#This Row],[Piezas OK]]</f>
+        <v>0</v>
+      </c>
+      <c r="J34" s="1">
+        <f t="shared" ref="J34:J44" si="3">ABS(G$3-I34)</f>
+        <v>1</v>
+      </c>
+      <c r="K34" s="5">
+        <f>Tabla158[[#This Row],[FTQ]]</f>
+        <v>1</v>
+      </c>
+      <c r="M34" s="4">
+        <v>46223</v>
+      </c>
+      <c r="N34" s="12">
+        <f>WEEKNUM(Tabla2610[[#This Row],[Fecha]])</f>
+        <v>30</v>
+      </c>
+      <c r="O34" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="P34" s="1">
+        <v>400</v>
+      </c>
+      <c r="Q34" s="9">
+        <v>12264714</v>
+      </c>
+      <c r="R34" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="S34" s="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="35" spans="2:19" x14ac:dyDescent="0.3">
+      <c r="B35" s="4">
+        <v>46223</v>
+      </c>
+      <c r="C35" s="1">
+        <f>WEEKNUM(Tabla158[[#This Row],[Fecha]])</f>
+        <v>30</v>
+      </c>
+      <c r="D35" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="E35" s="1">
+        <v>200</v>
+      </c>
+      <c r="F35" s="9">
+        <v>12264714</v>
+      </c>
+      <c r="G35" s="1">
+        <v>69</v>
+      </c>
+      <c r="H35" s="10">
+        <v>1</v>
+      </c>
+      <c r="I35" s="3">
+        <f>Tabla158[[#This Row],[Piezas NOK]]/Tabla158[[#This Row],[Piezas OK]]</f>
+        <v>1.4492753623188406E-2</v>
+      </c>
+      <c r="J35" s="1">
+        <f t="shared" si="3"/>
+        <v>0.98550724637681164</v>
+      </c>
+      <c r="K35" s="5">
+        <f>Tabla158[[#This Row],[FTQ]]</f>
+        <v>0.98550724637681164</v>
+      </c>
+      <c r="M35" s="4">
+        <v>46223</v>
+      </c>
+      <c r="N35" s="12">
+        <f>WEEKNUM(Tabla2610[[#This Row],[Fecha]])</f>
+        <v>30</v>
+      </c>
+      <c r="O35" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="P35" s="1">
+        <v>400</v>
+      </c>
+      <c r="Q35" s="9">
+        <v>12264714</v>
+      </c>
+      <c r="R35" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="S35" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="36" spans="2:19" x14ac:dyDescent="0.3">
+      <c r="B36" s="4">
+        <v>46223</v>
+      </c>
+      <c r="C36" s="1">
+        <f>WEEKNUM(Tabla158[[#This Row],[Fecha]])</f>
+        <v>30</v>
+      </c>
+      <c r="D36" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="E36" s="1">
+        <v>300</v>
+      </c>
+      <c r="F36" s="9">
+        <v>12264714</v>
+      </c>
+      <c r="G36" s="1">
+        <v>66</v>
+      </c>
+      <c r="H36" s="1">
+        <v>4</v>
+      </c>
+      <c r="I36" s="3">
+        <f>Tabla158[[#This Row],[Piezas NOK]]/Tabla158[[#This Row],[Piezas OK]]</f>
+        <v>6.0606060606060608E-2</v>
+      </c>
+      <c r="J36" s="1">
+        <f t="shared" si="3"/>
+        <v>0.93939393939393945</v>
+      </c>
+      <c r="K36" s="5">
+        <f>Tabla158[[#This Row],[FTQ]]</f>
+        <v>0.93939393939393945</v>
+      </c>
+      <c r="M36" s="4">
+        <v>46223</v>
+      </c>
+      <c r="N36" s="12">
+        <f>WEEKNUM(Tabla2610[[#This Row],[Fecha]])</f>
+        <v>30</v>
+      </c>
+      <c r="O36" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="P36" s="1">
+        <v>400</v>
+      </c>
+      <c r="Q36" s="9">
+        <v>12264714</v>
+      </c>
+      <c r="R36" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="S36" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="37" spans="2:19" x14ac:dyDescent="0.3">
+      <c r="B37" s="4">
+        <v>46223</v>
+      </c>
+      <c r="C37" s="1">
+        <f>WEEKNUM(Tabla158[[#This Row],[Fecha]])</f>
+        <v>30</v>
+      </c>
+      <c r="D37" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="E37" s="1">
+        <v>400</v>
+      </c>
+      <c r="F37" s="9">
+        <v>12264714</v>
+      </c>
+      <c r="G37" s="1">
+        <v>50</v>
+      </c>
+      <c r="H37" s="1">
+        <v>24</v>
+      </c>
+      <c r="I37" s="3">
+        <f>Tabla158[[#This Row],[Piezas NOK]]/Tabla158[[#This Row],[Piezas OK]]</f>
+        <v>0.48</v>
+      </c>
+      <c r="J37" s="1">
+        <f t="shared" si="3"/>
+        <v>0.52</v>
+      </c>
+      <c r="K37" s="5">
+        <f>Tabla158[[#This Row],[FTQ]]</f>
+        <v>0.52</v>
+      </c>
+      <c r="M37" s="4">
+        <v>46223</v>
+      </c>
+      <c r="N37" s="12">
+        <f>WEEKNUM(Tabla2610[[#This Row],[Fecha]])</f>
+        <v>30</v>
+      </c>
+      <c r="O37" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="P37" s="1">
+        <v>400</v>
+      </c>
+      <c r="Q37" s="9">
+        <v>12264714</v>
+      </c>
+      <c r="R37" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="S37" s="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="38" spans="2:19" x14ac:dyDescent="0.3">
+      <c r="B38" s="4">
+        <v>46223</v>
+      </c>
+      <c r="C38" s="1">
+        <f>WEEKNUM(Tabla158[[#This Row],[Fecha]])</f>
+        <v>30</v>
+      </c>
+      <c r="D38" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="E38" s="1">
+        <v>600</v>
+      </c>
+      <c r="F38" s="9">
+        <v>12264714</v>
+      </c>
+      <c r="G38" s="1">
+        <v>35</v>
+      </c>
+      <c r="H38" s="1">
+        <v>4</v>
+      </c>
+      <c r="I38" s="3">
+        <f>Tabla158[[#This Row],[Piezas NOK]]/Tabla158[[#This Row],[Piezas OK]]</f>
+        <v>0.11428571428571428</v>
+      </c>
+      <c r="J38" s="1">
+        <f t="shared" si="3"/>
+        <v>0.88571428571428568</v>
+      </c>
+      <c r="K38" s="5">
+        <f>Tabla158[[#This Row],[FTQ]]</f>
+        <v>0.88571428571428568</v>
+      </c>
+      <c r="M38" s="4">
+        <v>46223</v>
+      </c>
+      <c r="N38" s="12">
+        <f>WEEKNUM(Tabla2610[[#This Row],[Fecha]])</f>
+        <v>30</v>
+      </c>
+      <c r="O38" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="P38" s="1">
+        <v>400</v>
+      </c>
+      <c r="Q38" s="9">
+        <v>12264714</v>
+      </c>
+      <c r="R38" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="S38" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="39" spans="2:19" x14ac:dyDescent="0.3">
+      <c r="B39" s="4">
+        <v>46223</v>
+      </c>
+      <c r="C39" s="1">
+        <f>WEEKNUM(Tabla158[[#This Row],[Fecha]])</f>
+        <v>30</v>
+      </c>
+      <c r="D39" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="E39" s="1">
+        <v>700</v>
+      </c>
+      <c r="F39" s="9">
+        <v>12264714</v>
+      </c>
+      <c r="G39" s="1">
+        <v>35</v>
+      </c>
+      <c r="H39" s="1">
+        <v>9</v>
+      </c>
+      <c r="I39" s="3">
+        <f>Tabla158[[#This Row],[Piezas NOK]]/Tabla158[[#This Row],[Piezas OK]]</f>
+        <v>0.25714285714285712</v>
+      </c>
+      <c r="J39" s="1">
+        <f t="shared" si="3"/>
+        <v>0.74285714285714288</v>
+      </c>
+      <c r="K39" s="5">
+        <f>Tabla158[[#This Row],[FTQ]]</f>
+        <v>0.74285714285714288</v>
+      </c>
+      <c r="M39" s="4">
+        <v>46223</v>
+      </c>
+      <c r="N39" s="12">
+        <f>WEEKNUM(Tabla2610[[#This Row],[Fecha]])</f>
+        <v>30</v>
+      </c>
+      <c r="O39" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="P39" s="1">
+        <v>600</v>
+      </c>
+      <c r="Q39" s="9">
+        <v>12264714</v>
+      </c>
+      <c r="R39" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="S39" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="40" spans="2:19" x14ac:dyDescent="0.3">
+      <c r="B40" s="4">
+        <v>46223</v>
+      </c>
+      <c r="C40" s="1">
+        <f>WEEKNUM(Tabla158[[#This Row],[Fecha]])</f>
+        <v>30</v>
+      </c>
+      <c r="D40" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="E40" s="1">
+        <v>800</v>
+      </c>
+      <c r="F40" s="9">
+        <v>12264714</v>
+      </c>
+      <c r="G40" s="1">
+        <v>35</v>
+      </c>
+      <c r="H40" s="1">
+        <v>14</v>
+      </c>
+      <c r="I40" s="3">
+        <f>Tabla158[[#This Row],[Piezas NOK]]/Tabla158[[#This Row],[Piezas OK]]</f>
+        <v>0.4</v>
+      </c>
+      <c r="J40" s="1">
+        <f t="shared" si="3"/>
+        <v>0.6</v>
+      </c>
+      <c r="K40" s="5">
+        <f>Tabla158[[#This Row],[FTQ]]</f>
+        <v>0.6</v>
+      </c>
+      <c r="M40" s="4">
+        <v>46223</v>
+      </c>
+      <c r="N40" s="12">
+        <f>WEEKNUM(Tabla2610[[#This Row],[Fecha]])</f>
+        <v>30</v>
+      </c>
+      <c r="O40" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="P40" s="1">
+        <v>600</v>
+      </c>
+      <c r="Q40" s="9">
+        <v>12264714</v>
+      </c>
+      <c r="R40" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="S40" s="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="41" spans="2:19" x14ac:dyDescent="0.3">
+      <c r="B41" s="4">
+        <v>46223</v>
+      </c>
+      <c r="C41" s="1">
+        <f>WEEKNUM(Tabla158[[#This Row],[Fecha]])</f>
+        <v>30</v>
+      </c>
+      <c r="D41" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="E41" s="1">
+        <v>900</v>
+      </c>
+      <c r="F41" s="9">
+        <v>12264714</v>
+      </c>
+      <c r="G41" s="1">
+        <v>21</v>
+      </c>
+      <c r="H41" s="1">
+        <v>0</v>
+      </c>
+      <c r="I41" s="3">
+        <f>Tabla158[[#This Row],[Piezas NOK]]/Tabla158[[#This Row],[Piezas OK]]</f>
+        <v>0</v>
+      </c>
+      <c r="J41" s="1">
+        <f t="shared" si="3"/>
+        <v>1</v>
+      </c>
+      <c r="K41" s="5">
+        <f>Tabla158[[#This Row],[FTQ]]</f>
+        <v>1</v>
+      </c>
+      <c r="M41" s="4">
+        <v>46223</v>
+      </c>
+      <c r="N41" s="12">
+        <f>WEEKNUM(Tabla2610[[#This Row],[Fecha]])</f>
+        <v>30</v>
+      </c>
+      <c r="O41" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="P41" s="1">
+        <v>700</v>
+      </c>
+      <c r="Q41" s="9">
+        <v>12264714</v>
+      </c>
+      <c r="R41" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="S41" s="1">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="42" spans="2:19" x14ac:dyDescent="0.3">
+      <c r="B42" s="4">
+        <v>46223</v>
+      </c>
+      <c r="C42" s="1">
+        <f>WEEKNUM(Tabla158[[#This Row],[Fecha]])</f>
+        <v>30</v>
+      </c>
+      <c r="D42" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="E42" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="F42" s="9">
+        <v>12264714</v>
+      </c>
+      <c r="G42" s="1">
+        <v>21</v>
+      </c>
+      <c r="H42" s="1">
+        <v>0</v>
+      </c>
+      <c r="I42" s="3">
+        <f>Tabla158[[#This Row],[Piezas NOK]]/Tabla158[[#This Row],[Piezas OK]]</f>
+        <v>0</v>
+      </c>
+      <c r="J42" s="1">
+        <f t="shared" si="3"/>
+        <v>1</v>
+      </c>
+      <c r="K42" s="5">
+        <f>Tabla158[[#This Row],[FTQ]]</f>
+        <v>1</v>
+      </c>
+      <c r="M42" s="4">
+        <v>46223</v>
+      </c>
+      <c r="N42" s="12">
+        <f>WEEKNUM(Tabla2610[[#This Row],[Fecha]])</f>
+        <v>30</v>
+      </c>
+      <c r="O42" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="P42" s="1">
+        <v>700</v>
+      </c>
+      <c r="Q42" s="9">
+        <v>12264714</v>
+      </c>
+      <c r="R42" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="S42" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="43" spans="2:19" x14ac:dyDescent="0.3">
+      <c r="B43" s="4">
+        <v>46223</v>
+      </c>
+      <c r="C43" s="1">
+        <f>WEEKNUM(Tabla158[[#This Row],[Fecha]])</f>
+        <v>30</v>
+      </c>
+      <c r="D43" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="E43" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F43" s="9">
+        <v>12264714</v>
+      </c>
+      <c r="G43" s="1">
+        <v>10</v>
+      </c>
+      <c r="H43" s="1">
+        <v>0</v>
+      </c>
+      <c r="I43" s="3">
+        <f>Tabla158[[#This Row],[Piezas NOK]]/Tabla158[[#This Row],[Piezas OK]]</f>
+        <v>0</v>
+      </c>
+      <c r="J43" s="1">
+        <f t="shared" si="3"/>
+        <v>1</v>
+      </c>
+      <c r="K43" s="5">
+        <f>Tabla158[[#This Row],[FTQ]]</f>
+        <v>1</v>
+      </c>
+      <c r="M43" s="4">
+        <v>46223</v>
+      </c>
+      <c r="N43" s="1">
+        <f>WEEKNUM(Tabla2610[[#This Row],[Fecha]])</f>
+        <v>30</v>
+      </c>
+      <c r="O43" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="P43" s="1">
+        <v>800</v>
+      </c>
+      <c r="Q43" s="9">
+        <v>12264714</v>
+      </c>
+      <c r="R43" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="S43" s="1">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="44" spans="2:19" x14ac:dyDescent="0.3">
+      <c r="B44" s="4">
+        <v>46227</v>
+      </c>
+      <c r="C44" s="1">
+        <f>WEEKNUM(Tabla158[[#This Row],[Fecha]])</f>
+        <v>30</v>
+      </c>
+      <c r="D44" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="E44" s="1">
+        <v>100</v>
+      </c>
+      <c r="F44" s="9">
+        <v>12260416</v>
+      </c>
+      <c r="G44" s="1">
+        <v>30</v>
+      </c>
+      <c r="H44" s="1">
+        <v>0</v>
+      </c>
+      <c r="I44" s="3">
+        <f>Tabla158[[#This Row],[Piezas NOK]]/Tabla158[[#This Row],[Piezas OK]]</f>
+        <v>0</v>
+      </c>
+      <c r="J44" s="1">
+        <f t="shared" si="3"/>
+        <v>1</v>
+      </c>
+      <c r="K44" s="5">
+        <f>Tabla158[[#This Row],[FTQ]]</f>
+        <v>1</v>
+      </c>
+      <c r="M44" s="4">
+        <v>46227</v>
+      </c>
+      <c r="N44" s="12">
+        <f>WEEKNUM(Tabla2610[[#This Row],[Fecha]])</f>
+        <v>30</v>
+      </c>
+      <c r="O44" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="P44" s="1">
+        <v>200</v>
+      </c>
+      <c r="Q44" s="9">
+        <v>12260416</v>
+      </c>
+      <c r="R44" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="S44" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="45" spans="2:19" x14ac:dyDescent="0.3">
+      <c r="B45" s="4">
+        <v>46227</v>
+      </c>
+      <c r="C45" s="12">
+        <f>WEEKNUM(Tabla158[[#This Row],[Fecha]])</f>
+        <v>30</v>
+      </c>
+      <c r="D45" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="E45" s="1">
+        <v>200</v>
+      </c>
+      <c r="F45" s="9">
+        <v>12260416</v>
+      </c>
+      <c r="G45" s="1">
+        <v>25</v>
+      </c>
+      <c r="H45" s="1">
+        <v>1</v>
+      </c>
+      <c r="I45" s="3">
+        <f>Tabla158[[#This Row],[Piezas NOK]]/Tabla158[[#This Row],[Piezas OK]]</f>
+        <v>0.04</v>
+      </c>
+      <c r="J45" s="12">
+        <f t="shared" ref="J45:J52" si="4">ABS(G$3-I45)</f>
+        <v>0.96</v>
+      </c>
+      <c r="K45" s="5">
+        <f>Tabla158[[#This Row],[FTQ]]</f>
+        <v>0.96</v>
+      </c>
+      <c r="M45" s="4">
+        <v>46227</v>
+      </c>
+      <c r="N45" s="12">
+        <f>WEEKNUM(Tabla2610[[#This Row],[Fecha]])</f>
+        <v>30</v>
+      </c>
+      <c r="O45" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="P45" s="1">
+        <v>300</v>
+      </c>
+      <c r="Q45" s="9">
+        <v>12260416</v>
+      </c>
+      <c r="R45" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="S45" s="1">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="46" spans="2:19" x14ac:dyDescent="0.3">
+      <c r="B46" s="4">
+        <v>46227</v>
+      </c>
+      <c r="C46" s="12">
+        <f>WEEKNUM(Tabla158[[#This Row],[Fecha]])</f>
+        <v>30</v>
+      </c>
+      <c r="D46" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="E46" s="1">
+        <v>300</v>
+      </c>
+      <c r="F46" s="9">
+        <v>12260416</v>
+      </c>
+      <c r="G46" s="1">
+        <v>16</v>
+      </c>
+      <c r="H46" s="1">
+        <v>4</v>
+      </c>
+      <c r="I46" s="3">
+        <f>Tabla158[[#This Row],[Piezas NOK]]/Tabla158[[#This Row],[Piezas OK]]</f>
+        <v>0.25</v>
+      </c>
+      <c r="J46" s="12">
+        <f t="shared" si="4"/>
+        <v>0.75</v>
+      </c>
+      <c r="K46" s="5">
+        <f>Tabla158[[#This Row],[FTQ]]</f>
+        <v>0.75</v>
+      </c>
+      <c r="M46" s="4">
+        <v>46227</v>
+      </c>
+      <c r="N46" s="12">
+        <f>WEEKNUM(Tabla2610[[#This Row],[Fecha]])</f>
+        <v>30</v>
+      </c>
+      <c r="O46" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="P46" s="1">
+        <v>300</v>
+      </c>
+      <c r="Q46" s="9">
+        <v>12260416</v>
+      </c>
+      <c r="R46" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="S46" s="1">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="47" spans="2:19" x14ac:dyDescent="0.3">
+      <c r="B47" s="4">
+        <v>46227</v>
+      </c>
+      <c r="C47" s="12">
+        <f>WEEKNUM(Tabla158[[#This Row],[Fecha]])</f>
+        <v>30</v>
+      </c>
+      <c r="D47" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="E47" s="1">
+        <v>400</v>
+      </c>
+      <c r="F47" s="9">
+        <v>12260416</v>
+      </c>
+      <c r="G47" s="1">
+        <v>20</v>
+      </c>
+      <c r="H47" s="1">
+        <v>10</v>
+      </c>
+      <c r="I47" s="3">
+        <f>Tabla158[[#This Row],[Piezas NOK]]/Tabla158[[#This Row],[Piezas OK]]</f>
+        <v>0.5</v>
+      </c>
+      <c r="J47" s="12">
+        <f t="shared" si="4"/>
+        <v>0.5</v>
+      </c>
+      <c r="K47" s="5">
+        <f>Tabla158[[#This Row],[FTQ]]</f>
+        <v>0.5</v>
+      </c>
+      <c r="M47" s="4">
+        <v>46227</v>
+      </c>
+      <c r="N47" s="12">
+        <f>WEEKNUM(Tabla2610[[#This Row],[Fecha]])</f>
+        <v>30</v>
+      </c>
+      <c r="O47" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="P47" s="1">
+        <v>400</v>
+      </c>
+      <c r="Q47" s="9">
+        <v>12260416</v>
+      </c>
+      <c r="R47" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="S47" s="1">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="48" spans="2:19" x14ac:dyDescent="0.3">
+      <c r="B48" s="4">
+        <v>46227</v>
+      </c>
+      <c r="C48" s="12">
+        <f>WEEKNUM(Tabla158[[#This Row],[Fecha]])</f>
+        <v>30</v>
+      </c>
+      <c r="D48" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="E48" s="1">
+        <v>600</v>
+      </c>
+      <c r="F48" s="9">
+        <v>12260416</v>
+      </c>
+      <c r="G48" s="1">
+        <v>20</v>
+      </c>
+      <c r="H48" s="1">
+        <v>4</v>
+      </c>
+      <c r="I48" s="3">
+        <f>Tabla158[[#This Row],[Piezas NOK]]/Tabla158[[#This Row],[Piezas OK]]</f>
+        <v>0.2</v>
+      </c>
+      <c r="J48" s="12">
+        <f t="shared" si="4"/>
+        <v>0.8</v>
+      </c>
+      <c r="K48" s="5">
+        <f>Tabla158[[#This Row],[FTQ]]</f>
+        <v>0.8</v>
+      </c>
+      <c r="M48" s="4">
+        <v>46227</v>
+      </c>
+      <c r="N48" s="12">
+        <f>WEEKNUM(Tabla2610[[#This Row],[Fecha]])</f>
+        <v>30</v>
+      </c>
+      <c r="O48" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="P48" s="1">
+        <v>400</v>
+      </c>
+      <c r="Q48" s="9">
+        <v>12260416</v>
+      </c>
+      <c r="R48" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="S48" s="1">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="49" spans="2:19" x14ac:dyDescent="0.3">
+      <c r="B49" s="4">
+        <v>46227</v>
+      </c>
+      <c r="C49" s="12">
+        <f>WEEKNUM(Tabla158[[#This Row],[Fecha]])</f>
+        <v>30</v>
+      </c>
+      <c r="D49" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="E49" s="1">
+        <v>700</v>
+      </c>
+      <c r="F49" s="9">
+        <v>12260416</v>
+      </c>
+      <c r="G49" s="1">
+        <v>13</v>
+      </c>
+      <c r="H49" s="1">
+        <v>9</v>
+      </c>
+      <c r="I49" s="3">
+        <f>Tabla158[[#This Row],[Piezas NOK]]/Tabla158[[#This Row],[Piezas OK]]</f>
+        <v>0.69230769230769229</v>
+      </c>
+      <c r="J49" s="12">
+        <f t="shared" si="4"/>
+        <v>0.30769230769230771</v>
+      </c>
+      <c r="K49" s="5">
+        <f>Tabla158[[#This Row],[FTQ]]</f>
+        <v>0.30769230769230771</v>
+      </c>
+      <c r="M49" s="4">
+        <v>46227</v>
+      </c>
+      <c r="N49" s="12">
+        <f>WEEKNUM(Tabla2610[[#This Row],[Fecha]])</f>
+        <v>30</v>
+      </c>
+      <c r="O49" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="P49" s="1">
+        <v>400</v>
+      </c>
+      <c r="Q49" s="9">
+        <v>12260416</v>
+      </c>
+      <c r="R49" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="S49" s="1">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="50" spans="2:19" x14ac:dyDescent="0.3">
+      <c r="B50" s="4">
+        <v>46227</v>
+      </c>
+      <c r="C50" s="12">
+        <f>WEEKNUM(Tabla158[[#This Row],[Fecha]])</f>
+        <v>30</v>
+      </c>
+      <c r="D50" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="E50" s="1">
+        <v>800</v>
+      </c>
+      <c r="F50" s="9">
+        <v>12260416</v>
+      </c>
+      <c r="G50" s="1">
+        <v>38</v>
+      </c>
+      <c r="H50" s="1">
+        <v>2</v>
+      </c>
+      <c r="I50" s="3">
+        <f>Tabla158[[#This Row],[Piezas NOK]]/Tabla158[[#This Row],[Piezas OK]]</f>
+        <v>5.2631578947368418E-2</v>
+      </c>
+      <c r="J50" s="12">
+        <f t="shared" si="4"/>
+        <v>0.94736842105263164</v>
+      </c>
+      <c r="K50" s="5">
+        <f>Tabla158[[#This Row],[FTQ]]</f>
+        <v>0.94736842105263164</v>
+      </c>
+      <c r="M50" s="4">
+        <v>46227</v>
+      </c>
+      <c r="N50" s="12">
+        <f>WEEKNUM(Tabla2610[[#This Row],[Fecha]])</f>
+        <v>30</v>
+      </c>
+      <c r="O50" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="P50" s="1">
+        <v>400</v>
+      </c>
+      <c r="Q50" s="9">
+        <v>12260416</v>
+      </c>
+      <c r="R50" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="S50" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="51" spans="2:19" x14ac:dyDescent="0.3">
+      <c r="B51" s="4">
+        <v>46227</v>
+      </c>
+      <c r="C51" s="12">
+        <f>WEEKNUM(Tabla158[[#This Row],[Fecha]])</f>
+        <v>30</v>
+      </c>
+      <c r="D51" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="E51" s="1">
+        <v>900</v>
+      </c>
+      <c r="F51" s="9">
+        <v>12260416</v>
+      </c>
+      <c r="G51" s="1">
+        <v>38</v>
+      </c>
+      <c r="H51" s="1">
+        <v>0</v>
+      </c>
+      <c r="I51" s="3">
+        <f>Tabla158[[#This Row],[Piezas NOK]]/Tabla158[[#This Row],[Piezas OK]]</f>
+        <v>0</v>
+      </c>
+      <c r="J51" s="12">
+        <f t="shared" si="4"/>
+        <v>1</v>
+      </c>
+      <c r="K51" s="5">
+        <f>Tabla158[[#This Row],[FTQ]]</f>
+        <v>1</v>
+      </c>
+      <c r="M51" s="4">
+        <v>46227</v>
+      </c>
+      <c r="N51" s="12">
+        <f>WEEKNUM(Tabla2610[[#This Row],[Fecha]])</f>
+        <v>30</v>
+      </c>
+      <c r="O51" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="P51" s="1">
+        <v>400</v>
+      </c>
+      <c r="Q51" s="9">
+        <v>12260416</v>
+      </c>
+      <c r="R51" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="S51" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="52" spans="2:19" x14ac:dyDescent="0.3">
+      <c r="B52" s="4">
+        <v>46227</v>
+      </c>
+      <c r="C52" s="12">
+        <f>WEEKNUM(Tabla158[[#This Row],[Fecha]])</f>
+        <v>30</v>
+      </c>
+      <c r="D52" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="E52" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="F52" s="9">
+        <v>12260416</v>
+      </c>
+      <c r="G52" s="1">
+        <v>32</v>
+      </c>
+      <c r="H52" s="1">
+        <v>6</v>
+      </c>
+      <c r="I52" s="3">
+        <f>Tabla158[[#This Row],[Piezas NOK]]/Tabla158[[#This Row],[Piezas OK]]</f>
+        <v>0.1875</v>
+      </c>
+      <c r="J52" s="12">
+        <f t="shared" si="4"/>
+        <v>0.8125</v>
+      </c>
+      <c r="K52" s="5">
+        <f>Tabla158[[#This Row],[FTQ]]</f>
+        <v>0.8125</v>
+      </c>
+      <c r="M52" s="4">
+        <v>46227</v>
+      </c>
+      <c r="N52" s="12">
+        <f>WEEKNUM(Tabla2610[[#This Row],[Fecha]])</f>
+        <v>30</v>
+      </c>
+      <c r="O52" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="P52" s="1">
+        <v>400</v>
+      </c>
+      <c r="Q52" s="9">
+        <v>12260416</v>
+      </c>
+      <c r="R52" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="S52" s="1">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="53" spans="2:19" x14ac:dyDescent="0.3">
+      <c r="B53" s="4">
+        <v>46227</v>
+      </c>
+      <c r="C53" s="12">
+        <f>WEEKNUM(Tabla158[[#This Row],[Fecha]])</f>
+        <v>30</v>
+      </c>
+      <c r="D53" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="E53" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F53" s="9">
+        <v>12260416</v>
+      </c>
+      <c r="G53" s="1">
+        <v>20</v>
+      </c>
+      <c r="H53" s="1">
+        <v>0</v>
+      </c>
+      <c r="I53" s="3">
+        <f>Tabla158[[#This Row],[Piezas NOK]]/Tabla158[[#This Row],[Piezas OK]]</f>
+        <v>0</v>
+      </c>
+      <c r="J53" s="12">
+        <f>ABS(G$3-I53)</f>
+        <v>1</v>
+      </c>
+      <c r="K53" s="5">
+        <f>Tabla158[[#This Row],[FTQ]]</f>
+        <v>1</v>
+      </c>
+      <c r="M53" s="4">
+        <v>46227</v>
+      </c>
+      <c r="N53" s="12">
+        <f>WEEKNUM(Tabla2610[[#This Row],[Fecha]])</f>
+        <v>30</v>
+      </c>
+      <c r="O53" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="P53" s="1">
+        <v>800</v>
+      </c>
+      <c r="Q53" s="9">
+        <v>12260416</v>
+      </c>
+      <c r="R53" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="S53" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="54" spans="2:19" x14ac:dyDescent="0.3">
+      <c r="B54" s="4">
+        <v>46227</v>
+      </c>
+      <c r="C54" s="12">
+        <f>WEEKNUM(Tabla158[[#This Row],[Fecha]])</f>
+        <v>30</v>
+      </c>
+      <c r="D54" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="E54" s="1">
+        <v>100</v>
+      </c>
+      <c r="F54" s="9">
+        <v>12260415</v>
+      </c>
+      <c r="G54" s="1">
+        <v>20</v>
+      </c>
+      <c r="H54" s="1">
+        <v>0</v>
+      </c>
+      <c r="I54" s="3">
+        <f>Tabla158[[#This Row],[Piezas NOK]]/Tabla158[[#This Row],[Piezas OK]]</f>
+        <v>0</v>
+      </c>
+      <c r="J54" s="12">
+        <f t="shared" ref="J54:J61" si="5">ABS(G$3-I54)</f>
+        <v>1</v>
+      </c>
+      <c r="K54" s="5">
+        <f>Tabla158[[#This Row],[FTQ]]</f>
+        <v>1</v>
+      </c>
+      <c r="M54" s="4">
+        <v>46227</v>
+      </c>
+      <c r="N54" s="12">
+        <f>WEEKNUM(Tabla2610[[#This Row],[Fecha]])</f>
+        <v>30</v>
+      </c>
+      <c r="O54" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="P54" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q54" s="9">
+        <v>12260416</v>
+      </c>
+      <c r="R54" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="S54" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="55" spans="2:19" x14ac:dyDescent="0.3">
+      <c r="B55" s="4">
+        <v>46227</v>
+      </c>
+      <c r="C55" s="12">
+        <f>WEEKNUM(Tabla158[[#This Row],[Fecha]])</f>
+        <v>30</v>
+      </c>
+      <c r="D55" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="E55" s="1">
+        <v>200</v>
+      </c>
+      <c r="F55" s="9">
+        <v>12260415</v>
+      </c>
+      <c r="G55" s="1">
+        <v>20</v>
+      </c>
+      <c r="H55" s="1">
+        <v>0</v>
+      </c>
+      <c r="I55" s="3">
+        <f>Tabla158[[#This Row],[Piezas NOK]]/Tabla158[[#This Row],[Piezas OK]]</f>
+        <v>0</v>
+      </c>
+      <c r="J55" s="12">
+        <f t="shared" si="5"/>
+        <v>1</v>
+      </c>
+      <c r="K55" s="5">
+        <f>Tabla158[[#This Row],[FTQ]]</f>
+        <v>1</v>
+      </c>
+      <c r="M55" s="4">
+        <v>46227</v>
+      </c>
+      <c r="N55" s="12">
+        <f>WEEKNUM(Tabla2610[[#This Row],[Fecha]])</f>
+        <v>30</v>
+      </c>
+      <c r="O55" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="P55" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q55" s="9">
+        <v>12260416</v>
+      </c>
+      <c r="R55" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="S55" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="56" spans="2:19" x14ac:dyDescent="0.3">
+      <c r="B56" s="4">
+        <v>46227</v>
+      </c>
+      <c r="C56" s="12">
+        <f>WEEKNUM(Tabla158[[#This Row],[Fecha]])</f>
+        <v>30</v>
+      </c>
+      <c r="D56" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="E56" s="1">
+        <v>300</v>
+      </c>
+      <c r="F56" s="9">
+        <v>12260415</v>
+      </c>
+      <c r="G56" s="1">
+        <v>20</v>
+      </c>
+      <c r="H56" s="1">
+        <v>0</v>
+      </c>
+      <c r="I56" s="3">
+        <f>Tabla158[[#This Row],[Piezas NOK]]/Tabla158[[#This Row],[Piezas OK]]</f>
+        <v>0</v>
+      </c>
+      <c r="J56" s="12">
+        <f t="shared" si="5"/>
+        <v>1</v>
+      </c>
+      <c r="K56" s="5">
+        <f>Tabla158[[#This Row],[FTQ]]</f>
+        <v>1</v>
+      </c>
+      <c r="M56" s="4">
+        <v>46227</v>
+      </c>
+      <c r="N56" s="12">
+        <f>WEEKNUM(Tabla2610[[#This Row],[Fecha]])</f>
+        <v>30</v>
+      </c>
+      <c r="O56" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="P56" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q56" s="9">
+        <v>12260416</v>
+      </c>
+      <c r="R56" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="S56" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="57" spans="2:19" x14ac:dyDescent="0.3">
+      <c r="B57" s="4">
+        <v>46227</v>
+      </c>
+      <c r="C57" s="12">
+        <f>WEEKNUM(Tabla158[[#This Row],[Fecha]])</f>
+        <v>30</v>
+      </c>
+      <c r="D57" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="E57" s="1">
+        <v>400</v>
+      </c>
+      <c r="F57" s="9">
+        <v>12260415</v>
+      </c>
+      <c r="G57" s="1">
+        <v>19</v>
+      </c>
+      <c r="H57" s="1">
+        <v>0</v>
+      </c>
+      <c r="I57" s="3">
+        <f>Tabla158[[#This Row],[Piezas NOK]]/Tabla158[[#This Row],[Piezas OK]]</f>
+        <v>0</v>
+      </c>
+      <c r="J57" s="12">
+        <f t="shared" si="5"/>
+        <v>1</v>
+      </c>
+      <c r="K57" s="5">
+        <f>Tabla158[[#This Row],[FTQ]]</f>
+        <v>1</v>
+      </c>
+      <c r="M57" s="4">
+        <v>46227</v>
+      </c>
+      <c r="N57" s="12">
+        <f>WEEKNUM(Tabla2610[[#This Row],[Fecha]])</f>
+        <v>30</v>
+      </c>
+      <c r="O57" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="P57" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q57" s="9">
+        <v>12260416</v>
+      </c>
+      <c r="R57" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="S57" s="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="2:19" x14ac:dyDescent="0.3">
+      <c r="B58" s="4">
+        <v>46227</v>
+      </c>
+      <c r="C58" s="12">
+        <f>WEEKNUM(Tabla158[[#This Row],[Fecha]])</f>
+        <v>30</v>
+      </c>
+      <c r="D58" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="E58" s="1">
+        <v>600</v>
+      </c>
+      <c r="F58" s="9">
+        <v>12260415</v>
+      </c>
+      <c r="G58" s="1">
+        <v>19</v>
+      </c>
+      <c r="H58" s="1">
+        <v>3</v>
+      </c>
+      <c r="I58" s="3">
+        <f>Tabla158[[#This Row],[Piezas NOK]]/Tabla158[[#This Row],[Piezas OK]]</f>
+        <v>0.15789473684210525</v>
+      </c>
+      <c r="J58" s="12">
+        <f t="shared" si="5"/>
+        <v>0.84210526315789469</v>
+      </c>
+      <c r="K58" s="5">
+        <f>Tabla158[[#This Row],[FTQ]]</f>
+        <v>0.84210526315789469</v>
+      </c>
+      <c r="M58" s="4">
+        <v>46220</v>
+      </c>
+      <c r="N58" s="12">
+        <f>WEEKNUM(Tabla2610[[#This Row],[Fecha]])</f>
+        <v>29</v>
+      </c>
+      <c r="O58" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="P58" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="Q58" s="9">
+        <v>12264714</v>
+      </c>
+      <c r="R58" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="S58" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="59" spans="2:19" x14ac:dyDescent="0.3">
+      <c r="B59" s="4">
+        <v>46227</v>
+      </c>
+      <c r="C59" s="12">
+        <f>WEEKNUM(Tabla158[[#This Row],[Fecha]])</f>
+        <v>30</v>
+      </c>
+      <c r="D59" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="E59" s="1">
+        <v>700</v>
+      </c>
+      <c r="F59" s="9">
+        <v>12260415</v>
+      </c>
+      <c r="G59" s="1">
+        <v>18</v>
+      </c>
+      <c r="H59" s="1">
+        <v>1</v>
+      </c>
+      <c r="I59" s="3">
+        <f>Tabla158[[#This Row],[Piezas NOK]]/Tabla158[[#This Row],[Piezas OK]]</f>
+        <v>5.5555555555555552E-2</v>
+      </c>
+      <c r="J59" s="12">
+        <f t="shared" si="5"/>
+        <v>0.94444444444444442</v>
+      </c>
+      <c r="K59" s="5">
+        <f>Tabla158[[#This Row],[FTQ]]</f>
+        <v>0.94444444444444442</v>
+      </c>
+      <c r="M59" s="4">
+        <v>46227</v>
+      </c>
+      <c r="N59" s="12">
+        <f>WEEKNUM(Tabla2610[[#This Row],[Fecha]])</f>
+        <v>30</v>
+      </c>
+      <c r="O59" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="P59" s="1">
+        <v>600</v>
+      </c>
+      <c r="Q59" s="9">
+        <v>12260415</v>
+      </c>
+      <c r="R59" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="S59" s="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="2:19" x14ac:dyDescent="0.3">
+      <c r="B60" s="4">
+        <v>46227</v>
+      </c>
+      <c r="C60" s="12">
+        <f>WEEKNUM(Tabla158[[#This Row],[Fecha]])</f>
+        <v>30</v>
+      </c>
+      <c r="D60" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="E60" s="1">
+        <v>800</v>
+      </c>
+      <c r="F60" s="9">
+        <v>12260415</v>
+      </c>
+      <c r="G60" s="1">
+        <v>18</v>
+      </c>
+      <c r="H60" s="1">
+        <v>4</v>
+      </c>
+      <c r="I60" s="3">
+        <f>Tabla158[[#This Row],[Piezas NOK]]/Tabla158[[#This Row],[Piezas OK]]</f>
+        <v>0.22222222222222221</v>
+      </c>
+      <c r="J60" s="12">
+        <f t="shared" si="5"/>
+        <v>0.77777777777777779</v>
+      </c>
+      <c r="K60" s="5">
+        <f>Tabla158[[#This Row],[FTQ]]</f>
+        <v>0.77777777777777779</v>
+      </c>
+      <c r="M60" s="4">
+        <v>46227</v>
+      </c>
+      <c r="N60" s="12">
+        <f>WEEKNUM(Tabla2610[[#This Row],[Fecha]])</f>
+        <v>30</v>
+      </c>
+      <c r="O60" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="P60" s="1">
+        <v>700</v>
+      </c>
+      <c r="Q60" s="9">
+        <v>12260415</v>
+      </c>
+      <c r="R60" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S60" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="61" spans="2:19" x14ac:dyDescent="0.3">
+      <c r="B61" s="4">
+        <v>46227</v>
+      </c>
+      <c r="C61" s="12">
+        <f>WEEKNUM(Tabla158[[#This Row],[Fecha]])</f>
+        <v>30</v>
+      </c>
+      <c r="D61" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="E61" s="1">
+        <v>900</v>
+      </c>
+      <c r="F61" s="9">
+        <v>12260415</v>
+      </c>
+      <c r="G61" s="1">
+        <v>18</v>
+      </c>
+      <c r="H61" s="1">
+        <v>0</v>
+      </c>
+      <c r="I61" s="3">
+        <f>Tabla158[[#This Row],[Piezas NOK]]/Tabla158[[#This Row],[Piezas OK]]</f>
+        <v>0</v>
+      </c>
+      <c r="J61" s="12">
+        <f t="shared" si="5"/>
+        <v>1</v>
+      </c>
+      <c r="K61" s="5">
+        <f>Tabla158[[#This Row],[FTQ]]</f>
+        <v>1</v>
+      </c>
+      <c r="M61" s="4">
+        <v>46227</v>
+      </c>
+      <c r="N61" s="12">
+        <f>WEEKNUM(Tabla2610[[#This Row],[Fecha]])</f>
+        <v>30</v>
+      </c>
+      <c r="O61" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="P61" s="1">
+        <v>800</v>
+      </c>
+      <c r="Q61" s="9">
+        <v>12260416</v>
+      </c>
+      <c r="R61" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="S61" s="1">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="62" spans="2:19" x14ac:dyDescent="0.3">
+      <c r="B62" s="4">
+        <v>46227</v>
+      </c>
+      <c r="C62" s="12">
+        <f>WEEKNUM(Tabla158[[#This Row],[Fecha]])</f>
+        <v>30</v>
+      </c>
+      <c r="D62" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="E62" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="F62" s="9">
+        <v>12260415</v>
+      </c>
+      <c r="G62" s="1">
+        <v>40</v>
+      </c>
+      <c r="H62" s="1">
+        <v>0</v>
+      </c>
+      <c r="I62" s="3">
+        <f>Tabla158[[#This Row],[Piezas NOK]]/Tabla158[[#This Row],[Piezas OK]]</f>
+        <v>0</v>
+      </c>
+      <c r="J62" s="12">
+        <f t="shared" ref="J62" si="6">ABS(G$3-I62)</f>
+        <v>1</v>
+      </c>
+      <c r="K62" s="5">
+        <f>Tabla158[[#This Row],[FTQ]]</f>
+        <v>1</v>
+      </c>
       <c r="M62" s="4"/>
     </row>
-    <row r="63" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="63" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B63" s="4"/>
       <c r="I63" s="3"/>
       <c r="J63" s="1"/>
       <c r="K63" s="5"/>
       <c r="M63" s="4"/>
     </row>
-    <row r="64" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="64" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B64" s="4"/>
       <c r="I64" s="3"/>
       <c r="J64" s="1"/>
@@ -27648,6 +29206,8 @@
       <c r="J221" s="1"/>
       <c r="K221" s="5"/>
       <c r="M221" s="4"/>
+      <c r="U221" s="1"/>
+      <c r="V221" s="1"/>
     </row>
     <row r="222" spans="2:22" x14ac:dyDescent="0.3">
       <c r="B222" s="4"/>
@@ -27664,8 +29224,6 @@
       <c r="J223" s="1"/>
       <c r="K223" s="5"/>
       <c r="M223" s="4"/>
-      <c r="U223" s="1"/>
-      <c r="V223" s="1"/>
     </row>
     <row r="224" spans="2:22" x14ac:dyDescent="0.3">
       <c r="B224" s="4"/>
@@ -27770,7 +29328,7 @@
       <c r="I238" s="3"/>
       <c r="J238" s="1"/>
       <c r="K238" s="5"/>
-      <c r="M238" s="4"/>
+      <c r="M238" s="8"/>
     </row>
     <row r="239" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B239" s="4"/>
@@ -27791,7 +29349,7 @@
       <c r="I241" s="3"/>
       <c r="J241" s="1"/>
       <c r="K241" s="5"/>
-      <c r="M241" s="8"/>
+      <c r="M241" s="4"/>
     </row>
     <row r="242" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B242" s="4"/>
@@ -28077,7 +29635,6 @@
       <c r="B282" s="4"/>
       <c r="I282" s="3"/>
       <c r="J282" s="1"/>
-      <c r="K282" s="5"/>
       <c r="M282" s="4"/>
     </row>
     <row r="283" spans="2:13" x14ac:dyDescent="0.3">
@@ -28102,7 +29659,6 @@
       <c r="B286" s="4"/>
       <c r="I286" s="3"/>
       <c r="J286" s="1"/>
-      <c r="M286" s="4"/>
     </row>
     <row r="287" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B287" s="4"/>
@@ -28114,165 +29670,165 @@
       <c r="I288" s="3"/>
       <c r="J288" s="1"/>
     </row>
-    <row r="289" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="289" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B289" s="4"/>
       <c r="I289" s="3"/>
       <c r="J289" s="1"/>
     </row>
-    <row r="290" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="290" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B290" s="4"/>
       <c r="I290" s="3"/>
       <c r="J290" s="1"/>
     </row>
-    <row r="291" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="291" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B291" s="4"/>
       <c r="I291" s="3"/>
       <c r="J291" s="1"/>
     </row>
-    <row r="292" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="292" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B292" s="4"/>
       <c r="I292" s="3"/>
       <c r="J292" s="1"/>
     </row>
-    <row r="293" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="293" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B293" s="4"/>
       <c r="I293" s="3"/>
       <c r="J293" s="1"/>
     </row>
-    <row r="294" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="294" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B294" s="4"/>
       <c r="I294" s="3"/>
       <c r="J294" s="1"/>
     </row>
-    <row r="295" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="295" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B295" s="4"/>
       <c r="I295" s="3"/>
       <c r="J295" s="1"/>
     </row>
-    <row r="296" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="296" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B296" s="4"/>
       <c r="I296" s="3"/>
       <c r="J296" s="1"/>
     </row>
-    <row r="297" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="297" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B297" s="4"/>
       <c r="I297" s="3"/>
       <c r="J297" s="1"/>
     </row>
-    <row r="298" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="298" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B298" s="4"/>
       <c r="I298" s="3"/>
       <c r="J298" s="1"/>
     </row>
-    <row r="299" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="299" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B299" s="4"/>
       <c r="I299" s="3"/>
       <c r="J299" s="1"/>
     </row>
-    <row r="300" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="300" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B300" s="4"/>
       <c r="I300" s="3"/>
       <c r="J300" s="1"/>
     </row>
-    <row r="301" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="301" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B301" s="4"/>
       <c r="I301" s="3"/>
       <c r="J301" s="1"/>
     </row>
-    <row r="302" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="302" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B302" s="4"/>
       <c r="I302" s="3"/>
       <c r="J302" s="1"/>
     </row>
-    <row r="303" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="303" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B303" s="4"/>
       <c r="I303" s="3"/>
       <c r="J303" s="1"/>
     </row>
-    <row r="304" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="304" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A304" t="s">
+        <v>0</v>
+      </c>
       <c r="B304" s="4"/>
       <c r="I304" s="3"/>
       <c r="J304" s="1"/>
     </row>
-    <row r="305" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A305" t="s">
-        <v>0</v>
-      </c>
+    <row r="305" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B305" s="4"/>
       <c r="I305" s="3"/>
       <c r="J305" s="1"/>
     </row>
-    <row r="306" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="306" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B306" s="4"/>
       <c r="I306" s="3"/>
       <c r="J306" s="1"/>
     </row>
-    <row r="307" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="307" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B307" s="4"/>
       <c r="I307" s="3"/>
       <c r="J307" s="1"/>
     </row>
-    <row r="308" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="308" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B308" s="4"/>
       <c r="I308" s="3"/>
       <c r="J308" s="1"/>
     </row>
-    <row r="309" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="309" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B309" s="4"/>
       <c r="I309" s="3"/>
       <c r="J309" s="1"/>
     </row>
-    <row r="310" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="310" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B310" s="4"/>
       <c r="I310" s="3"/>
       <c r="J310" s="1"/>
     </row>
-    <row r="311" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="311" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B311" s="4"/>
       <c r="I311" s="3"/>
       <c r="J311" s="1"/>
     </row>
-    <row r="312" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="312" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B312" s="4"/>
       <c r="I312" s="3"/>
       <c r="J312" s="1"/>
     </row>
-    <row r="313" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="313" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B313" s="4"/>
       <c r="I313" s="3"/>
       <c r="J313" s="1"/>
     </row>
-    <row r="314" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="314" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B314" s="4"/>
       <c r="I314" s="3"/>
       <c r="J314" s="1"/>
     </row>
-    <row r="315" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="315" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B315" s="4"/>
       <c r="I315" s="3"/>
       <c r="J315" s="1"/>
     </row>
-    <row r="316" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="316" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B316" s="4"/>
       <c r="I316" s="3"/>
       <c r="J316" s="1"/>
     </row>
-    <row r="317" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="317" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B317" s="4"/>
       <c r="I317" s="3"/>
       <c r="J317" s="1"/>
     </row>
-    <row r="318" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="318" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B318" s="4"/>
       <c r="I318" s="3"/>
       <c r="J318" s="1"/>
     </row>
-    <row r="319" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="319" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B319" s="4"/>
       <c r="I319" s="3"/>
       <c r="J319" s="1"/>
     </row>
-    <row r="320" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="320" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B320" s="4"/>
       <c r="I320" s="3"/>
       <c r="J320" s="1"/>
@@ -28393,14 +29949,14 @@
       <c r="J343" s="1"/>
     </row>
     <row r="344" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A344" t="s">
+        <v>0</v>
+      </c>
       <c r="B344" s="4"/>
       <c r="I344" s="3"/>
       <c r="J344" s="1"/>
     </row>
     <row r="345" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A345" t="s">
-        <v>0</v>
-      </c>
       <c r="B345" s="4"/>
       <c r="I345" s="3"/>
       <c r="J345" s="1"/>
@@ -28819,6 +30375,9 @@
       <c r="B428" s="4"/>
       <c r="I428" s="3"/>
       <c r="J428" s="1"/>
+      <c r="M428" s="7"/>
+      <c r="N428" s="7"/>
+      <c r="O428" s="7"/>
     </row>
     <row r="429" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B429" s="4"/>
@@ -28969,7 +30528,7 @@
       <c r="I447" s="3"/>
       <c r="J447" s="1"/>
       <c r="M447" s="7"/>
-      <c r="N447" s="7"/>
+      <c r="N447" s="8"/>
       <c r="O447" s="7"/>
     </row>
     <row r="448" spans="2:15" x14ac:dyDescent="0.3">
@@ -28977,7 +30536,7 @@
       <c r="I448" s="3"/>
       <c r="J448" s="1"/>
       <c r="M448" s="7"/>
-      <c r="N448" s="8"/>
+      <c r="N448" s="7"/>
       <c r="O448" s="7"/>
     </row>
     <row r="449" spans="2:15" x14ac:dyDescent="0.3">
@@ -29200,9 +30759,6 @@
       <c r="B476" s="4"/>
       <c r="I476" s="3"/>
       <c r="J476" s="1"/>
-      <c r="M476" s="7"/>
-      <c r="N476" s="7"/>
-      <c r="O476" s="7"/>
     </row>
     <row r="477" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B477" s="4"/>
@@ -30235,14 +31791,14 @@
       <c r="J682" s="1"/>
     </row>
     <row r="683" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A683" t="s">
+        <v>0</v>
+      </c>
       <c r="B683" s="4"/>
       <c r="I683" s="3"/>
       <c r="J683" s="1"/>
     </row>
     <row r="684" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A684" t="s">
-        <v>0</v>
-      </c>
       <c r="B684" s="4"/>
       <c r="I684" s="3"/>
       <c r="J684" s="1"/>
@@ -30268,14 +31824,14 @@
       <c r="J688" s="1"/>
     </row>
     <row r="689" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A689" t="s">
+        <v>0</v>
+      </c>
       <c r="B689" s="4"/>
       <c r="I689" s="3"/>
       <c r="J689" s="1"/>
     </row>
     <row r="690" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A690" t="s">
-        <v>0</v>
-      </c>
       <c r="B690" s="4"/>
       <c r="I690" s="3"/>
       <c r="J690" s="1"/>
@@ -30301,14 +31857,14 @@
       <c r="J694" s="1"/>
     </row>
     <row r="695" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A695" t="s">
+        <v>0</v>
+      </c>
       <c r="B695" s="4"/>
       <c r="I695" s="3"/>
       <c r="J695" s="1"/>
     </row>
     <row r="696" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A696" t="s">
-        <v>0</v>
-      </c>
       <c r="B696" s="4"/>
       <c r="I696" s="3"/>
       <c r="J696" s="1"/>
@@ -30334,14 +31890,14 @@
       <c r="J700" s="1"/>
     </row>
     <row r="701" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A701" t="s">
+        <v>0</v>
+      </c>
       <c r="B701" s="4"/>
       <c r="I701" s="3"/>
       <c r="J701" s="1"/>
     </row>
     <row r="702" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A702" t="s">
-        <v>0</v>
-      </c>
       <c r="B702" s="4"/>
       <c r="I702" s="3"/>
       <c r="J702" s="1"/>
@@ -30367,14 +31923,14 @@
       <c r="J706" s="1"/>
     </row>
     <row r="707" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A707" t="s">
+        <v>0</v>
+      </c>
       <c r="B707" s="4"/>
       <c r="I707" s="3"/>
       <c r="J707" s="1"/>
     </row>
     <row r="708" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A708" t="s">
-        <v>0</v>
-      </c>
       <c r="B708" s="4"/>
       <c r="I708" s="3"/>
       <c r="J708" s="1"/>
@@ -30400,14 +31956,14 @@
       <c r="J712" s="1"/>
     </row>
     <row r="713" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A713" t="s">
+        <v>0</v>
+      </c>
       <c r="B713" s="4"/>
       <c r="I713" s="3"/>
       <c r="J713" s="1"/>
     </row>
     <row r="714" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A714" t="s">
-        <v>0</v>
-      </c>
       <c r="B714" s="4"/>
       <c r="I714" s="3"/>
       <c r="J714" s="1"/>
@@ -30523,14 +32079,14 @@
       <c r="J736" s="1"/>
     </row>
     <row r="737" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A737" t="s">
+        <v>0</v>
+      </c>
       <c r="B737" s="4"/>
       <c r="I737" s="3"/>
       <c r="J737" s="1"/>
     </row>
     <row r="738" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A738" t="s">
-        <v>0</v>
-      </c>
       <c r="B738" s="4"/>
       <c r="I738" s="3"/>
       <c r="J738" s="1"/>
@@ -30616,14 +32172,14 @@
       <c r="J754" s="1"/>
     </row>
     <row r="755" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A755" t="s">
+        <v>0</v>
+      </c>
       <c r="B755" s="4"/>
       <c r="I755" s="3"/>
       <c r="J755" s="1"/>
     </row>
     <row r="756" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A756" t="s">
-        <v>0</v>
-      </c>
       <c r="B756" s="4"/>
       <c r="I756" s="3"/>
       <c r="J756" s="1"/>
@@ -30799,11 +32355,11 @@
       <c r="J790" s="1"/>
     </row>
     <row r="791" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B791" s="4"/>
       <c r="I791" s="3"/>
       <c r="J791" s="1"/>
     </row>
     <row r="792" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B792" s="4"/>
       <c r="I792" s="3"/>
       <c r="J792" s="1"/>
     </row>
@@ -30859,12 +32415,12 @@
     </row>
     <row r="803" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B803" s="4"/>
+      <c r="G803" s="4"/>
       <c r="I803" s="3"/>
       <c r="J803" s="1"/>
     </row>
     <row r="804" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B804" s="4"/>
-      <c r="G804" s="4"/>
       <c r="I804" s="3"/>
       <c r="J804" s="1"/>
     </row>
@@ -30997,11 +32553,6 @@
       <c r="B830" s="4"/>
       <c r="I830" s="3"/>
       <c r="J830" s="1"/>
-    </row>
-    <row r="831" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B831" s="4"/>
-      <c r="I831" s="3"/>
-      <c r="J831" s="1"/>
     </row>
   </sheetData>
   <mergeCells count="2">

--- a/BASE DE DATOS.xlsx
+++ b/BASE DE DATOS.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="J:\LAUNCH MANAGEMENT\1 KI\4_NX5a\09_Information\10_FTQ\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B81C1498-AB3E-42BA-9099-F89FB4C26158}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B35C4435-97D1-4CE5-BD79-745B6F832C0C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{439F1396-05A1-464E-A03B-8C77E5396FAA}"/>
   </bookViews>
@@ -21,7 +21,7 @@
     <externalReference r:id="rId4"/>
   </externalReferences>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'BASE DE DATOS RIVIAN'!$B$4:$J$62</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'BASE DE DATOS RIVIAN'!$B$4:$J$82</definedName>
     <definedName name="DATA_01">[1]Data_Lineal!$H$4:$Y$30</definedName>
     <definedName name="DB_01">#REF!</definedName>
     <definedName name="DB_CAP01">'[2]CAPACIDAD (1)'!$X$9:$AM$29</definedName>
@@ -64,7 +64,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="220" uniqueCount="51">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="289" uniqueCount="65">
   <si>
     <t>*</t>
   </si>
@@ -217,6 +217,48 @@
   </si>
   <si>
     <t>Detecta pieza sin pasar en operación anterior Op.700</t>
+  </si>
+  <si>
+    <t>Safe Launch</t>
+  </si>
+  <si>
+    <t>Falla de secuencia Op.100</t>
+  </si>
+  <si>
+    <t>Se pasa pieza de prueba (NOK) Op.200</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Falla inspección visual por mal acomodo de Upper Housing Op.300 </t>
+  </si>
+  <si>
+    <t>Palanca dañada Op.300</t>
+  </si>
+  <si>
+    <t>Pide pieza master antes de fin de turno Op.400</t>
+  </si>
+  <si>
+    <t>MES - Falla de seguimiento en piezas Op.600</t>
+  </si>
+  <si>
+    <t>Falla en scanner por lectura de etiqueta Op.200</t>
+  </si>
+  <si>
+    <t>Falla en scanner por lectura de etiqueta Op.700</t>
+  </si>
+  <si>
+    <t>Picos en puntos de soldeo Op.800</t>
+  </si>
+  <si>
+    <t>Falla en scanner por lectura de etiqueta Op.900</t>
+  </si>
+  <si>
+    <t>Falla de secuencia Op.900</t>
+  </si>
+  <si>
+    <t>1000A</t>
+  </si>
+  <si>
+    <t>Falla 0200.010 Op.1100A</t>
   </si>
 </sst>
 </file>
@@ -24321,7 +24363,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{421FD8D0-4DB9-4A88-8653-0AE7AE89107A}" name="Tabla158" displayName="Tabla158" ref="B4:K62" totalsRowShown="0" headerRowDxfId="20" dataDxfId="19">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{421FD8D0-4DB9-4A88-8653-0AE7AE89107A}" name="Tabla158" displayName="Tabla158" ref="B4:K82" totalsRowShown="0" headerRowDxfId="20" dataDxfId="19">
   <tableColumns count="10">
     <tableColumn id="1" xr3:uid="{CDAA4D20-2955-41E2-BD7E-9330E166FFF4}" name="Fecha" dataDxfId="18"/>
     <tableColumn id="9" xr3:uid="{F70BB124-92DE-4024-874C-EE3BA966CDE6}" name="Semana" dataDxfId="17">
@@ -24347,7 +24389,7 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{83880157-341F-4984-9DA8-9308A0C526D5}" name="Tabla2610" displayName="Tabla2610" ref="M4:S61" totalsRowShown="0" headerRowDxfId="8" dataDxfId="7">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{83880157-341F-4984-9DA8-9308A0C526D5}" name="Tabla2610" displayName="Tabla2610" ref="M4:S83" totalsRowShown="0" headerRowDxfId="8" dataDxfId="7">
   <tableColumns count="7">
     <tableColumn id="1" xr3:uid="{D688BA2E-A64E-4433-85E0-7EDBF854AF60}" name="Fecha" dataDxfId="6"/>
     <tableColumn id="7" xr3:uid="{D3EA5E8D-DD68-48AC-8DAC-4A4077839479}" name="Semana" dataDxfId="5">
@@ -24644,7 +24686,7 @@
     <col min="15" max="15" width="12.44140625" style="1" customWidth="1"/>
     <col min="16" max="16" width="13.21875" style="1" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="11.77734375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="50.44140625" style="1" customWidth="1"/>
+    <col min="18" max="18" width="57.109375" style="1" customWidth="1"/>
     <col min="19" max="19" width="13" style="1" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -26297,7 +26339,7 @@
       <c r="M31" s="4">
         <v>46223</v>
       </c>
-      <c r="N31" s="12">
+      <c r="N31" s="1">
         <f>WEEKNUM(Tabla2610[[#This Row],[Fecha]])</f>
         <v>30</v>
       </c>
@@ -26355,7 +26397,7 @@
       <c r="M32" s="4">
         <v>46223</v>
       </c>
-      <c r="N32" s="12">
+      <c r="N32" s="1">
         <f>WEEKNUM(Tabla2610[[#This Row],[Fecha]])</f>
         <v>30</v>
       </c>
@@ -26413,7 +26455,7 @@
       <c r="M33" s="4">
         <v>46223</v>
       </c>
-      <c r="N33" s="12">
+      <c r="N33" s="1">
         <f>WEEKNUM(Tabla2610[[#This Row],[Fecha]])</f>
         <v>30</v>
       </c>
@@ -26471,7 +26513,7 @@
       <c r="M34" s="4">
         <v>46223</v>
       </c>
-      <c r="N34" s="12">
+      <c r="N34" s="1">
         <f>WEEKNUM(Tabla2610[[#This Row],[Fecha]])</f>
         <v>30</v>
       </c>
@@ -26529,7 +26571,7 @@
       <c r="M35" s="4">
         <v>46223</v>
       </c>
-      <c r="N35" s="12">
+      <c r="N35" s="1">
         <f>WEEKNUM(Tabla2610[[#This Row],[Fecha]])</f>
         <v>30</v>
       </c>
@@ -26587,7 +26629,7 @@
       <c r="M36" s="4">
         <v>46223</v>
       </c>
-      <c r="N36" s="12">
+      <c r="N36" s="1">
         <f>WEEKNUM(Tabla2610[[#This Row],[Fecha]])</f>
         <v>30</v>
       </c>
@@ -26645,7 +26687,7 @@
       <c r="M37" s="4">
         <v>46223</v>
       </c>
-      <c r="N37" s="12">
+      <c r="N37" s="1">
         <f>WEEKNUM(Tabla2610[[#This Row],[Fecha]])</f>
         <v>30</v>
       </c>
@@ -26703,7 +26745,7 @@
       <c r="M38" s="4">
         <v>46223</v>
       </c>
-      <c r="N38" s="12">
+      <c r="N38" s="1">
         <f>WEEKNUM(Tabla2610[[#This Row],[Fecha]])</f>
         <v>30</v>
       </c>
@@ -26761,7 +26803,7 @@
       <c r="M39" s="4">
         <v>46223</v>
       </c>
-      <c r="N39" s="12">
+      <c r="N39" s="1">
         <f>WEEKNUM(Tabla2610[[#This Row],[Fecha]])</f>
         <v>30</v>
       </c>
@@ -26819,7 +26861,7 @@
       <c r="M40" s="4">
         <v>46223</v>
       </c>
-      <c r="N40" s="12">
+      <c r="N40" s="1">
         <f>WEEKNUM(Tabla2610[[#This Row],[Fecha]])</f>
         <v>30</v>
       </c>
@@ -26877,7 +26919,7 @@
       <c r="M41" s="4">
         <v>46223</v>
       </c>
-      <c r="N41" s="12">
+      <c r="N41" s="1">
         <f>WEEKNUM(Tabla2610[[#This Row],[Fecha]])</f>
         <v>30</v>
       </c>
@@ -26935,7 +26977,7 @@
       <c r="M42" s="4">
         <v>46223</v>
       </c>
-      <c r="N42" s="12">
+      <c r="N42" s="1">
         <f>WEEKNUM(Tabla2610[[#This Row],[Fecha]])</f>
         <v>30</v>
       </c>
@@ -27051,7 +27093,7 @@
       <c r="M44" s="4">
         <v>46227</v>
       </c>
-      <c r="N44" s="12">
+      <c r="N44" s="1">
         <f>WEEKNUM(Tabla2610[[#This Row],[Fecha]])</f>
         <v>30</v>
       </c>
@@ -27075,7 +27117,7 @@
       <c r="B45" s="4">
         <v>46227</v>
       </c>
-      <c r="C45" s="12">
+      <c r="C45" s="1">
         <f>WEEKNUM(Tabla158[[#This Row],[Fecha]])</f>
         <v>30</v>
       </c>
@@ -27098,7 +27140,7 @@
         <f>Tabla158[[#This Row],[Piezas NOK]]/Tabla158[[#This Row],[Piezas OK]]</f>
         <v>0.04</v>
       </c>
-      <c r="J45" s="12">
+      <c r="J45" s="1">
         <f t="shared" ref="J45:J52" si="4">ABS(G$3-I45)</f>
         <v>0.96</v>
       </c>
@@ -27109,7 +27151,7 @@
       <c r="M45" s="4">
         <v>46227</v>
       </c>
-      <c r="N45" s="12">
+      <c r="N45" s="1">
         <f>WEEKNUM(Tabla2610[[#This Row],[Fecha]])</f>
         <v>30</v>
       </c>
@@ -27133,7 +27175,7 @@
       <c r="B46" s="4">
         <v>46227</v>
       </c>
-      <c r="C46" s="12">
+      <c r="C46" s="1">
         <f>WEEKNUM(Tabla158[[#This Row],[Fecha]])</f>
         <v>30</v>
       </c>
@@ -27156,7 +27198,7 @@
         <f>Tabla158[[#This Row],[Piezas NOK]]/Tabla158[[#This Row],[Piezas OK]]</f>
         <v>0.25</v>
       </c>
-      <c r="J46" s="12">
+      <c r="J46" s="1">
         <f t="shared" si="4"/>
         <v>0.75</v>
       </c>
@@ -27167,7 +27209,7 @@
       <c r="M46" s="4">
         <v>46227</v>
       </c>
-      <c r="N46" s="12">
+      <c r="N46" s="1">
         <f>WEEKNUM(Tabla2610[[#This Row],[Fecha]])</f>
         <v>30</v>
       </c>
@@ -27191,7 +27233,7 @@
       <c r="B47" s="4">
         <v>46227</v>
       </c>
-      <c r="C47" s="12">
+      <c r="C47" s="1">
         <f>WEEKNUM(Tabla158[[#This Row],[Fecha]])</f>
         <v>30</v>
       </c>
@@ -27214,7 +27256,7 @@
         <f>Tabla158[[#This Row],[Piezas NOK]]/Tabla158[[#This Row],[Piezas OK]]</f>
         <v>0.5</v>
       </c>
-      <c r="J47" s="12">
+      <c r="J47" s="1">
         <f t="shared" si="4"/>
         <v>0.5</v>
       </c>
@@ -27225,7 +27267,7 @@
       <c r="M47" s="4">
         <v>46227</v>
       </c>
-      <c r="N47" s="12">
+      <c r="N47" s="1">
         <f>WEEKNUM(Tabla2610[[#This Row],[Fecha]])</f>
         <v>30</v>
       </c>
@@ -27249,7 +27291,7 @@
       <c r="B48" s="4">
         <v>46227</v>
       </c>
-      <c r="C48" s="12">
+      <c r="C48" s="1">
         <f>WEEKNUM(Tabla158[[#This Row],[Fecha]])</f>
         <v>30</v>
       </c>
@@ -27272,7 +27314,7 @@
         <f>Tabla158[[#This Row],[Piezas NOK]]/Tabla158[[#This Row],[Piezas OK]]</f>
         <v>0.2</v>
       </c>
-      <c r="J48" s="12">
+      <c r="J48" s="1">
         <f t="shared" si="4"/>
         <v>0.8</v>
       </c>
@@ -27283,7 +27325,7 @@
       <c r="M48" s="4">
         <v>46227</v>
       </c>
-      <c r="N48" s="12">
+      <c r="N48" s="1">
         <f>WEEKNUM(Tabla2610[[#This Row],[Fecha]])</f>
         <v>30</v>
       </c>
@@ -27307,7 +27349,7 @@
       <c r="B49" s="4">
         <v>46227</v>
       </c>
-      <c r="C49" s="12">
+      <c r="C49" s="1">
         <f>WEEKNUM(Tabla158[[#This Row],[Fecha]])</f>
         <v>30</v>
       </c>
@@ -27330,7 +27372,7 @@
         <f>Tabla158[[#This Row],[Piezas NOK]]/Tabla158[[#This Row],[Piezas OK]]</f>
         <v>0.69230769230769229</v>
       </c>
-      <c r="J49" s="12">
+      <c r="J49" s="1">
         <f t="shared" si="4"/>
         <v>0.30769230769230771</v>
       </c>
@@ -27341,7 +27383,7 @@
       <c r="M49" s="4">
         <v>46227</v>
       </c>
-      <c r="N49" s="12">
+      <c r="N49" s="1">
         <f>WEEKNUM(Tabla2610[[#This Row],[Fecha]])</f>
         <v>30</v>
       </c>
@@ -27365,7 +27407,7 @@
       <c r="B50" s="4">
         <v>46227</v>
       </c>
-      <c r="C50" s="12">
+      <c r="C50" s="1">
         <f>WEEKNUM(Tabla158[[#This Row],[Fecha]])</f>
         <v>30</v>
       </c>
@@ -27388,7 +27430,7 @@
         <f>Tabla158[[#This Row],[Piezas NOK]]/Tabla158[[#This Row],[Piezas OK]]</f>
         <v>5.2631578947368418E-2</v>
       </c>
-      <c r="J50" s="12">
+      <c r="J50" s="1">
         <f t="shared" si="4"/>
         <v>0.94736842105263164</v>
       </c>
@@ -27399,7 +27441,7 @@
       <c r="M50" s="4">
         <v>46227</v>
       </c>
-      <c r="N50" s="12">
+      <c r="N50" s="1">
         <f>WEEKNUM(Tabla2610[[#This Row],[Fecha]])</f>
         <v>30</v>
       </c>
@@ -27423,7 +27465,7 @@
       <c r="B51" s="4">
         <v>46227</v>
       </c>
-      <c r="C51" s="12">
+      <c r="C51" s="1">
         <f>WEEKNUM(Tabla158[[#This Row],[Fecha]])</f>
         <v>30</v>
       </c>
@@ -27446,7 +27488,7 @@
         <f>Tabla158[[#This Row],[Piezas NOK]]/Tabla158[[#This Row],[Piezas OK]]</f>
         <v>0</v>
       </c>
-      <c r="J51" s="12">
+      <c r="J51" s="1">
         <f t="shared" si="4"/>
         <v>1</v>
       </c>
@@ -27457,7 +27499,7 @@
       <c r="M51" s="4">
         <v>46227</v>
       </c>
-      <c r="N51" s="12">
+      <c r="N51" s="1">
         <f>WEEKNUM(Tabla2610[[#This Row],[Fecha]])</f>
         <v>30</v>
       </c>
@@ -27481,7 +27523,7 @@
       <c r="B52" s="4">
         <v>46227</v>
       </c>
-      <c r="C52" s="12">
+      <c r="C52" s="1">
         <f>WEEKNUM(Tabla158[[#This Row],[Fecha]])</f>
         <v>30</v>
       </c>
@@ -27504,7 +27546,7 @@
         <f>Tabla158[[#This Row],[Piezas NOK]]/Tabla158[[#This Row],[Piezas OK]]</f>
         <v>0.1875</v>
       </c>
-      <c r="J52" s="12">
+      <c r="J52" s="1">
         <f t="shared" si="4"/>
         <v>0.8125</v>
       </c>
@@ -27515,7 +27557,7 @@
       <c r="M52" s="4">
         <v>46227</v>
       </c>
-      <c r="N52" s="12">
+      <c r="N52" s="1">
         <f>WEEKNUM(Tabla2610[[#This Row],[Fecha]])</f>
         <v>30</v>
       </c>
@@ -27539,7 +27581,7 @@
       <c r="B53" s="4">
         <v>46227</v>
       </c>
-      <c r="C53" s="12">
+      <c r="C53" s="1">
         <f>WEEKNUM(Tabla158[[#This Row],[Fecha]])</f>
         <v>30</v>
       </c>
@@ -27562,7 +27604,7 @@
         <f>Tabla158[[#This Row],[Piezas NOK]]/Tabla158[[#This Row],[Piezas OK]]</f>
         <v>0</v>
       </c>
-      <c r="J53" s="12">
+      <c r="J53" s="1">
         <f>ABS(G$3-I53)</f>
         <v>1</v>
       </c>
@@ -27573,7 +27615,7 @@
       <c r="M53" s="4">
         <v>46227</v>
       </c>
-      <c r="N53" s="12">
+      <c r="N53" s="1">
         <f>WEEKNUM(Tabla2610[[#This Row],[Fecha]])</f>
         <v>30</v>
       </c>
@@ -27597,7 +27639,7 @@
       <c r="B54" s="4">
         <v>46227</v>
       </c>
-      <c r="C54" s="12">
+      <c r="C54" s="1">
         <f>WEEKNUM(Tabla158[[#This Row],[Fecha]])</f>
         <v>30</v>
       </c>
@@ -27620,7 +27662,7 @@
         <f>Tabla158[[#This Row],[Piezas NOK]]/Tabla158[[#This Row],[Piezas OK]]</f>
         <v>0</v>
       </c>
-      <c r="J54" s="12">
+      <c r="J54" s="1">
         <f t="shared" ref="J54:J61" si="5">ABS(G$3-I54)</f>
         <v>1</v>
       </c>
@@ -27631,7 +27673,7 @@
       <c r="M54" s="4">
         <v>46227</v>
       </c>
-      <c r="N54" s="12">
+      <c r="N54" s="1">
         <f>WEEKNUM(Tabla2610[[#This Row],[Fecha]])</f>
         <v>30</v>
       </c>
@@ -27655,7 +27697,7 @@
       <c r="B55" s="4">
         <v>46227</v>
       </c>
-      <c r="C55" s="12">
+      <c r="C55" s="1">
         <f>WEEKNUM(Tabla158[[#This Row],[Fecha]])</f>
         <v>30</v>
       </c>
@@ -27678,7 +27720,7 @@
         <f>Tabla158[[#This Row],[Piezas NOK]]/Tabla158[[#This Row],[Piezas OK]]</f>
         <v>0</v>
       </c>
-      <c r="J55" s="12">
+      <c r="J55" s="1">
         <f t="shared" si="5"/>
         <v>1</v>
       </c>
@@ -27689,7 +27731,7 @@
       <c r="M55" s="4">
         <v>46227</v>
       </c>
-      <c r="N55" s="12">
+      <c r="N55" s="1">
         <f>WEEKNUM(Tabla2610[[#This Row],[Fecha]])</f>
         <v>30</v>
       </c>
@@ -27713,7 +27755,7 @@
       <c r="B56" s="4">
         <v>46227</v>
       </c>
-      <c r="C56" s="12">
+      <c r="C56" s="1">
         <f>WEEKNUM(Tabla158[[#This Row],[Fecha]])</f>
         <v>30</v>
       </c>
@@ -27736,7 +27778,7 @@
         <f>Tabla158[[#This Row],[Piezas NOK]]/Tabla158[[#This Row],[Piezas OK]]</f>
         <v>0</v>
       </c>
-      <c r="J56" s="12">
+      <c r="J56" s="1">
         <f t="shared" si="5"/>
         <v>1</v>
       </c>
@@ -27747,7 +27789,7 @@
       <c r="M56" s="4">
         <v>46227</v>
       </c>
-      <c r="N56" s="12">
+      <c r="N56" s="1">
         <f>WEEKNUM(Tabla2610[[#This Row],[Fecha]])</f>
         <v>30</v>
       </c>
@@ -27771,7 +27813,7 @@
       <c r="B57" s="4">
         <v>46227</v>
       </c>
-      <c r="C57" s="12">
+      <c r="C57" s="1">
         <f>WEEKNUM(Tabla158[[#This Row],[Fecha]])</f>
         <v>30</v>
       </c>
@@ -27794,7 +27836,7 @@
         <f>Tabla158[[#This Row],[Piezas NOK]]/Tabla158[[#This Row],[Piezas OK]]</f>
         <v>0</v>
       </c>
-      <c r="J57" s="12">
+      <c r="J57" s="1">
         <f t="shared" si="5"/>
         <v>1</v>
       </c>
@@ -27805,7 +27847,7 @@
       <c r="M57" s="4">
         <v>46227</v>
       </c>
-      <c r="N57" s="12">
+      <c r="N57" s="1">
         <f>WEEKNUM(Tabla2610[[#This Row],[Fecha]])</f>
         <v>30</v>
       </c>
@@ -27829,7 +27871,7 @@
       <c r="B58" s="4">
         <v>46227</v>
       </c>
-      <c r="C58" s="12">
+      <c r="C58" s="1">
         <f>WEEKNUM(Tabla158[[#This Row],[Fecha]])</f>
         <v>30</v>
       </c>
@@ -27852,7 +27894,7 @@
         <f>Tabla158[[#This Row],[Piezas NOK]]/Tabla158[[#This Row],[Piezas OK]]</f>
         <v>0.15789473684210525</v>
       </c>
-      <c r="J58" s="12">
+      <c r="J58" s="1">
         <f t="shared" si="5"/>
         <v>0.84210526315789469</v>
       </c>
@@ -27863,7 +27905,7 @@
       <c r="M58" s="4">
         <v>46220</v>
       </c>
-      <c r="N58" s="12">
+      <c r="N58" s="1">
         <f>WEEKNUM(Tabla2610[[#This Row],[Fecha]])</f>
         <v>29</v>
       </c>
@@ -27887,7 +27929,7 @@
       <c r="B59" s="4">
         <v>46227</v>
       </c>
-      <c r="C59" s="12">
+      <c r="C59" s="1">
         <f>WEEKNUM(Tabla158[[#This Row],[Fecha]])</f>
         <v>30</v>
       </c>
@@ -27910,7 +27952,7 @@
         <f>Tabla158[[#This Row],[Piezas NOK]]/Tabla158[[#This Row],[Piezas OK]]</f>
         <v>5.5555555555555552E-2</v>
       </c>
-      <c r="J59" s="12">
+      <c r="J59" s="1">
         <f t="shared" si="5"/>
         <v>0.94444444444444442</v>
       </c>
@@ -27921,7 +27963,7 @@
       <c r="M59" s="4">
         <v>46227</v>
       </c>
-      <c r="N59" s="12">
+      <c r="N59" s="1">
         <f>WEEKNUM(Tabla2610[[#This Row],[Fecha]])</f>
         <v>30</v>
       </c>
@@ -27945,7 +27987,7 @@
       <c r="B60" s="4">
         <v>46227</v>
       </c>
-      <c r="C60" s="12">
+      <c r="C60" s="1">
         <f>WEEKNUM(Tabla158[[#This Row],[Fecha]])</f>
         <v>30</v>
       </c>
@@ -27968,7 +28010,7 @@
         <f>Tabla158[[#This Row],[Piezas NOK]]/Tabla158[[#This Row],[Piezas OK]]</f>
         <v>0.22222222222222221</v>
       </c>
-      <c r="J60" s="12">
+      <c r="J60" s="1">
         <f t="shared" si="5"/>
         <v>0.77777777777777779</v>
       </c>
@@ -27979,7 +28021,7 @@
       <c r="M60" s="4">
         <v>46227</v>
       </c>
-      <c r="N60" s="12">
+      <c r="N60" s="1">
         <f>WEEKNUM(Tabla2610[[#This Row],[Fecha]])</f>
         <v>30</v>
       </c>
@@ -28003,7 +28045,7 @@
       <c r="B61" s="4">
         <v>46227</v>
       </c>
-      <c r="C61" s="12">
+      <c r="C61" s="1">
         <f>WEEKNUM(Tabla158[[#This Row],[Fecha]])</f>
         <v>30</v>
       </c>
@@ -28026,7 +28068,7 @@
         <f>Tabla158[[#This Row],[Piezas NOK]]/Tabla158[[#This Row],[Piezas OK]]</f>
         <v>0</v>
       </c>
-      <c r="J61" s="12">
+      <c r="J61" s="1">
         <f t="shared" si="5"/>
         <v>1</v>
       </c>
@@ -28037,7 +28079,7 @@
       <c r="M61" s="4">
         <v>46227</v>
       </c>
-      <c r="N61" s="12">
+      <c r="N61" s="1">
         <f>WEEKNUM(Tabla2610[[#This Row],[Fecha]])</f>
         <v>30</v>
       </c>
@@ -28061,7 +28103,7 @@
       <c r="B62" s="4">
         <v>46227</v>
       </c>
-      <c r="C62" s="12">
+      <c r="C62" s="1">
         <f>WEEKNUM(Tabla158[[#This Row],[Fecha]])</f>
         <v>30</v>
       </c>
@@ -28084,7 +28126,7 @@
         <f>Tabla158[[#This Row],[Piezas NOK]]/Tabla158[[#This Row],[Piezas OK]]</f>
         <v>0</v>
       </c>
-      <c r="J62" s="12">
+      <c r="J62" s="1">
         <f t="shared" ref="J62" si="6">ABS(G$3-I62)</f>
         <v>1</v>
       </c>
@@ -28092,240 +28134,1302 @@
         <f>Tabla158[[#This Row],[FTQ]]</f>
         <v>1</v>
       </c>
-      <c r="M62" s="4"/>
+      <c r="M62" s="4">
+        <v>46265</v>
+      </c>
+      <c r="N62" s="12">
+        <f>WEEKNUM(Tabla2610[[#This Row],[Fecha]])</f>
+        <v>36</v>
+      </c>
+      <c r="O62" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="P62" s="1">
+        <v>100</v>
+      </c>
+      <c r="Q62" s="9">
+        <v>12260415</v>
+      </c>
+      <c r="R62" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="S62" s="1">
+        <v>1</v>
+      </c>
     </row>
     <row r="63" spans="2:19" x14ac:dyDescent="0.3">
-      <c r="B63" s="4"/>
-      <c r="I63" s="3"/>
-      <c r="J63" s="1"/>
-      <c r="K63" s="5"/>
-      <c r="M63" s="4"/>
+      <c r="B63" s="4">
+        <v>46265</v>
+      </c>
+      <c r="C63" s="12">
+        <f>WEEKNUM(Tabla158[[#This Row],[Fecha]])</f>
+        <v>36</v>
+      </c>
+      <c r="D63" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="E63" s="1">
+        <v>100</v>
+      </c>
+      <c r="F63" s="9">
+        <v>12260415</v>
+      </c>
+      <c r="G63" s="1">
+        <v>100</v>
+      </c>
+      <c r="H63" s="1">
+        <v>1</v>
+      </c>
+      <c r="I63" s="3">
+        <f>Tabla158[[#This Row],[Piezas NOK]]/Tabla158[[#This Row],[Piezas OK]]</f>
+        <v>0.01</v>
+      </c>
+      <c r="J63" s="12">
+        <f t="shared" ref="J63:J71" si="7">ABS(G$3-I63)</f>
+        <v>0.99</v>
+      </c>
+      <c r="K63" s="5">
+        <f>Tabla158[[#This Row],[FTQ]]</f>
+        <v>0.99</v>
+      </c>
+      <c r="M63" s="4">
+        <v>46265</v>
+      </c>
+      <c r="N63" s="12">
+        <f>WEEKNUM(Tabla2610[[#This Row],[Fecha]])</f>
+        <v>36</v>
+      </c>
+      <c r="O63" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="P63" s="1">
+        <v>100</v>
+      </c>
+      <c r="Q63" s="9">
+        <v>12260416</v>
+      </c>
+      <c r="R63" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="S63" s="1">
+        <v>1</v>
+      </c>
     </row>
     <row r="64" spans="2:19" x14ac:dyDescent="0.3">
-      <c r="B64" s="4"/>
-      <c r="I64" s="3"/>
-      <c r="J64" s="1"/>
-      <c r="K64" s="5"/>
-      <c r="M64" s="4"/>
-    </row>
-    <row r="65" spans="2:13" x14ac:dyDescent="0.3">
-      <c r="B65" s="4"/>
-      <c r="I65" s="3"/>
-      <c r="J65" s="1"/>
-      <c r="K65" s="5"/>
-      <c r="M65" s="4"/>
-    </row>
-    <row r="66" spans="2:13" x14ac:dyDescent="0.3">
-      <c r="B66" s="4"/>
-      <c r="I66" s="3"/>
-      <c r="J66" s="1"/>
-      <c r="K66" s="5"/>
-      <c r="M66" s="4"/>
-    </row>
-    <row r="67" spans="2:13" x14ac:dyDescent="0.3">
-      <c r="B67" s="4"/>
-      <c r="I67" s="3"/>
-      <c r="J67" s="1"/>
-      <c r="K67" s="5"/>
-      <c r="M67" s="4"/>
-    </row>
-    <row r="68" spans="2:13" x14ac:dyDescent="0.3">
-      <c r="B68" s="4"/>
-      <c r="I68" s="3"/>
-      <c r="J68" s="1"/>
-      <c r="K68" s="5"/>
-      <c r="M68" s="4"/>
-    </row>
-    <row r="69" spans="2:13" x14ac:dyDescent="0.3">
-      <c r="B69" s="4"/>
-      <c r="I69" s="3"/>
-      <c r="J69" s="1"/>
-      <c r="K69" s="5"/>
-      <c r="M69" s="4"/>
-    </row>
-    <row r="70" spans="2:13" x14ac:dyDescent="0.3">
-      <c r="B70" s="4"/>
-      <c r="I70" s="3"/>
-      <c r="J70" s="1"/>
-      <c r="K70" s="5"/>
-      <c r="M70" s="4"/>
-    </row>
-    <row r="71" spans="2:13" x14ac:dyDescent="0.3">
-      <c r="B71" s="4"/>
-      <c r="I71" s="3"/>
-      <c r="J71" s="1"/>
-      <c r="K71" s="5"/>
-      <c r="M71" s="4"/>
-    </row>
-    <row r="72" spans="2:13" x14ac:dyDescent="0.3">
-      <c r="B72" s="4"/>
-      <c r="I72" s="3"/>
-      <c r="J72" s="1"/>
-      <c r="K72" s="5"/>
-      <c r="M72" s="4"/>
-    </row>
-    <row r="73" spans="2:13" x14ac:dyDescent="0.3">
-      <c r="B73" s="4"/>
-      <c r="I73" s="3"/>
-      <c r="J73" s="1"/>
-      <c r="K73" s="5"/>
-      <c r="M73" s="4"/>
-    </row>
-    <row r="74" spans="2:13" x14ac:dyDescent="0.3">
-      <c r="B74" s="4"/>
-      <c r="I74" s="3"/>
-      <c r="J74" s="1"/>
-      <c r="K74" s="5"/>
-      <c r="M74" s="4"/>
-    </row>
-    <row r="75" spans="2:13" x14ac:dyDescent="0.3">
-      <c r="B75" s="4"/>
-      <c r="I75" s="3"/>
-      <c r="J75" s="1"/>
-      <c r="K75" s="5"/>
-      <c r="M75" s="4"/>
-    </row>
-    <row r="76" spans="2:13" x14ac:dyDescent="0.3">
-      <c r="B76" s="4"/>
-      <c r="I76" s="3"/>
-      <c r="J76" s="1"/>
-      <c r="K76" s="5"/>
-      <c r="M76" s="4"/>
-    </row>
-    <row r="77" spans="2:13" x14ac:dyDescent="0.3">
-      <c r="B77" s="4"/>
-      <c r="I77" s="3"/>
-      <c r="J77" s="1"/>
-      <c r="K77" s="5"/>
-      <c r="M77" s="4"/>
-    </row>
-    <row r="78" spans="2:13" x14ac:dyDescent="0.3">
-      <c r="B78" s="4"/>
-      <c r="I78" s="3"/>
-      <c r="J78" s="1"/>
-      <c r="K78" s="5"/>
-      <c r="M78" s="4"/>
-    </row>
-    <row r="79" spans="2:13" x14ac:dyDescent="0.3">
-      <c r="B79" s="4"/>
-      <c r="I79" s="3"/>
-      <c r="J79" s="1"/>
-      <c r="K79" s="5"/>
-      <c r="M79" s="4"/>
-    </row>
-    <row r="80" spans="2:13" x14ac:dyDescent="0.3">
-      <c r="B80" s="4"/>
-      <c r="I80" s="3"/>
-      <c r="J80" s="1"/>
-      <c r="K80" s="5"/>
-      <c r="M80" s="4"/>
-    </row>
-    <row r="81" spans="2:13" x14ac:dyDescent="0.3">
-      <c r="B81" s="4"/>
-      <c r="I81" s="3"/>
-      <c r="J81" s="1"/>
-      <c r="K81" s="5"/>
-      <c r="M81" s="4"/>
-    </row>
-    <row r="82" spans="2:13" x14ac:dyDescent="0.3">
-      <c r="B82" s="4"/>
-      <c r="I82" s="3"/>
-      <c r="J82" s="1"/>
-      <c r="K82" s="5"/>
-      <c r="M82" s="4"/>
-    </row>
-    <row r="83" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="B64" s="4">
+        <v>46265</v>
+      </c>
+      <c r="C64" s="12">
+        <f>WEEKNUM(Tabla158[[#This Row],[Fecha]])</f>
+        <v>36</v>
+      </c>
+      <c r="D64" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="E64" s="1">
+        <v>200</v>
+      </c>
+      <c r="F64" s="9">
+        <v>12260415</v>
+      </c>
+      <c r="G64" s="1">
+        <v>80</v>
+      </c>
+      <c r="H64" s="1">
+        <v>1</v>
+      </c>
+      <c r="I64" s="3">
+        <f>Tabla158[[#This Row],[Piezas NOK]]/Tabla158[[#This Row],[Piezas OK]]</f>
+        <v>1.2500000000000001E-2</v>
+      </c>
+      <c r="J64" s="12">
+        <f t="shared" si="7"/>
+        <v>0.98750000000000004</v>
+      </c>
+      <c r="K64" s="5">
+        <f>Tabla158[[#This Row],[FTQ]]</f>
+        <v>0.98750000000000004</v>
+      </c>
+      <c r="M64" s="4">
+        <v>46265</v>
+      </c>
+      <c r="N64" s="12">
+        <f>WEEKNUM(Tabla2610[[#This Row],[Fecha]])</f>
+        <v>36</v>
+      </c>
+      <c r="O64" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="P64" s="1">
+        <v>200</v>
+      </c>
+      <c r="Q64" s="9">
+        <v>12260415</v>
+      </c>
+      <c r="R64" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="S64" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="65" spans="2:19" x14ac:dyDescent="0.3">
+      <c r="B65" s="4">
+        <v>46265</v>
+      </c>
+      <c r="C65" s="12">
+        <f>WEEKNUM(Tabla158[[#This Row],[Fecha]])</f>
+        <v>36</v>
+      </c>
+      <c r="D65" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="E65" s="1">
+        <v>300</v>
+      </c>
+      <c r="F65" s="9">
+        <v>12260415</v>
+      </c>
+      <c r="G65" s="1">
+        <v>81</v>
+      </c>
+      <c r="H65" s="1">
+        <v>3</v>
+      </c>
+      <c r="I65" s="3">
+        <f>Tabla158[[#This Row],[Piezas NOK]]/Tabla158[[#This Row],[Piezas OK]]</f>
+        <v>3.7037037037037035E-2</v>
+      </c>
+      <c r="J65" s="12">
+        <f t="shared" si="7"/>
+        <v>0.96296296296296302</v>
+      </c>
+      <c r="K65" s="5">
+        <f>Tabla158[[#This Row],[FTQ]]</f>
+        <v>0.96296296296296302</v>
+      </c>
+      <c r="M65" s="4">
+        <v>46265</v>
+      </c>
+      <c r="N65" s="12">
+        <f>WEEKNUM(Tabla2610[[#This Row],[Fecha]])</f>
+        <v>36</v>
+      </c>
+      <c r="O65" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="P65" s="1">
+        <v>200</v>
+      </c>
+      <c r="Q65" s="9">
+        <v>12260416</v>
+      </c>
+      <c r="R65" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="S65" s="1">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="66" spans="2:19" x14ac:dyDescent="0.3">
+      <c r="B66" s="4">
+        <v>46265</v>
+      </c>
+      <c r="C66" s="12">
+        <f>WEEKNUM(Tabla158[[#This Row],[Fecha]])</f>
+        <v>36</v>
+      </c>
+      <c r="D66" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="E66" s="1">
+        <v>400</v>
+      </c>
+      <c r="F66" s="9">
+        <v>12260415</v>
+      </c>
+      <c r="G66" s="1">
+        <v>80</v>
+      </c>
+      <c r="H66" s="1">
+        <v>7</v>
+      </c>
+      <c r="I66" s="3">
+        <f>Tabla158[[#This Row],[Piezas NOK]]/Tabla158[[#This Row],[Piezas OK]]</f>
+        <v>8.7499999999999994E-2</v>
+      </c>
+      <c r="J66" s="12">
+        <f t="shared" si="7"/>
+        <v>0.91249999999999998</v>
+      </c>
+      <c r="K66" s="5">
+        <f>Tabla158[[#This Row],[FTQ]]</f>
+        <v>0.91249999999999998</v>
+      </c>
+      <c r="M66" s="4">
+        <v>46265</v>
+      </c>
+      <c r="N66" s="12">
+        <f>WEEKNUM(Tabla2610[[#This Row],[Fecha]])</f>
+        <v>36</v>
+      </c>
+      <c r="O66" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="P66" s="1">
+        <v>300</v>
+      </c>
+      <c r="Q66" s="9">
+        <v>12260415</v>
+      </c>
+      <c r="R66" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="S66" s="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:19" x14ac:dyDescent="0.3">
+      <c r="B67" s="4">
+        <v>46265</v>
+      </c>
+      <c r="C67" s="12">
+        <f>WEEKNUM(Tabla158[[#This Row],[Fecha]])</f>
+        <v>36</v>
+      </c>
+      <c r="D67" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="E67" s="1">
+        <v>600</v>
+      </c>
+      <c r="F67" s="9">
+        <v>12260415</v>
+      </c>
+      <c r="G67" s="1">
+        <v>75</v>
+      </c>
+      <c r="H67" s="1">
+        <v>3</v>
+      </c>
+      <c r="I67" s="3">
+        <f>Tabla158[[#This Row],[Piezas NOK]]/Tabla158[[#This Row],[Piezas OK]]</f>
+        <v>0.04</v>
+      </c>
+      <c r="J67" s="12">
+        <f t="shared" si="7"/>
+        <v>0.96</v>
+      </c>
+      <c r="K67" s="5">
+        <f>Tabla158[[#This Row],[FTQ]]</f>
+        <v>0.96</v>
+      </c>
+      <c r="M67" s="4">
+        <v>46265</v>
+      </c>
+      <c r="N67" s="12">
+        <f>WEEKNUM(Tabla2610[[#This Row],[Fecha]])</f>
+        <v>36</v>
+      </c>
+      <c r="O67" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="P67" s="1">
+        <v>300</v>
+      </c>
+      <c r="Q67" s="9">
+        <v>12260416</v>
+      </c>
+      <c r="R67" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="S67" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="68" spans="2:19" x14ac:dyDescent="0.3">
+      <c r="B68" s="4">
+        <v>46265</v>
+      </c>
+      <c r="C68" s="12">
+        <f>WEEKNUM(Tabla158[[#This Row],[Fecha]])</f>
+        <v>36</v>
+      </c>
+      <c r="D68" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="E68" s="1">
+        <v>700</v>
+      </c>
+      <c r="F68" s="9">
+        <v>12260415</v>
+      </c>
+      <c r="G68" s="1">
+        <v>75</v>
+      </c>
+      <c r="H68" s="1">
+        <v>2</v>
+      </c>
+      <c r="I68" s="3">
+        <f>Tabla158[[#This Row],[Piezas NOK]]/Tabla158[[#This Row],[Piezas OK]]</f>
+        <v>2.6666666666666668E-2</v>
+      </c>
+      <c r="J68" s="12">
+        <f t="shared" si="7"/>
+        <v>0.97333333333333338</v>
+      </c>
+      <c r="K68" s="5">
+        <f>Tabla158[[#This Row],[FTQ]]</f>
+        <v>0.97333333333333338</v>
+      </c>
+      <c r="M68" s="4">
+        <v>46265</v>
+      </c>
+      <c r="N68" s="12">
+        <f>WEEKNUM(Tabla2610[[#This Row],[Fecha]])</f>
+        <v>36</v>
+      </c>
+      <c r="O68" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="P68" s="1">
+        <v>400</v>
+      </c>
+      <c r="Q68" s="9">
+        <v>12260415</v>
+      </c>
+      <c r="R68" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="S68" s="1">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="69" spans="2:19" x14ac:dyDescent="0.3">
+      <c r="B69" s="4">
+        <v>46265</v>
+      </c>
+      <c r="C69" s="12">
+        <f>WEEKNUM(Tabla158[[#This Row],[Fecha]])</f>
+        <v>36</v>
+      </c>
+      <c r="D69" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="E69" s="1">
+        <v>800</v>
+      </c>
+      <c r="F69" s="9">
+        <v>12260415</v>
+      </c>
+      <c r="G69" s="1">
+        <v>37</v>
+      </c>
+      <c r="H69" s="1">
+        <v>17</v>
+      </c>
+      <c r="I69" s="3">
+        <f>Tabla158[[#This Row],[Piezas NOK]]/Tabla158[[#This Row],[Piezas OK]]</f>
+        <v>0.45945945945945948</v>
+      </c>
+      <c r="J69" s="12">
+        <f t="shared" si="7"/>
+        <v>0.54054054054054057</v>
+      </c>
+      <c r="K69" s="5">
+        <f>Tabla158[[#This Row],[FTQ]]</f>
+        <v>0.54054054054054057</v>
+      </c>
+      <c r="M69" s="4">
+        <v>46265</v>
+      </c>
+      <c r="N69" s="12">
+        <f>WEEKNUM(Tabla2610[[#This Row],[Fecha]])</f>
+        <v>36</v>
+      </c>
+      <c r="O69" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="P69" s="1">
+        <v>400</v>
+      </c>
+      <c r="Q69" s="9">
+        <v>12260416</v>
+      </c>
+      <c r="R69" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="S69" s="1">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="70" spans="2:19" x14ac:dyDescent="0.3">
+      <c r="B70" s="4">
+        <v>46265</v>
+      </c>
+      <c r="C70" s="12">
+        <f>WEEKNUM(Tabla158[[#This Row],[Fecha]])</f>
+        <v>36</v>
+      </c>
+      <c r="D70" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="E70" s="1">
+        <v>900</v>
+      </c>
+      <c r="F70" s="9">
+        <v>12260415</v>
+      </c>
+      <c r="G70" s="1">
+        <v>57</v>
+      </c>
+      <c r="H70" s="1">
+        <v>5</v>
+      </c>
+      <c r="I70" s="3">
+        <f>Tabla158[[#This Row],[Piezas NOK]]/Tabla158[[#This Row],[Piezas OK]]</f>
+        <v>8.771929824561403E-2</v>
+      </c>
+      <c r="J70" s="12">
+        <f t="shared" si="7"/>
+        <v>0.91228070175438591</v>
+      </c>
+      <c r="K70" s="5">
+        <f>Tabla158[[#This Row],[FTQ]]</f>
+        <v>0.91228070175438591</v>
+      </c>
+      <c r="M70" s="4">
+        <v>46265</v>
+      </c>
+      <c r="N70" s="12">
+        <f>WEEKNUM(Tabla2610[[#This Row],[Fecha]])</f>
+        <v>36</v>
+      </c>
+      <c r="O70" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="P70" s="1">
+        <v>400</v>
+      </c>
+      <c r="Q70" s="9">
+        <v>12260416</v>
+      </c>
+      <c r="R70" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="S70" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="71" spans="2:19" x14ac:dyDescent="0.3">
+      <c r="B71" s="4">
+        <v>46265</v>
+      </c>
+      <c r="C71" s="12">
+        <f>WEEKNUM(Tabla158[[#This Row],[Fecha]])</f>
+        <v>36</v>
+      </c>
+      <c r="D71" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="E71" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="F71" s="9">
+        <v>12260415</v>
+      </c>
+      <c r="G71" s="1">
+        <v>57</v>
+      </c>
+      <c r="H71" s="1">
+        <v>3</v>
+      </c>
+      <c r="I71" s="3">
+        <f>Tabla158[[#This Row],[Piezas NOK]]/Tabla158[[#This Row],[Piezas OK]]</f>
+        <v>5.2631578947368418E-2</v>
+      </c>
+      <c r="J71" s="12">
+        <f t="shared" si="7"/>
+        <v>0.94736842105263164</v>
+      </c>
+      <c r="K71" s="5">
+        <f>Tabla158[[#This Row],[FTQ]]</f>
+        <v>0.94736842105263164</v>
+      </c>
+      <c r="M71" s="4">
+        <v>46265</v>
+      </c>
+      <c r="N71" s="12">
+        <f>WEEKNUM(Tabla2610[[#This Row],[Fecha]])</f>
+        <v>36</v>
+      </c>
+      <c r="O71" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="P71" s="1">
+        <v>600</v>
+      </c>
+      <c r="Q71" s="9">
+        <v>12260415</v>
+      </c>
+      <c r="R71" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="S71" s="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="72" spans="2:19" x14ac:dyDescent="0.3">
+      <c r="B72" s="4">
+        <v>46265</v>
+      </c>
+      <c r="C72" s="12">
+        <f>WEEKNUM(Tabla158[[#This Row],[Fecha]])</f>
+        <v>36</v>
+      </c>
+      <c r="D72" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="E72" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="F72" s="9">
+        <v>12260415</v>
+      </c>
+      <c r="G72" s="1">
+        <v>57</v>
+      </c>
+      <c r="H72" s="1">
+        <v>0</v>
+      </c>
+      <c r="I72" s="3">
+        <f>Tabla158[[#This Row],[Piezas NOK]]/Tabla158[[#This Row],[Piezas OK]]</f>
+        <v>0</v>
+      </c>
+      <c r="J72" s="12">
+        <f t="shared" ref="J72:J75" si="8">ABS(G$3-I72)</f>
+        <v>1</v>
+      </c>
+      <c r="K72" s="5">
+        <f>Tabla158[[#This Row],[FTQ]]</f>
+        <v>1</v>
+      </c>
+      <c r="M72" s="4">
+        <v>46265</v>
+      </c>
+      <c r="N72" s="12">
+        <f>WEEKNUM(Tabla2610[[#This Row],[Fecha]])</f>
+        <v>36</v>
+      </c>
+      <c r="O72" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="P72" s="1">
+        <v>600</v>
+      </c>
+      <c r="Q72" s="9">
+        <v>12260416</v>
+      </c>
+      <c r="R72" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="S72" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="73" spans="2:19" x14ac:dyDescent="0.3">
+      <c r="B73" s="4">
+        <v>46265</v>
+      </c>
+      <c r="C73" s="12">
+        <f>WEEKNUM(Tabla158[[#This Row],[Fecha]])</f>
+        <v>36</v>
+      </c>
+      <c r="D73" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="E73" s="1">
+        <v>100</v>
+      </c>
+      <c r="F73" s="9">
+        <v>12260416</v>
+      </c>
+      <c r="G73" s="1">
+        <v>139</v>
+      </c>
+      <c r="H73" s="1">
+        <v>1</v>
+      </c>
+      <c r="I73" s="3">
+        <f>Tabla158[[#This Row],[Piezas NOK]]/Tabla158[[#This Row],[Piezas OK]]</f>
+        <v>7.1942446043165471E-3</v>
+      </c>
+      <c r="J73" s="12">
+        <f t="shared" si="8"/>
+        <v>0.9928057553956835</v>
+      </c>
+      <c r="K73" s="5">
+        <f>Tabla158[[#This Row],[FTQ]]</f>
+        <v>0.9928057553956835</v>
+      </c>
+      <c r="M73" s="4">
+        <v>46265</v>
+      </c>
+      <c r="N73" s="12">
+        <f>WEEKNUM(Tabla2610[[#This Row],[Fecha]])</f>
+        <v>36</v>
+      </c>
+      <c r="O73" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="P73" s="1">
+        <v>700</v>
+      </c>
+      <c r="Q73" s="9">
+        <v>12260415</v>
+      </c>
+      <c r="R73" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="S73" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="74" spans="2:19" x14ac:dyDescent="0.3">
+      <c r="B74" s="4">
+        <v>46265</v>
+      </c>
+      <c r="C74" s="12">
+        <f>WEEKNUM(Tabla158[[#This Row],[Fecha]])</f>
+        <v>36</v>
+      </c>
+      <c r="D74" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="E74" s="1">
+        <v>200</v>
+      </c>
+      <c r="F74" s="9">
+        <v>12260416</v>
+      </c>
+      <c r="G74" s="1">
+        <v>137</v>
+      </c>
+      <c r="H74" s="1">
+        <v>4</v>
+      </c>
+      <c r="I74" s="3">
+        <f>Tabla158[[#This Row],[Piezas NOK]]/Tabla158[[#This Row],[Piezas OK]]</f>
+        <v>2.9197080291970802E-2</v>
+      </c>
+      <c r="J74" s="12">
+        <f t="shared" si="8"/>
+        <v>0.97080291970802923</v>
+      </c>
+      <c r="K74" s="5">
+        <f>Tabla158[[#This Row],[FTQ]]</f>
+        <v>0.97080291970802923</v>
+      </c>
+      <c r="M74" s="4">
+        <v>46265</v>
+      </c>
+      <c r="N74" s="12">
+        <f>WEEKNUM(Tabla2610[[#This Row],[Fecha]])</f>
+        <v>36</v>
+      </c>
+      <c r="O74" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="P74" s="1">
+        <v>700</v>
+      </c>
+      <c r="Q74" s="9">
+        <v>12260415</v>
+      </c>
+      <c r="R74" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="S74" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="75" spans="2:19" x14ac:dyDescent="0.3">
+      <c r="B75" s="4">
+        <v>46265</v>
+      </c>
+      <c r="C75" s="12">
+        <f>WEEKNUM(Tabla158[[#This Row],[Fecha]])</f>
+        <v>36</v>
+      </c>
+      <c r="D75" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="E75" s="1">
+        <v>300</v>
+      </c>
+      <c r="F75" s="9">
+        <v>12260416</v>
+      </c>
+      <c r="G75" s="1">
+        <v>134</v>
+      </c>
+      <c r="H75" s="1">
+        <v>1</v>
+      </c>
+      <c r="I75" s="3">
+        <f>Tabla158[[#This Row],[Piezas NOK]]/Tabla158[[#This Row],[Piezas OK]]</f>
+        <v>7.462686567164179E-3</v>
+      </c>
+      <c r="J75" s="12">
+        <f t="shared" si="8"/>
+        <v>0.9925373134328358</v>
+      </c>
+      <c r="K75" s="5">
+        <f>Tabla158[[#This Row],[FTQ]]</f>
+        <v>0.9925373134328358</v>
+      </c>
+      <c r="M75" s="4">
+        <v>46265</v>
+      </c>
+      <c r="N75" s="12">
+        <f>WEEKNUM(Tabla2610[[#This Row],[Fecha]])</f>
+        <v>36</v>
+      </c>
+      <c r="O75" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="P75" s="1">
+        <v>700</v>
+      </c>
+      <c r="Q75" s="9">
+        <v>12260416</v>
+      </c>
+      <c r="R75" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="S75" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="76" spans="2:19" x14ac:dyDescent="0.3">
+      <c r="B76" s="4">
+        <v>46265</v>
+      </c>
+      <c r="C76" s="12">
+        <f>WEEKNUM(Tabla158[[#This Row],[Fecha]])</f>
+        <v>36</v>
+      </c>
+      <c r="D76" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="E76" s="1">
+        <v>400</v>
+      </c>
+      <c r="F76" s="9">
+        <v>12260416</v>
+      </c>
+      <c r="G76" s="1">
+        <v>125</v>
+      </c>
+      <c r="H76" s="1">
+        <v>5</v>
+      </c>
+      <c r="I76" s="3">
+        <f>Tabla158[[#This Row],[Piezas NOK]]/Tabla158[[#This Row],[Piezas OK]]</f>
+        <v>0.04</v>
+      </c>
+      <c r="J76" s="12">
+        <f t="shared" ref="J76:J82" si="9">ABS(G$3-I76)</f>
+        <v>0.96</v>
+      </c>
+      <c r="K76" s="5">
+        <f>Tabla158[[#This Row],[FTQ]]</f>
+        <v>0.96</v>
+      </c>
+      <c r="M76" s="4">
+        <v>46265</v>
+      </c>
+      <c r="N76" s="12">
+        <f>WEEKNUM(Tabla2610[[#This Row],[Fecha]])</f>
+        <v>36</v>
+      </c>
+      <c r="O76" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="P76" s="1">
+        <v>800</v>
+      </c>
+      <c r="Q76" s="9">
+        <v>12260415</v>
+      </c>
+      <c r="R76" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="S76" s="1">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="77" spans="2:19" x14ac:dyDescent="0.3">
+      <c r="B77" s="4">
+        <v>46265</v>
+      </c>
+      <c r="C77" s="12">
+        <f>WEEKNUM(Tabla158[[#This Row],[Fecha]])</f>
+        <v>36</v>
+      </c>
+      <c r="D77" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="E77" s="1">
+        <v>600</v>
+      </c>
+      <c r="F77" s="9">
+        <v>12260416</v>
+      </c>
+      <c r="G77" s="1">
+        <v>128</v>
+      </c>
+      <c r="H77" s="1">
+        <v>1</v>
+      </c>
+      <c r="I77" s="3">
+        <f>Tabla158[[#This Row],[Piezas NOK]]/Tabla158[[#This Row],[Piezas OK]]</f>
+        <v>7.8125E-3</v>
+      </c>
+      <c r="J77" s="12">
+        <f t="shared" si="9"/>
+        <v>0.9921875</v>
+      </c>
+      <c r="K77" s="5">
+        <f>Tabla158[[#This Row],[FTQ]]</f>
+        <v>0.9921875</v>
+      </c>
+      <c r="M77" s="4">
+        <v>46265</v>
+      </c>
+      <c r="N77" s="12">
+        <f>WEEKNUM(Tabla2610[[#This Row],[Fecha]])</f>
+        <v>36</v>
+      </c>
+      <c r="O77" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="P77" s="1">
+        <v>800</v>
+      </c>
+      <c r="Q77" s="9">
+        <v>12260415</v>
+      </c>
+      <c r="R77" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="S77" s="1">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="78" spans="2:19" x14ac:dyDescent="0.3">
+      <c r="B78" s="4">
+        <v>46265</v>
+      </c>
+      <c r="C78" s="12">
+        <f>WEEKNUM(Tabla158[[#This Row],[Fecha]])</f>
+        <v>36</v>
+      </c>
+      <c r="D78" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="E78" s="1">
+        <v>700</v>
+      </c>
+      <c r="F78" s="9">
+        <v>12260416</v>
+      </c>
+      <c r="G78" s="1">
+        <v>122</v>
+      </c>
+      <c r="H78" s="1">
+        <v>2</v>
+      </c>
+      <c r="I78" s="3">
+        <f>Tabla158[[#This Row],[Piezas NOK]]/Tabla158[[#This Row],[Piezas OK]]</f>
+        <v>1.6393442622950821E-2</v>
+      </c>
+      <c r="J78" s="12">
+        <f t="shared" si="9"/>
+        <v>0.98360655737704916</v>
+      </c>
+      <c r="K78" s="5">
+        <f>Tabla158[[#This Row],[FTQ]]</f>
+        <v>0.98360655737704916</v>
+      </c>
+      <c r="M78" s="4">
+        <v>46265</v>
+      </c>
+      <c r="N78" s="12">
+        <f>WEEKNUM(Tabla2610[[#This Row],[Fecha]])</f>
+        <v>36</v>
+      </c>
+      <c r="O78" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="P78" s="1">
+        <v>800</v>
+      </c>
+      <c r="Q78" s="9">
+        <v>12260415</v>
+      </c>
+      <c r="R78" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="S78" s="1">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="79" spans="2:19" x14ac:dyDescent="0.3">
+      <c r="B79" s="4">
+        <v>46265</v>
+      </c>
+      <c r="C79" s="12">
+        <f>WEEKNUM(Tabla158[[#This Row],[Fecha]])</f>
+        <v>36</v>
+      </c>
+      <c r="D79" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="E79" s="1">
+        <v>800</v>
+      </c>
+      <c r="F79" s="9">
+        <v>12260416</v>
+      </c>
+      <c r="G79" s="1">
+        <v>91</v>
+      </c>
+      <c r="H79" s="1">
+        <v>2</v>
+      </c>
+      <c r="I79" s="3">
+        <f>Tabla158[[#This Row],[Piezas NOK]]/Tabla158[[#This Row],[Piezas OK]]</f>
+        <v>2.197802197802198E-2</v>
+      </c>
+      <c r="J79" s="12">
+        <f t="shared" si="9"/>
+        <v>0.97802197802197799</v>
+      </c>
+      <c r="K79" s="5">
+        <f>Tabla158[[#This Row],[FTQ]]</f>
+        <v>0.97802197802197799</v>
+      </c>
+      <c r="M79" s="4">
+        <v>46265</v>
+      </c>
+      <c r="N79" s="12">
+        <f>WEEKNUM(Tabla2610[[#This Row],[Fecha]])</f>
+        <v>36</v>
+      </c>
+      <c r="O79" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="P79" s="1">
+        <v>800</v>
+      </c>
+      <c r="Q79" s="9">
+        <v>12260416</v>
+      </c>
+      <c r="R79" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="S79" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="80" spans="2:19" x14ac:dyDescent="0.3">
+      <c r="B80" s="4">
+        <v>46265</v>
+      </c>
+      <c r="C80" s="12">
+        <f>WEEKNUM(Tabla158[[#This Row],[Fecha]])</f>
+        <v>36</v>
+      </c>
+      <c r="D80" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="E80" s="1">
+        <v>900</v>
+      </c>
+      <c r="F80" s="9">
+        <v>12260416</v>
+      </c>
+      <c r="G80" s="1">
+        <v>102</v>
+      </c>
+      <c r="H80" s="1">
+        <v>6</v>
+      </c>
+      <c r="I80" s="3">
+        <f>Tabla158[[#This Row],[Piezas NOK]]/Tabla158[[#This Row],[Piezas OK]]</f>
+        <v>5.8823529411764705E-2</v>
+      </c>
+      <c r="J80" s="12">
+        <f t="shared" si="9"/>
+        <v>0.94117647058823528</v>
+      </c>
+      <c r="K80" s="5">
+        <f>Tabla158[[#This Row],[FTQ]]</f>
+        <v>0.94117647058823528</v>
+      </c>
+      <c r="M80" s="4">
+        <v>46265</v>
+      </c>
+      <c r="N80" s="12">
+        <f>WEEKNUM(Tabla2610[[#This Row],[Fecha]])</f>
+        <v>36</v>
+      </c>
+      <c r="O80" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="P80" s="1">
+        <v>900</v>
+      </c>
+      <c r="Q80" s="9">
+        <v>12260415</v>
+      </c>
+      <c r="R80" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="S80" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="81" spans="2:19" x14ac:dyDescent="0.3">
+      <c r="B81" s="4">
+        <v>46265</v>
+      </c>
+      <c r="C81" s="12">
+        <f>WEEKNUM(Tabla158[[#This Row],[Fecha]])</f>
+        <v>36</v>
+      </c>
+      <c r="D81" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="E81" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="F81" s="9">
+        <v>12260416</v>
+      </c>
+      <c r="G81" s="1">
+        <v>102</v>
+      </c>
+      <c r="H81" s="1">
+        <v>0</v>
+      </c>
+      <c r="I81" s="3">
+        <f>Tabla158[[#This Row],[Piezas NOK]]/Tabla158[[#This Row],[Piezas OK]]</f>
+        <v>0</v>
+      </c>
+      <c r="J81" s="12">
+        <f t="shared" si="9"/>
+        <v>1</v>
+      </c>
+      <c r="K81" s="5">
+        <f>Tabla158[[#This Row],[FTQ]]</f>
+        <v>1</v>
+      </c>
+      <c r="M81" s="4">
+        <v>46265</v>
+      </c>
+      <c r="N81" s="12">
+        <f>WEEKNUM(Tabla2610[[#This Row],[Fecha]])</f>
+        <v>36</v>
+      </c>
+      <c r="O81" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="P81" s="1">
+        <v>900</v>
+      </c>
+      <c r="Q81" s="9">
+        <v>12260416</v>
+      </c>
+      <c r="R81" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="S81" s="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="2:19" x14ac:dyDescent="0.3">
+      <c r="B82" s="4">
+        <v>46265</v>
+      </c>
+      <c r="C82" s="12">
+        <f>WEEKNUM(Tabla158[[#This Row],[Fecha]])</f>
+        <v>36</v>
+      </c>
+      <c r="D82" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="E82" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="F82" s="9">
+        <v>12260416</v>
+      </c>
+      <c r="G82" s="1">
+        <v>102</v>
+      </c>
+      <c r="H82" s="1">
+        <v>0</v>
+      </c>
+      <c r="I82" s="3">
+        <f>Tabla158[[#This Row],[Piezas NOK]]/Tabla158[[#This Row],[Piezas OK]]</f>
+        <v>0</v>
+      </c>
+      <c r="J82" s="12">
+        <f t="shared" si="9"/>
+        <v>1</v>
+      </c>
+      <c r="K82" s="5">
+        <f>Tabla158[[#This Row],[FTQ]]</f>
+        <v>1</v>
+      </c>
+      <c r="M82" s="4">
+        <v>46265</v>
+      </c>
+      <c r="N82" s="12">
+        <f>WEEKNUM(Tabla2610[[#This Row],[Fecha]])</f>
+        <v>36</v>
+      </c>
+      <c r="O82" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="P82" s="1">
+        <v>900</v>
+      </c>
+      <c r="Q82" s="9">
+        <v>12260416</v>
+      </c>
+      <c r="R82" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="S82" s="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="83" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B83" s="4"/>
       <c r="I83" s="3"/>
       <c r="J83" s="1"/>
       <c r="K83" s="5"/>
-      <c r="M83" s="4"/>
-    </row>
-    <row r="84" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="M83" s="4">
+        <v>46265</v>
+      </c>
+      <c r="N83" s="12">
+        <f>WEEKNUM(Tabla2610[[#This Row],[Fecha]])</f>
+        <v>36</v>
+      </c>
+      <c r="O83" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="P83" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="Q83" s="9">
+        <v>12260415</v>
+      </c>
+      <c r="R83" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="S83" s="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B84" s="4"/>
       <c r="I84" s="3"/>
       <c r="J84" s="1"/>
       <c r="K84" s="5"/>
       <c r="M84" s="4"/>
     </row>
-    <row r="85" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="85" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B85" s="4"/>
       <c r="I85" s="3"/>
       <c r="J85" s="1"/>
       <c r="K85" s="5"/>
       <c r="M85" s="4"/>
     </row>
-    <row r="86" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="86" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B86" s="4"/>
       <c r="I86" s="3"/>
       <c r="J86" s="1"/>
       <c r="K86" s="5"/>
       <c r="M86" s="4"/>
     </row>
-    <row r="87" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="87" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B87" s="4"/>
       <c r="I87" s="3"/>
       <c r="J87" s="1"/>
       <c r="K87" s="5"/>
       <c r="M87" s="4"/>
     </row>
-    <row r="88" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="88" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B88" s="4"/>
       <c r="I88" s="3"/>
       <c r="J88" s="1"/>
       <c r="K88" s="5"/>
       <c r="M88" s="4"/>
     </row>
-    <row r="89" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="89" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B89" s="4"/>
       <c r="I89" s="3"/>
       <c r="J89" s="1"/>
       <c r="K89" s="5"/>
       <c r="M89" s="4"/>
     </row>
-    <row r="90" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="90" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B90" s="4"/>
       <c r="I90" s="3"/>
       <c r="J90" s="1"/>
       <c r="K90" s="5"/>
       <c r="M90" s="4"/>
     </row>
-    <row r="91" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="91" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B91" s="4"/>
       <c r="I91" s="3"/>
       <c r="J91" s="1"/>
       <c r="K91" s="5"/>
       <c r="M91" s="4"/>
     </row>
-    <row r="92" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="92" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B92" s="4"/>
       <c r="I92" s="3"/>
       <c r="J92" s="1"/>
       <c r="K92" s="5"/>
       <c r="M92" s="4"/>
     </row>
-    <row r="93" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="93" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B93" s="4"/>
       <c r="I93" s="3"/>
       <c r="J93" s="1"/>
       <c r="K93" s="5"/>
       <c r="M93" s="4"/>
     </row>
-    <row r="94" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="94" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B94" s="4"/>
       <c r="I94" s="3"/>
       <c r="J94" s="1"/>
       <c r="K94" s="5"/>
       <c r="M94" s="4"/>
     </row>
-    <row r="95" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="95" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B95" s="4"/>
       <c r="I95" s="3"/>
       <c r="J95" s="1"/>
       <c r="K95" s="5"/>
       <c r="M95" s="4"/>
     </row>
-    <row r="96" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="96" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B96" s="4"/>
       <c r="I96" s="3"/>
       <c r="J96" s="1"/>
